--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -8429,10 +8429,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129056718</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>91805</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,37 +8440,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602758</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8514,19 +8514,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129056699</v>
+        <v>129049465</v>
       </c>
       <c r="B76" t="n">
         <v>80139</v>
@@ -8557,17 +8557,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602729</v>
+        <v>602650</v>
       </c>
       <c r="R76" t="n">
-        <v>7018756</v>
+        <v>7018649</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8611,19 +8611,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129049465</v>
+        <v>129045649</v>
       </c>
       <c r="B77" t="n">
         <v>80139</v>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602650</v>
+        <v>602688</v>
       </c>
       <c r="R77" t="n">
-        <v>7018649</v>
+        <v>7018774</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8720,32 +8720,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129045649</v>
+        <v>129044345</v>
       </c>
       <c r="B78" t="n">
-        <v>80139</v>
+        <v>91721</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602688</v>
+        <v>602772</v>
       </c>
       <c r="R78" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8817,48 +8817,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129044345</v>
+        <v>129056676</v>
       </c>
       <c r="B79" t="n">
-        <v>91721</v>
+        <v>57723</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602772</v>
+        <v>602667</v>
       </c>
       <c r="R79" t="n">
-        <v>7018759</v>
+        <v>7018779</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8888,6 +8888,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8902,22 +8907,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129046472</v>
+        <v>129056718</v>
       </c>
       <c r="B80" t="n">
-        <v>91805</v>
+        <v>79034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8925,37 +8930,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602666</v>
+        <v>602758</v>
       </c>
       <c r="R80" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,22 +9004,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129056699</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602729</v>
       </c>
       <c r="R81" t="n">
-        <v>7018779</v>
+        <v>7018756</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,48 +9113,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129045508</v>
+        <v>129058573</v>
       </c>
       <c r="B82" t="n">
-        <v>91805</v>
+        <v>98651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602674</v>
+        <v>602756</v>
       </c>
       <c r="R82" t="n">
-        <v>7018842</v>
+        <v>7018669</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9192,50 +9196,51 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129046057</v>
+        <v>129048233</v>
       </c>
       <c r="B83" t="n">
-        <v>80099</v>
+        <v>79034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9245,10 +9250,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602648</v>
+        <v>602744</v>
       </c>
       <c r="R83" t="n">
-        <v>7018840</v>
+        <v>7018615</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9307,10 +9312,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129056687</v>
+        <v>129048100</v>
       </c>
       <c r="B84" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,37 +9323,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602733</v>
+        <v>602670</v>
       </c>
       <c r="R84" t="n">
-        <v>7018822</v>
+        <v>7018643</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9392,64 +9397,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058573</v>
+        <v>129045508</v>
       </c>
       <c r="B85" t="n">
-        <v>98651</v>
+        <v>91805</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602756</v>
+        <v>602674</v>
       </c>
       <c r="R85" t="n">
-        <v>7018669</v>
+        <v>7018842</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9487,51 +9488,50 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129048233</v>
+        <v>129046057</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>80099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602744</v>
+        <v>602648</v>
       </c>
       <c r="R86" t="n">
-        <v>7018615</v>
+        <v>7018840</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129048100</v>
+        <v>129056687</v>
       </c>
       <c r="B87" t="n">
-        <v>80139</v>
+        <v>91805</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9614,37 +9614,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602670</v>
+        <v>602733</v>
       </c>
       <c r="R87" t="n">
-        <v>7018643</v>
+        <v>7018822</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9688,12 +9688,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045453</v>
+        <v>129056697</v>
       </c>
       <c r="B102" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11086,37 +11086,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602673</v>
+        <v>602730</v>
       </c>
       <c r="R102" t="n">
-        <v>7018844</v>
+        <v>7018719</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11160,12 +11160,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056693</v>
+        <v>129045453</v>
       </c>
       <c r="B107" t="n">
-        <v>80139</v>
+        <v>91520</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11571,37 +11571,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602670</v>
+        <v>602673</v>
       </c>
       <c r="R107" t="n">
-        <v>7018818</v>
+        <v>7018844</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11631,11 +11631,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11650,19 +11645,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056697</v>
+        <v>129056693</v>
       </c>
       <c r="B108" t="n">
         <v>80139</v>
@@ -11697,10 +11692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602730</v>
+        <v>602670</v>
       </c>
       <c r="R108" t="n">
-        <v>7018719</v>
+        <v>7018818</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11733,6 +11728,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11759,52 +11759,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129050244</v>
+        <v>129056684</v>
       </c>
       <c r="B109" t="n">
-        <v>98651</v>
+        <v>91805</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602665</v>
+        <v>602651</v>
       </c>
       <c r="R109" t="n">
-        <v>7018784</v>
+        <v>7018826</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11848,22 +11844,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056684</v>
+        <v>129056671</v>
       </c>
       <c r="B110" t="n">
-        <v>91805</v>
+        <v>91520</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11871,21 +11867,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11895,10 +11891,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602651</v>
+        <v>602735</v>
       </c>
       <c r="R110" t="n">
-        <v>7018826</v>
+        <v>7018592</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11957,48 +11953,52 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129056671</v>
+        <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602735</v>
+        <v>602665</v>
       </c>
       <c r="R111" t="n">
-        <v>7018592</v>
+        <v>7018784</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,64 +12042,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044719</v>
+        <v>129056708</v>
       </c>
       <c r="B112" t="n">
-        <v>98651</v>
+        <v>91538</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602727</v>
+        <v>602663</v>
       </c>
       <c r="R112" t="n">
-        <v>7018795</v>
+        <v>7018823</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12143,60 +12139,60 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129056708</v>
+        <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>91538</v>
+        <v>91485</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602663</v>
+        <v>602669</v>
       </c>
       <c r="R113" t="n">
-        <v>7018823</v>
+        <v>7018753</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12240,12 +12236,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12349,45 +12345,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129046525</v>
+        <v>129046367</v>
       </c>
       <c r="B115" t="n">
-        <v>91485</v>
+        <v>57723</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602669</v>
+        <v>602644</v>
       </c>
       <c r="R115" t="n">
-        <v>7018753</v>
+        <v>7018800</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12420,6 +12421,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12446,7 +12452,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129046367</v>
+        <v>129044230</v>
       </c>
       <c r="B116" t="n">
         <v>57723</v>
@@ -12477,7 +12483,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12486,10 +12492,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602644</v>
+        <v>602777</v>
       </c>
       <c r="R116" t="n">
-        <v>7018800</v>
+        <v>7018753</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12526,7 +12532,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12553,38 +12559,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129044230</v>
+        <v>129044719</v>
       </c>
       <c r="B117" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -12593,10 +12598,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602777</v>
+        <v>602727</v>
       </c>
       <c r="R117" t="n">
-        <v>7018753</v>
+        <v>7018795</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12629,11 +12634,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12660,10 +12660,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129050601</v>
+        <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>10964</v>
+        <v>91538</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,38 +12671,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>101449</v>
+        <v>5432</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602698</v>
+        <v>602766</v>
       </c>
       <c r="R118" t="n">
-        <v>7018836</v>
+        <v>7018781</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12737,18 +12733,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12760,55 +12750,59 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B119" t="n">
-        <v>98651</v>
+        <v>10964</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R119" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12842,7 +12836,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12851,28 +12845,29 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129044475</v>
+        <v>129056702</v>
       </c>
       <c r="B120" t="n">
-        <v>91538</v>
+        <v>80139</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12880,37 +12875,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602766</v>
+        <v>602649</v>
       </c>
       <c r="R120" t="n">
-        <v>7018781</v>
+        <v>7018829</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12954,22 +12949,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056702</v>
+        <v>129056681</v>
       </c>
       <c r="B121" t="n">
-        <v>80139</v>
+        <v>91805</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12977,21 +12972,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13001,10 +12996,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602649</v>
+        <v>602736</v>
       </c>
       <c r="R121" t="n">
-        <v>7018829</v>
+        <v>7018593</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13063,32 +13058,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056681</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>91805</v>
+        <v>98651</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13098,10 +13093,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602736</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018593</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13134,6 +13129,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13160,7 +13160,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129044962</v>
+        <v>129056668</v>
       </c>
       <c r="B123" t="n">
         <v>91485</v>
@@ -13191,17 +13191,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602750</v>
+        <v>602738</v>
       </c>
       <c r="R123" t="n">
-        <v>7018799</v>
+        <v>7018795</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13245,64 +13245,60 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129046716</v>
+        <v>129056700</v>
       </c>
       <c r="B124" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602747</v>
+        <v>602684</v>
       </c>
       <c r="R124" t="n">
-        <v>7018722</v>
+        <v>7018776</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13346,60 +13342,60 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056700</v>
+        <v>129050404</v>
       </c>
       <c r="B125" t="n">
-        <v>80139</v>
+        <v>80168</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R125" t="n">
-        <v>7018776</v>
+        <v>7018808</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13443,60 +13439,60 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129050404</v>
+        <v>129056689</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>91805</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602672</v>
+        <v>602754</v>
       </c>
       <c r="R126" t="n">
-        <v>7018808</v>
+        <v>7018806</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,60 +13536,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056689</v>
+        <v>129044962</v>
       </c>
       <c r="B127" t="n">
-        <v>91805</v>
+        <v>91485</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602754</v>
+        <v>602750</v>
       </c>
       <c r="R127" t="n">
-        <v>7018806</v>
+        <v>7018799</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,60 +13633,64 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056668</v>
+        <v>129046716</v>
       </c>
       <c r="B128" t="n">
-        <v>91485</v>
+        <v>98651</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602738</v>
+        <v>602747</v>
       </c>
       <c r="R128" t="n">
-        <v>7018795</v>
+        <v>7018722</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,12 +13734,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14522,52 +14522,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129046891</v>
+        <v>129056694</v>
       </c>
       <c r="B137" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602726</v>
+        <v>602656</v>
       </c>
       <c r="R137" t="n">
-        <v>7018723</v>
+        <v>7018656</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14611,22 +14607,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056694</v>
+        <v>129056692</v>
       </c>
       <c r="B138" t="n">
-        <v>80139</v>
+        <v>10964</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14634,21 +14630,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14658,10 +14649,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602656</v>
+        <v>602687</v>
       </c>
       <c r="R138" t="n">
-        <v>7018656</v>
+        <v>7018836</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14720,48 +14711,52 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056667</v>
+        <v>129046891</v>
       </c>
       <c r="B139" t="n">
-        <v>96897</v>
+        <v>98651</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602672</v>
+        <v>602726</v>
       </c>
       <c r="R139" t="n">
-        <v>7018807</v>
+        <v>7018723</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14805,22 +14800,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056692</v>
+        <v>129056667</v>
       </c>
       <c r="B140" t="n">
-        <v>10964</v>
+        <v>96897</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14828,16 +14823,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101449</v>
+        <v>53</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602687</v>
+        <v>602672</v>
       </c>
       <c r="R140" t="n">
-        <v>7018836</v>
+        <v>7018807</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15506,49 +15506,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129045069</v>
+        <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602751</v>
+        <v>602748</v>
       </c>
       <c r="R147" t="n">
-        <v>7018815</v>
+        <v>7018591</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15607,7 +15603,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
         <v>98651</v>
@@ -15646,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15708,45 +15704,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129048489</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602748</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018591</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16193,48 +16193,43 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129050391</v>
+        <v>129056691</v>
       </c>
       <c r="B154" t="n">
-        <v>80043</v>
+        <v>10964</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602671</v>
+        <v>602659</v>
       </c>
       <c r="R154" t="n">
-        <v>7018809</v>
+        <v>7018825</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16278,44 +16273,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129044275</v>
+        <v>129045378</v>
       </c>
       <c r="B155" t="n">
-        <v>91805</v>
+        <v>92218</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16325,10 +16320,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602766</v>
+        <v>602682</v>
       </c>
       <c r="R155" t="n">
-        <v>7018767</v>
+        <v>7018833</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16387,10 +16382,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129056691</v>
+        <v>129044275</v>
       </c>
       <c r="B156" t="n">
-        <v>10964</v>
+        <v>91805</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16398,32 +16393,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602659</v>
+        <v>602766</v>
       </c>
       <c r="R156" t="n">
-        <v>7018825</v>
+        <v>7018767</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16467,57 +16467,61 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129045378</v>
+        <v>129048151</v>
       </c>
       <c r="B157" t="n">
-        <v>92218</v>
+        <v>98651</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602682</v>
+        <v>602715</v>
       </c>
       <c r="R157" t="n">
-        <v>7018833</v>
+        <v>7018634</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16576,49 +16580,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B158" t="n">
-        <v>98651</v>
+        <v>80043</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R158" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16774,10 +16774,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129047010</v>
+        <v>129045867</v>
       </c>
       <c r="B160" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,21 +16785,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602728</v>
+        <v>602663</v>
       </c>
       <c r="R160" t="n">
-        <v>7018716</v>
+        <v>7018805</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16871,48 +16871,52 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129045867</v>
+        <v>129058444</v>
       </c>
       <c r="B161" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R161" t="n">
-        <v>7018805</v>
+        <v>7018673</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16950,67 +16954,64 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B162" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R162" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -17069,48 +17070,52 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129056685</v>
+        <v>129044553</v>
       </c>
       <c r="B163" t="n">
-        <v>91805</v>
+        <v>98651</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602683</v>
+        <v>602758</v>
       </c>
       <c r="R163" t="n">
-        <v>7018835</v>
+        <v>7018769</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17154,61 +17159,57 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129058444</v>
+        <v>129056685</v>
       </c>
       <c r="B164" t="n">
-        <v>98651</v>
+        <v>91805</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602760</v>
+        <v>602683</v>
       </c>
       <c r="R164" t="n">
-        <v>7018673</v>
+        <v>7018835</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17249,7 +17250,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,48 +6872,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056682</v>
+        <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>91805</v>
+        <v>80043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602751</v>
+        <v>602684</v>
       </c>
       <c r="R59" t="n">
-        <v>7018603</v>
+        <v>7018786</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,22 +6957,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056690</v>
+        <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602758</v>
+        <v>602751</v>
       </c>
       <c r="R60" t="n">
-        <v>7018806</v>
+        <v>7018603</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,48 +7066,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045660</v>
+        <v>129056690</v>
       </c>
       <c r="B61" t="n">
-        <v>80043</v>
+        <v>91808</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602684</v>
+        <v>602758</v>
       </c>
       <c r="R61" t="n">
-        <v>7018786</v>
+        <v>7018806</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,44 +7151,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129045225</v>
       </c>
       <c r="B62" t="n">
-        <v>91805</v>
+        <v>97527</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602705</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018799</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,48 +7260,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048001</v>
+        <v>129056720</v>
       </c>
       <c r="B63" t="n">
-        <v>91975</v>
+        <v>80174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602696</v>
+        <v>602773</v>
       </c>
       <c r="R63" t="n">
-        <v>7018662</v>
+        <v>7018642</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129045225</v>
+        <v>129050367</v>
       </c>
       <c r="B64" t="n">
-        <v>97522</v>
+        <v>80099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602705</v>
+        <v>602671</v>
       </c>
       <c r="R64" t="n">
-        <v>7018799</v>
+        <v>7018809</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7454,32 +7454,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129050367</v>
+        <v>129048977</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>91808</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602671</v>
+        <v>602712</v>
       </c>
       <c r="R65" t="n">
-        <v>7018809</v>
+        <v>7018600</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7551,48 +7551,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129056720</v>
+        <v>129048001</v>
       </c>
       <c r="B66" t="n">
-        <v>80174</v>
+        <v>91978</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602773</v>
+        <v>602696</v>
       </c>
       <c r="R66" t="n">
-        <v>7018642</v>
+        <v>7018662</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7636,44 +7636,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045733</v>
+        <v>129044277</v>
       </c>
       <c r="B67" t="n">
-        <v>80168</v>
+        <v>91523</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602669</v>
+        <v>602759</v>
       </c>
       <c r="R67" t="n">
-        <v>7018781</v>
+        <v>7018767</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7745,32 +7745,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129050732</v>
+        <v>129045343</v>
       </c>
       <c r="B68" t="n">
-        <v>91805</v>
+        <v>91934</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602710</v>
+        <v>602684</v>
       </c>
       <c r="R68" t="n">
-        <v>7018856</v>
+        <v>7018837</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7816,6 +7816,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7842,48 +7847,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129056680</v>
+        <v>129050732</v>
       </c>
       <c r="B69" t="n">
-        <v>91975</v>
+        <v>91808</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602732</v>
+        <v>602710</v>
       </c>
       <c r="R69" t="n">
-        <v>7018811</v>
+        <v>7018856</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7927,60 +7932,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129045343</v>
+        <v>129056680</v>
       </c>
       <c r="B70" t="n">
-        <v>91931</v>
+        <v>91978</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4217</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602684</v>
+        <v>602732</v>
       </c>
       <c r="R70" t="n">
-        <v>7018837</v>
+        <v>7018811</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8010,11 +8015,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8029,22 +8029,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129044277</v>
+        <v>129056672</v>
       </c>
       <c r="B71" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8072,17 +8072,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602759</v>
+        <v>602651</v>
       </c>
       <c r="R71" t="n">
-        <v>7018767</v>
+        <v>7018826</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8126,60 +8126,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056715</v>
+        <v>129045733</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602665</v>
+        <v>602669</v>
       </c>
       <c r="R72" t="n">
-        <v>7018777</v>
+        <v>7018781</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,19 +8223,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056712</v>
+        <v>129056715</v>
       </c>
       <c r="B73" t="n">
         <v>79034</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602730</v>
+        <v>602665</v>
       </c>
       <c r="R73" t="n">
-        <v>7018697</v>
+        <v>7018777</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056672</v>
+        <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8343,21 +8343,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602651</v>
+        <v>602730</v>
       </c>
       <c r="R74" t="n">
-        <v>7018826</v>
+        <v>7018697</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8429,32 +8429,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129044345</v>
       </c>
       <c r="B75" t="n">
-        <v>91805</v>
+        <v>91724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602772</v>
       </c>
       <c r="R75" t="n">
         <v>7018759</v>
@@ -8720,48 +8720,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129044345</v>
+        <v>129056718</v>
       </c>
       <c r="B78" t="n">
-        <v>91721</v>
+        <v>79034</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602772</v>
+        <v>602758</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056676</v>
+        <v>129056699</v>
       </c>
       <c r="B79" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602667</v>
+        <v>602729</v>
       </c>
       <c r="R79" t="n">
-        <v>7018779</v>
+        <v>7018756</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8888,11 +8888,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8919,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056718</v>
+        <v>129046472</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8930,37 +8925,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602758</v>
+        <v>602666</v>
       </c>
       <c r="R80" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9004,22 +8999,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056699</v>
+        <v>129056676</v>
       </c>
       <c r="B81" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,21 +9022,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9051,10 +9046,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602729</v>
+        <v>602667</v>
       </c>
       <c r="R81" t="n">
-        <v>7018756</v>
+        <v>7018779</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9087,6 +9082,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,52 +9113,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058573</v>
+        <v>129045508</v>
       </c>
       <c r="B82" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602756</v>
+        <v>602674</v>
       </c>
       <c r="R82" t="n">
-        <v>7018669</v>
+        <v>7018842</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9196,19 +9192,18 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9409,10 +9404,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129045508</v>
+        <v>129056687</v>
       </c>
       <c r="B85" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9440,17 +9435,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602674</v>
+        <v>602733</v>
       </c>
       <c r="R85" t="n">
-        <v>7018842</v>
+        <v>7018822</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9494,12 +9489,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9603,45 +9598,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129056687</v>
+        <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602733</v>
+        <v>602756</v>
       </c>
       <c r="R87" t="n">
-        <v>7018822</v>
+        <v>7018669</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9682,6 +9681,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056711</v>
+        <v>129056686</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,21 +9711,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602771</v>
+        <v>602702</v>
       </c>
       <c r="R88" t="n">
-        <v>7018641</v>
+        <v>7018842</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9797,10 +9797,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056686</v>
+        <v>129056688</v>
       </c>
       <c r="B89" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602702</v>
+        <v>602732</v>
       </c>
       <c r="R89" t="n">
-        <v>7018842</v>
+        <v>7018811</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056688</v>
+        <v>129056711</v>
       </c>
       <c r="B90" t="n">
-        <v>91805</v>
+        <v>79034</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602732</v>
+        <v>602771</v>
       </c>
       <c r="R90" t="n">
-        <v>7018811</v>
+        <v>7018641</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9994,7 +9994,7 @@
         <v>129044846</v>
       </c>
       <c r="B91" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>91538</v>
+        <v>80139</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R93" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,19 +10270,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B94" t="n">
         <v>80139</v>
@@ -10313,17 +10313,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R94" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,12 +10367,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10382,7 +10382,7 @@
         <v>129056683</v>
       </c>
       <c r="B95" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129046062</v>
+        <v>129056698</v>
       </c>
       <c r="B96" t="n">
         <v>80139</v>
@@ -10507,17 +10507,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602648</v>
+        <v>602735</v>
       </c>
       <c r="R96" t="n">
-        <v>7018840</v>
+        <v>7018716</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,22 +10561,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129048547</v>
+        <v>129056709</v>
       </c>
       <c r="B97" t="n">
-        <v>80139</v>
+        <v>91541</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10584,37 +10584,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602747</v>
+        <v>602654</v>
       </c>
       <c r="R97" t="n">
-        <v>7018592</v>
+        <v>7018820</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,22 +10658,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B98" t="n">
-        <v>98651</v>
+        <v>92148</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,38 +10681,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R98" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10747,12 +10746,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10771,51 +10776,52 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058560</v>
+        <v>129045623</v>
       </c>
       <c r="B99" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602760</v>
+        <v>602687</v>
       </c>
       <c r="R99" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10853,26 +10859,25 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129056713</v>
+        <v>129058560</v>
       </c>
       <c r="B100" t="n">
         <v>79034</v>
@@ -10901,16 +10906,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602690</v>
+        <v>602760</v>
       </c>
       <c r="R100" t="n">
-        <v>7018768</v>
+        <v>7018673</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10951,6 +10959,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10969,51 +10978,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129046720</v>
+        <v>129056713</v>
       </c>
       <c r="B101" t="n">
-        <v>92143</v>
+        <v>79034</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602747</v>
+        <v>602690</v>
       </c>
       <c r="R101" t="n">
-        <v>7018721</v>
+        <v>7018768</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11045,37 +11051,31 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129056697</v>
+        <v>129045582</v>
       </c>
       <c r="B102" t="n">
         <v>80139</v>
@@ -11106,17 +11106,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602730</v>
+        <v>602703</v>
       </c>
       <c r="R102" t="n">
-        <v>7018719</v>
+        <v>7018798</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11160,57 +11160,61 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044824</v>
+        <v>129050244</v>
       </c>
       <c r="B103" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602731</v>
+        <v>602665</v>
       </c>
       <c r="R103" t="n">
-        <v>7018789</v>
+        <v>7018784</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11269,10 +11273,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044805</v>
+        <v>129045453</v>
       </c>
       <c r="B104" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11280,21 +11284,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11304,10 +11308,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602747</v>
+        <v>602673</v>
       </c>
       <c r="R104" t="n">
-        <v>7018784</v>
+        <v>7018844</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11366,10 +11370,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045681</v>
+        <v>129044824</v>
       </c>
       <c r="B105" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11377,21 +11381,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11401,10 +11405,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602667</v>
+        <v>602731</v>
       </c>
       <c r="R105" t="n">
-        <v>7018779</v>
+        <v>7018789</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11463,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129045582</v>
+        <v>129044805</v>
       </c>
       <c r="B106" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11474,21 +11478,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11498,10 +11502,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602703</v>
+        <v>602747</v>
       </c>
       <c r="R106" t="n">
-        <v>7018798</v>
+        <v>7018784</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11560,10 +11564,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129045453</v>
+        <v>129045681</v>
       </c>
       <c r="B107" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11571,21 +11575,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11595,10 +11599,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602673</v>
+        <v>602667</v>
       </c>
       <c r="R107" t="n">
-        <v>7018844</v>
+        <v>7018779</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11657,10 +11661,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056693</v>
+        <v>129056684</v>
       </c>
       <c r="B108" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11668,21 +11672,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11692,10 +11696,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602670</v>
+        <v>602651</v>
       </c>
       <c r="R108" t="n">
-        <v>7018818</v>
+        <v>7018826</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11728,11 +11732,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11759,10 +11758,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056684</v>
+        <v>129056671</v>
       </c>
       <c r="B109" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11770,21 +11769,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11794,10 +11793,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602651</v>
+        <v>602735</v>
       </c>
       <c r="R109" t="n">
-        <v>7018826</v>
+        <v>7018592</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11856,10 +11855,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056671</v>
+        <v>129056693</v>
       </c>
       <c r="B110" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11867,21 +11866,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11891,10 +11890,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602735</v>
+        <v>602670</v>
       </c>
       <c r="R110" t="n">
-        <v>7018592</v>
+        <v>7018818</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11927,6 +11926,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11953,52 +11957,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129050244</v>
+        <v>129056697</v>
       </c>
       <c r="B111" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602665</v>
+        <v>602730</v>
       </c>
       <c r="R111" t="n">
-        <v>7018784</v>
+        <v>7018719</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,60 +12042,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129056708</v>
+        <v>129044298</v>
       </c>
       <c r="B112" t="n">
-        <v>91538</v>
+        <v>91978</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R112" t="n">
-        <v>7018823</v>
+        <v>7018767</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12139,12 +12139,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
         <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12248,45 +12248,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129044298</v>
+        <v>129044230</v>
       </c>
       <c r="B114" t="n">
-        <v>91975</v>
+        <v>57723</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602760</v>
+        <v>602777</v>
       </c>
       <c r="R114" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12319,6 +12324,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12452,38 +12462,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044230</v>
+        <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12492,10 +12501,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602777</v>
+        <v>602727</v>
       </c>
       <c r="R116" t="n">
-        <v>7018753</v>
+        <v>7018795</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12528,11 +12537,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12559,52 +12563,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129044719</v>
+        <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>98651</v>
+        <v>91541</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602727</v>
+        <v>602663</v>
       </c>
       <c r="R117" t="n">
-        <v>7018795</v>
+        <v>7018823</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12648,12 +12648,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12663,7 +12663,7 @@
         <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12757,10 +12757,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129050601</v>
+        <v>129056681</v>
       </c>
       <c r="B119" t="n">
-        <v>10964</v>
+        <v>91808</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,41 +12768,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602698</v>
+        <v>602736</v>
       </c>
       <c r="R119" t="n">
-        <v>7018836</v>
+        <v>7018593</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12834,40 +12830,34 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056702</v>
+        <v>129050601</v>
       </c>
       <c r="B120" t="n">
-        <v>80139</v>
+        <v>10964</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12875,37 +12865,41 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602649</v>
+        <v>602698</v>
       </c>
       <c r="R120" t="n">
-        <v>7018829</v>
+        <v>7018836</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12937,34 +12931,40 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B121" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12972,21 +12972,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R121" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13061,7 +13061,7 @@
         <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13160,48 +13160,52 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129056668</v>
+        <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>91485</v>
+        <v>98656</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602738</v>
+        <v>602747</v>
       </c>
       <c r="R123" t="n">
-        <v>7018795</v>
+        <v>7018722</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13245,22 +13249,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056700</v>
+        <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13268,21 +13272,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13292,10 +13296,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602684</v>
+        <v>602754</v>
       </c>
       <c r="R124" t="n">
-        <v>7018776</v>
+        <v>7018806</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13354,10 +13358,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129050404</v>
+        <v>129056668</v>
       </c>
       <c r="B125" t="n">
-        <v>80168</v>
+        <v>91488</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13365,37 +13369,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602672</v>
+        <v>602738</v>
       </c>
       <c r="R125" t="n">
-        <v>7018808</v>
+        <v>7018795</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13439,22 +13443,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B126" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13462,21 +13466,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13486,10 +13490,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R126" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13548,10 +13552,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129044962</v>
+        <v>129050404</v>
       </c>
       <c r="B127" t="n">
-        <v>91485</v>
+        <v>80168</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13559,21 +13563,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13583,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602750</v>
+        <v>602672</v>
       </c>
       <c r="R127" t="n">
-        <v>7018799</v>
+        <v>7018808</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -13645,49 +13649,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129046716</v>
+        <v>129044962</v>
       </c>
       <c r="B128" t="n">
-        <v>98651</v>
+        <v>91488</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602747</v>
+        <v>602750</v>
       </c>
       <c r="R128" t="n">
-        <v>7018722</v>
+        <v>7018799</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045512</v>
+        <v>129056694</v>
       </c>
       <c r="B132" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602682</v>
+        <v>602656</v>
       </c>
       <c r="R132" t="n">
-        <v>7018827</v>
+        <v>7018656</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,60 +14122,60 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129045677</v>
+        <v>129056675</v>
       </c>
       <c r="B133" t="n">
-        <v>91520</v>
+        <v>92223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018786</v>
+        <v>7018832</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14219,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129046455</v>
+        <v>129045512</v>
       </c>
       <c r="B134" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602667</v>
+        <v>602682</v>
       </c>
       <c r="R134" t="n">
-        <v>7018757</v>
+        <v>7018827</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14328,10 +14328,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129044406</v>
+        <v>129045677</v>
       </c>
       <c r="B135" t="n">
-        <v>80139</v>
+        <v>91523</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14339,21 +14339,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14363,10 +14363,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602756</v>
+        <v>602684</v>
       </c>
       <c r="R135" t="n">
-        <v>7018769</v>
+        <v>7018786</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14425,48 +14425,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056675</v>
+        <v>129046455</v>
       </c>
       <c r="B136" t="n">
-        <v>92218</v>
+        <v>79034</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602672</v>
+        <v>602667</v>
       </c>
       <c r="R136" t="n">
-        <v>7018832</v>
+        <v>7018757</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,19 +14510,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056694</v>
+        <v>129044406</v>
       </c>
       <c r="B137" t="n">
         <v>80139</v>
@@ -14553,17 +14553,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602656</v>
+        <v>602756</v>
       </c>
       <c r="R137" t="n">
-        <v>7018656</v>
+        <v>7018769</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14607,55 +14607,64 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056692</v>
+        <v>129046891</v>
       </c>
       <c r="B138" t="n">
-        <v>10964</v>
+        <v>98656</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602687</v>
+        <v>602726</v>
       </c>
       <c r="R138" t="n">
-        <v>7018836</v>
+        <v>7018723</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14699,64 +14708,60 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129046891</v>
+        <v>129056667</v>
       </c>
       <c r="B139" t="n">
-        <v>98651</v>
+        <v>96902</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602726</v>
+        <v>602672</v>
       </c>
       <c r="R139" t="n">
-        <v>7018723</v>
+        <v>7018807</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14800,22 +14805,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056667</v>
+        <v>129056692</v>
       </c>
       <c r="B140" t="n">
-        <v>96897</v>
+        <v>10964</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14823,21 +14828,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>53</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602672</v>
+        <v>602687</v>
       </c>
       <c r="R140" t="n">
-        <v>7018807</v>
+        <v>7018836</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14909,10 +14909,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129046813</v>
+        <v>129048944</v>
       </c>
       <c r="B141" t="n">
-        <v>91080</v>
+        <v>57723</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,34 +14920,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>937</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602732</v>
+        <v>602734</v>
       </c>
       <c r="R141" t="n">
-        <v>7018701</v>
+        <v>7018579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14980,6 +14985,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15006,32 +15016,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056679</v>
+        <v>129056696</v>
       </c>
       <c r="B142" t="n">
-        <v>91975</v>
+        <v>80139</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15041,10 +15051,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602737</v>
+        <v>602779</v>
       </c>
       <c r="R142" t="n">
-        <v>7018593</v>
+        <v>7018639</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15205,10 +15215,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129048944</v>
+        <v>129046813</v>
       </c>
       <c r="B144" t="n">
-        <v>57723</v>
+        <v>91083</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15216,39 +15226,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>937</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602734</v>
+        <v>602732</v>
       </c>
       <c r="R144" t="n">
-        <v>7018579</v>
+        <v>7018701</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -15281,11 +15286,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15312,32 +15312,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B145" t="n">
-        <v>80139</v>
+        <v>91978</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15347,10 +15347,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R145" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15409,7 +15409,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B146" t="n">
         <v>80139</v>
@@ -15444,10 +15444,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R146" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15506,45 +15506,49 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129048489</v>
+        <v>129045069</v>
       </c>
       <c r="B147" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602748</v>
+        <v>602751</v>
       </c>
       <c r="R147" t="n">
-        <v>7018591</v>
+        <v>7018815</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15603,10 +15607,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B148" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15642,10 +15646,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R148" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15704,49 +15708,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129046445</v>
+        <v>129048489</v>
       </c>
       <c r="B149" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602669</v>
+        <v>602748</v>
       </c>
       <c r="R149" t="n">
-        <v>7018754</v>
+        <v>7018591</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>90552</v>
+        <v>91808</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15816,21 +15816,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15840,10 +15840,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R150" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15902,10 +15902,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046382</v>
+        <v>129046543</v>
       </c>
       <c r="B151" t="n">
-        <v>91805</v>
+        <v>90555</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602637</v>
+        <v>602686</v>
       </c>
       <c r="R151" t="n">
-        <v>7018802</v>
+        <v>7018745</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15999,48 +15999,48 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129056716</v>
+        <v>129044697</v>
       </c>
       <c r="B152" t="n">
-        <v>79034</v>
+        <v>80099</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602754</v>
+        <v>602730</v>
       </c>
       <c r="R152" t="n">
-        <v>7018801</v>
+        <v>7018771</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16084,60 +16084,60 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129044697</v>
+        <v>129056716</v>
       </c>
       <c r="B153" t="n">
-        <v>80099</v>
+        <v>79034</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602730</v>
+        <v>602754</v>
       </c>
       <c r="R153" t="n">
-        <v>7018771</v>
+        <v>7018801</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16181,55 +16181,60 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129056691</v>
+        <v>129045378</v>
       </c>
       <c r="B154" t="n">
-        <v>10964</v>
+        <v>92223</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>101449</v>
+        <v>3298</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602659</v>
+        <v>602682</v>
       </c>
       <c r="R154" t="n">
-        <v>7018825</v>
+        <v>7018833</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16273,44 +16278,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129045378</v>
+        <v>129044275</v>
       </c>
       <c r="B155" t="n">
-        <v>92218</v>
+        <v>91808</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16320,10 +16325,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602682</v>
+        <v>602766</v>
       </c>
       <c r="R155" t="n">
-        <v>7018833</v>
+        <v>7018767</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16382,45 +16387,49 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129044275</v>
+        <v>129048151</v>
       </c>
       <c r="B156" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602766</v>
+        <v>602715</v>
       </c>
       <c r="R156" t="n">
-        <v>7018767</v>
+        <v>7018634</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16479,49 +16488,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B157" t="n">
-        <v>98651</v>
+        <v>80043</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R157" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16580,48 +16585,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129050391</v>
+        <v>129056714</v>
       </c>
       <c r="B158" t="n">
-        <v>80043</v>
+        <v>79034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602671</v>
+        <v>602678</v>
       </c>
       <c r="R158" t="n">
-        <v>7018809</v>
+        <v>7018771</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16665,22 +16670,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056714</v>
+        <v>129056691</v>
       </c>
       <c r="B159" t="n">
-        <v>79034</v>
+        <v>10964</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16688,21 +16693,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16712,10 +16712,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602678</v>
+        <v>602659</v>
       </c>
       <c r="R159" t="n">
-        <v>7018771</v>
+        <v>7018825</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16774,10 +16774,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129045867</v>
+        <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>80139</v>
+        <v>91523</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,21 +16785,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602663</v>
+        <v>602728</v>
       </c>
       <c r="R160" t="n">
-        <v>7018805</v>
+        <v>7018716</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16871,52 +16871,48 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129058444</v>
+        <v>129045867</v>
       </c>
       <c r="B161" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602760</v>
+        <v>602663</v>
       </c>
       <c r="R161" t="n">
-        <v>7018673</v>
+        <v>7018805</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16954,29 +16950,28 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129047010</v>
+        <v>129056685</v>
       </c>
       <c r="B162" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16984,37 +16979,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602728</v>
+        <v>602683</v>
       </c>
       <c r="R162" t="n">
-        <v>7018716</v>
+        <v>7018835</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17058,22 +17053,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129044553</v>
+        <v>129058444</v>
       </c>
       <c r="B163" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17098,24 +17093,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602758</v>
+        <v>602760</v>
       </c>
       <c r="R163" t="n">
-        <v>7018769</v>
+        <v>7018673</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17153,66 +17148,71 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129056685</v>
+        <v>129044553</v>
       </c>
       <c r="B164" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602683</v>
+        <v>602758</v>
       </c>
       <c r="R164" t="n">
-        <v>7018835</v>
+        <v>7018769</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17256,22 +17256,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129046627</v>
+        <v>129048297</v>
       </c>
       <c r="B165" t="n">
-        <v>78791</v>
+        <v>91808</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,21 +17279,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17303,10 +17303,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602705</v>
+        <v>602752</v>
       </c>
       <c r="R165" t="n">
-        <v>7018763</v>
+        <v>7018614</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17368,7 +17368,7 @@
         <v>129044893</v>
       </c>
       <c r="B166" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17462,10 +17462,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129046592</v>
+        <v>129046627</v>
       </c>
       <c r="B167" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,39 +17473,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602704</v>
+        <v>602705</v>
       </c>
       <c r="R167" t="n">
-        <v>7018751</v>
+        <v>7018763</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17538,11 +17533,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17569,7 +17559,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129048918</v>
+        <v>129046592</v>
       </c>
       <c r="B168" t="n">
         <v>57723</v>
@@ -17609,10 +17599,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602737</v>
+        <v>602704</v>
       </c>
       <c r="R168" t="n">
-        <v>7018577</v>
+        <v>7018751</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17649,7 +17639,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17676,48 +17666,53 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129056678</v>
+        <v>129048918</v>
       </c>
       <c r="B169" t="n">
-        <v>80043</v>
+        <v>57723</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602672</v>
+        <v>602737</v>
       </c>
       <c r="R169" t="n">
-        <v>7018832</v>
+        <v>7018577</v>
       </c>
       <c r="S169" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17747,6 +17742,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17761,44 +17761,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056666</v>
+        <v>129056678</v>
       </c>
       <c r="B170" t="n">
-        <v>96897</v>
+        <v>80043</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17808,10 +17808,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R170" t="n">
-        <v>7018643</v>
+        <v>7018832</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17870,10 +17870,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129048297</v>
+        <v>129056666</v>
       </c>
       <c r="B171" t="n">
-        <v>91805</v>
+        <v>96902</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17881,37 +17881,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602752</v>
+        <v>602756</v>
       </c>
       <c r="R171" t="n">
-        <v>7018614</v>
+        <v>7018643</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>129056690</v>
       </c>
       <c r="B61" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7163,32 +7163,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B62" t="n">
-        <v>97527</v>
+        <v>91811</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R62" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,48 +7260,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129056720</v>
+        <v>129048001</v>
       </c>
       <c r="B63" t="n">
-        <v>80174</v>
+        <v>91981</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602773</v>
+        <v>602696</v>
       </c>
       <c r="R63" t="n">
-        <v>7018642</v>
+        <v>7018662</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129050367</v>
+        <v>129045225</v>
       </c>
       <c r="B64" t="n">
-        <v>80099</v>
+        <v>97530</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602671</v>
+        <v>602705</v>
       </c>
       <c r="R64" t="n">
-        <v>7018809</v>
+        <v>7018799</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B65" t="n">
-        <v>91808</v>
+        <v>80175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R65" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,44 +7539,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129048001</v>
+        <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>91978</v>
+        <v>80100</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R66" t="n">
-        <v>7018662</v>
+        <v>7018809</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7651,7 +7651,7 @@
         <v>129044277</v>
       </c>
       <c r="B67" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>129045343</v>
       </c>
       <c r="B68" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7847,32 +7847,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129050732</v>
+        <v>129045733</v>
       </c>
       <c r="B69" t="n">
-        <v>91808</v>
+        <v>80169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602710</v>
+        <v>602669</v>
       </c>
       <c r="R69" t="n">
-        <v>7018856</v>
+        <v>7018781</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7947,7 +7947,7 @@
         <v>129056680</v>
       </c>
       <c r="B70" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>129056672</v>
       </c>
       <c r="B71" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8138,32 +8138,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129045733</v>
+        <v>129050732</v>
       </c>
       <c r="B72" t="n">
-        <v>80168</v>
+        <v>91811</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602669</v>
+        <v>602710</v>
       </c>
       <c r="R72" t="n">
-        <v>7018781</v>
+        <v>7018856</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8238,7 +8238,7 @@
         <v>129056715</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>129044345</v>
       </c>
       <c r="B75" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>129049465</v>
       </c>
       <c r="B76" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129045649</v>
+        <v>129046472</v>
       </c>
       <c r="B77" t="n">
-        <v>80139</v>
+        <v>91811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8634,21 +8634,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602688</v>
+        <v>602666</v>
       </c>
       <c r="R77" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8720,10 +8720,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129056718</v>
+        <v>129045649</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8731,37 +8731,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602758</v>
+        <v>602688</v>
       </c>
       <c r="R78" t="n">
-        <v>7018806</v>
+        <v>7018774</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056699</v>
+        <v>129056718</v>
       </c>
       <c r="B79" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602729</v>
+        <v>602758</v>
       </c>
       <c r="R79" t="n">
-        <v>7018756</v>
+        <v>7018806</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129046472</v>
+        <v>129056699</v>
       </c>
       <c r="B80" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8925,37 +8925,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602666</v>
+        <v>602729</v>
       </c>
       <c r="R80" t="n">
-        <v>7018759</v>
+        <v>7018756</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,12 +8999,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9116,7 +9116,7 @@
         <v>129045508</v>
       </c>
       <c r="B82" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129048233</v>
+        <v>129048100</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9221,21 +9221,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602744</v>
+        <v>602670</v>
       </c>
       <c r="R83" t="n">
-        <v>7018615</v>
+        <v>7018643</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9307,10 +9307,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048100</v>
+        <v>129048233</v>
       </c>
       <c r="B84" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,21 +9318,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602670</v>
+        <v>602744</v>
       </c>
       <c r="R84" t="n">
-        <v>7018643</v>
+        <v>7018615</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9404,48 +9404,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129056687</v>
+        <v>129046057</v>
       </c>
       <c r="B85" t="n">
-        <v>91808</v>
+        <v>80100</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602733</v>
+        <v>602648</v>
       </c>
       <c r="R85" t="n">
-        <v>7018822</v>
+        <v>7018840</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9489,60 +9489,64 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129046057</v>
+        <v>129058573</v>
       </c>
       <c r="B86" t="n">
-        <v>80099</v>
+        <v>98659</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602648</v>
+        <v>602756</v>
       </c>
       <c r="R86" t="n">
-        <v>7018840</v>
+        <v>7018669</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9580,67 +9584,64 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058573</v>
+        <v>129056687</v>
       </c>
       <c r="B87" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602756</v>
+        <v>602733</v>
       </c>
       <c r="R87" t="n">
-        <v>7018669</v>
+        <v>7018822</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9681,7 +9682,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056686</v>
+        <v>129056688</v>
       </c>
       <c r="B88" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602702</v>
+        <v>602732</v>
       </c>
       <c r="R88" t="n">
-        <v>7018842</v>
+        <v>7018811</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9797,10 +9797,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056688</v>
+        <v>129056686</v>
       </c>
       <c r="B89" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602732</v>
+        <v>602702</v>
       </c>
       <c r="R89" t="n">
-        <v>7018811</v>
+        <v>7018842</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9897,7 +9897,7 @@
         <v>129056711</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>129044846</v>
       </c>
       <c r="B91" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129046062</v>
+        <v>129056709</v>
       </c>
       <c r="B93" t="n">
-        <v>80139</v>
+        <v>91544</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602648</v>
+        <v>602654</v>
       </c>
       <c r="R93" t="n">
-        <v>7018840</v>
+        <v>7018820</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B94" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10313,17 +10313,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R94" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056683</v>
+        <v>129048547</v>
       </c>
       <c r="B95" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,37 +10390,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602739</v>
+        <v>602747</v>
       </c>
       <c r="R95" t="n">
-        <v>7018692</v>
+        <v>7018592</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10464,22 +10464,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056698</v>
+        <v>129046062</v>
       </c>
       <c r="B96" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10507,17 +10507,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602735</v>
+        <v>602648</v>
       </c>
       <c r="R96" t="n">
-        <v>7018716</v>
+        <v>7018840</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,22 +10561,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B97" t="n">
-        <v>91541</v>
+        <v>91811</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10584,21 +10584,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R97" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10673,7 +10673,7 @@
         <v>129046720</v>
       </c>
       <c r="B98" t="n">
-        <v>92148</v>
+        <v>92151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>129045623</v>
       </c>
       <c r="B99" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>129058560</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>129056713</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11075,10 +11075,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045582</v>
+        <v>129044824</v>
       </c>
       <c r="B102" t="n">
-        <v>80139</v>
+        <v>91811</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602703</v>
+        <v>602731</v>
       </c>
       <c r="R102" t="n">
-        <v>7018798</v>
+        <v>7018789</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11172,46 +11172,42 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129050244</v>
+        <v>129044805</v>
       </c>
       <c r="B103" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602665</v>
+        <v>602747</v>
       </c>
       <c r="R103" t="n">
         <v>7018784</v>
@@ -11273,10 +11269,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129045453</v>
+        <v>129045681</v>
       </c>
       <c r="B104" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11284,21 +11280,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11308,10 +11304,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602673</v>
+        <v>602667</v>
       </c>
       <c r="R104" t="n">
-        <v>7018844</v>
+        <v>7018779</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11370,10 +11366,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129044824</v>
+        <v>129045453</v>
       </c>
       <c r="B105" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11381,21 +11377,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11405,10 +11401,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602731</v>
+        <v>602673</v>
       </c>
       <c r="R105" t="n">
-        <v>7018789</v>
+        <v>7018844</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11467,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129044805</v>
+        <v>129056684</v>
       </c>
       <c r="B106" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11498,17 +11494,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602747</v>
+        <v>602651</v>
       </c>
       <c r="R106" t="n">
-        <v>7018784</v>
+        <v>7018826</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11552,22 +11548,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129045681</v>
+        <v>129056671</v>
       </c>
       <c r="B107" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11575,37 +11571,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602667</v>
+        <v>602735</v>
       </c>
       <c r="R107" t="n">
-        <v>7018779</v>
+        <v>7018592</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11649,22 +11645,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056684</v>
+        <v>129056693</v>
       </c>
       <c r="B108" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11672,21 +11668,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11696,10 +11692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602651</v>
+        <v>602670</v>
       </c>
       <c r="R108" t="n">
-        <v>7018826</v>
+        <v>7018818</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11732,6 +11728,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11758,10 +11759,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056671</v>
+        <v>129056697</v>
       </c>
       <c r="B109" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11769,21 +11770,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11793,10 +11794,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602735</v>
+        <v>602730</v>
       </c>
       <c r="R109" t="n">
-        <v>7018592</v>
+        <v>7018719</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11855,48 +11856,52 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056693</v>
+        <v>129050244</v>
       </c>
       <c r="B110" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602670</v>
+        <v>602665</v>
       </c>
       <c r="R110" t="n">
-        <v>7018818</v>
+        <v>7018784</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11926,11 +11931,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11945,22 +11945,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129056697</v>
+        <v>129045582</v>
       </c>
       <c r="B111" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11988,17 +11988,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602730</v>
+        <v>602703</v>
       </c>
       <c r="R111" t="n">
-        <v>7018719</v>
+        <v>7018798</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,12 +12042,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
         <v>129044298</v>
       </c>
       <c r="B112" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>129056681</v>
       </c>
       <c r="B119" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12961,32 +12961,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056702</v>
+        <v>129056704</v>
       </c>
       <c r="B121" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602649</v>
+        <v>602735</v>
       </c>
       <c r="R121" t="n">
-        <v>7018829</v>
+        <v>7018692</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13032,6 +13032,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13058,32 +13063,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056704</v>
+        <v>129056702</v>
       </c>
       <c r="B122" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13093,10 +13098,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602735</v>
+        <v>602649</v>
       </c>
       <c r="R122" t="n">
-        <v>7018692</v>
+        <v>7018829</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13129,11 +13134,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13160,49 +13160,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129046716</v>
+        <v>129044962</v>
       </c>
       <c r="B123" t="n">
-        <v>98656</v>
+        <v>91491</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602747</v>
+        <v>602750</v>
       </c>
       <c r="R123" t="n">
-        <v>7018722</v>
+        <v>7018799</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13261,48 +13257,52 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056689</v>
+        <v>129046716</v>
       </c>
       <c r="B124" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602754</v>
+        <v>602747</v>
       </c>
       <c r="R124" t="n">
-        <v>7018806</v>
+        <v>7018722</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13346,44 +13346,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056668</v>
+        <v>129056689</v>
       </c>
       <c r="B125" t="n">
-        <v>91488</v>
+        <v>91811</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13393,10 +13393,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602738</v>
+        <v>602754</v>
       </c>
       <c r="R125" t="n">
-        <v>7018795</v>
+        <v>7018806</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13455,32 +13455,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056700</v>
+        <v>129056668</v>
       </c>
       <c r="B126" t="n">
-        <v>80139</v>
+        <v>91491</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602684</v>
+        <v>602738</v>
       </c>
       <c r="R126" t="n">
-        <v>7018776</v>
+        <v>7018795</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13552,48 +13552,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129050404</v>
+        <v>129056700</v>
       </c>
       <c r="B127" t="n">
-        <v>80168</v>
+        <v>80140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R127" t="n">
-        <v>7018808</v>
+        <v>7018776</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,22 +13637,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129044962</v>
+        <v>129050404</v>
       </c>
       <c r="B128" t="n">
-        <v>91488</v>
+        <v>80169</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13660,21 +13660,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602750</v>
+        <v>602672</v>
       </c>
       <c r="R128" t="n">
-        <v>7018799</v>
+        <v>7018808</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13746,32 +13746,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129045554</v>
+        <v>129045756</v>
       </c>
       <c r="B129" t="n">
-        <v>80139</v>
+        <v>80100</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>602696</v>
+        <v>602663</v>
       </c>
       <c r="R129" t="n">
         <v>7018818</v>
@@ -13843,32 +13843,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B130" t="n">
-        <v>80099</v>
+        <v>80140</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R130" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13940,10 +13940,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129050334</v>
+        <v>129045554</v>
       </c>
       <c r="B131" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R131" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129056694</v>
+        <v>129045677</v>
       </c>
       <c r="B132" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602656</v>
+        <v>602684</v>
       </c>
       <c r="R132" t="n">
-        <v>7018656</v>
+        <v>7018786</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,60 +14122,60 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056675</v>
+        <v>129045512</v>
       </c>
       <c r="B133" t="n">
-        <v>92223</v>
+        <v>91526</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R133" t="n">
-        <v>7018832</v>
+        <v>7018827</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14219,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129045512</v>
+        <v>129046455</v>
       </c>
       <c r="B134" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602682</v>
+        <v>602667</v>
       </c>
       <c r="R134" t="n">
-        <v>7018827</v>
+        <v>7018757</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14328,10 +14328,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129045677</v>
+        <v>129044406</v>
       </c>
       <c r="B135" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14339,21 +14339,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14363,10 +14363,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602684</v>
+        <v>602756</v>
       </c>
       <c r="R135" t="n">
-        <v>7018786</v>
+        <v>7018769</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14425,48 +14425,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129046455</v>
+        <v>129056675</v>
       </c>
       <c r="B136" t="n">
-        <v>79034</v>
+        <v>92226</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602667</v>
+        <v>602672</v>
       </c>
       <c r="R136" t="n">
-        <v>7018757</v>
+        <v>7018832</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,57 +14510,61 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B137" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R137" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14619,52 +14623,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129046891</v>
+        <v>129056667</v>
       </c>
       <c r="B138" t="n">
-        <v>98656</v>
+        <v>96905</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602726</v>
+        <v>602672</v>
       </c>
       <c r="R138" t="n">
-        <v>7018723</v>
+        <v>7018807</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14708,22 +14708,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056667</v>
+        <v>129056694</v>
       </c>
       <c r="B139" t="n">
-        <v>96902</v>
+        <v>80140</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14731,21 +14731,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602672</v>
+        <v>602656</v>
       </c>
       <c r="R139" t="n">
-        <v>7018807</v>
+        <v>7018656</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14909,10 +14909,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B141" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,42 +14920,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R141" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14985,11 +14980,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15004,22 +14994,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056696</v>
+        <v>129048944</v>
       </c>
       <c r="B142" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15027,37 +15017,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602779</v>
+        <v>602734</v>
       </c>
       <c r="R142" t="n">
-        <v>7018639</v>
+        <v>7018579</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15087,6 +15082,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15101,22 +15101,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056705</v>
+        <v>129046813</v>
       </c>
       <c r="B143" t="n">
-        <v>56904</v>
+        <v>91086</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15124,37 +15124,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>102612</v>
+        <v>937</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602730</v>
+        <v>602732</v>
       </c>
       <c r="R143" t="n">
-        <v>7018719</v>
+        <v>7018701</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15184,11 +15184,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15203,22 +15198,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B144" t="n">
-        <v>91083</v>
+        <v>80140</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15226,37 +15221,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R144" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15300,44 +15295,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056679</v>
+        <v>129056705</v>
       </c>
       <c r="B145" t="n">
-        <v>91978</v>
+        <v>56904</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15347,10 +15342,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602737</v>
+        <v>602730</v>
       </c>
       <c r="R145" t="n">
-        <v>7018593</v>
+        <v>7018719</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15383,6 +15378,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15409,32 +15409,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B146" t="n">
-        <v>80139</v>
+        <v>91981</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15444,10 +15444,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R146" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15506,49 +15506,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129045069</v>
+        <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602751</v>
+        <v>602748</v>
       </c>
       <c r="R147" t="n">
-        <v>7018815</v>
+        <v>7018591</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15607,10 +15603,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15646,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15708,45 +15704,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129048489</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602748</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018591</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046382</v>
+        <v>129056716</v>
       </c>
       <c r="B150" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15816,37 +15816,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602637</v>
+        <v>602754</v>
       </c>
       <c r="R150" t="n">
-        <v>7018802</v>
+        <v>7018801</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15890,22 +15890,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B151" t="n">
-        <v>90555</v>
+        <v>91811</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R151" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15999,32 +15999,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129044697</v>
+        <v>129046543</v>
       </c>
       <c r="B152" t="n">
-        <v>80099</v>
+        <v>90558</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229497</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602730</v>
+        <v>602686</v>
       </c>
       <c r="R152" t="n">
-        <v>7018771</v>
+        <v>7018745</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16096,48 +16096,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129056716</v>
+        <v>129044697</v>
       </c>
       <c r="B153" t="n">
-        <v>79034</v>
+        <v>80100</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602754</v>
+        <v>602730</v>
       </c>
       <c r="R153" t="n">
-        <v>7018801</v>
+        <v>7018771</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16181,12 +16181,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16196,7 +16196,7 @@
         <v>129045378</v>
       </c>
       <c r="B154" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>129044275</v>
       </c>
       <c r="B155" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>129048151</v>
       </c>
       <c r="B156" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>129050391</v>
       </c>
       <c r="B157" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>129056714</v>
       </c>
       <c r="B158" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16774,48 +16774,52 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129047010</v>
+        <v>129058444</v>
       </c>
       <c r="B160" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602728</v>
+        <v>602760</v>
       </c>
       <c r="R160" t="n">
-        <v>7018716</v>
+        <v>7018673</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16853,28 +16857,29 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129045867</v>
+        <v>129047010</v>
       </c>
       <c r="B161" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16882,21 +16887,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16906,10 +16911,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602663</v>
+        <v>602728</v>
       </c>
       <c r="R161" t="n">
-        <v>7018805</v>
+        <v>7018716</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16968,10 +16973,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129056685</v>
+        <v>129045867</v>
       </c>
       <c r="B162" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16979,37 +16984,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602683</v>
+        <v>602663</v>
       </c>
       <c r="R162" t="n">
-        <v>7018835</v>
+        <v>7018805</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17053,22 +17058,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129058444</v>
+        <v>129044553</v>
       </c>
       <c r="B163" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17093,24 +17098,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602760</v>
+        <v>602758</v>
       </c>
       <c r="R163" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17148,71 +17153,66 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129044553</v>
+        <v>129056685</v>
       </c>
       <c r="B164" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602758</v>
+        <v>602683</v>
       </c>
       <c r="R164" t="n">
-        <v>7018769</v>
+        <v>7018835</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17256,22 +17256,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B165" t="n">
-        <v>91808</v>
+        <v>78792</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,21 +17279,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17303,10 +17303,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R165" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17365,10 +17365,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129044893</v>
+        <v>129048297</v>
       </c>
       <c r="B166" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602729</v>
+        <v>602752</v>
       </c>
       <c r="R166" t="n">
-        <v>7018798</v>
+        <v>7018614</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,10 +17462,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129046627</v>
+        <v>129044893</v>
       </c>
       <c r="B167" t="n">
-        <v>78791</v>
+        <v>91811</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,21 +17473,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602705</v>
+        <v>602729</v>
       </c>
       <c r="R167" t="n">
-        <v>7018763</v>
+        <v>7018798</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17773,32 +17773,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056678</v>
+        <v>129056666</v>
       </c>
       <c r="B170" t="n">
-        <v>80043</v>
+        <v>96905</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17808,10 +17808,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R170" t="n">
-        <v>7018832</v>
+        <v>7018643</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17870,32 +17870,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056666</v>
+        <v>129056678</v>
       </c>
       <c r="B171" t="n">
-        <v>96902</v>
+        <v>80044</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17905,10 +17905,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R171" t="n">
-        <v>7018643</v>
+        <v>7018832</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,7 +6775,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045323</v>
+        <v>129056682</v>
       </c>
       <c r="B58" t="n">
         <v>91811</v>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602682</v>
+        <v>602751</v>
       </c>
       <c r="R58" t="n">
-        <v>7018848</v>
+        <v>7018603</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,60 +6860,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045660</v>
+        <v>129056690</v>
       </c>
       <c r="B59" t="n">
-        <v>80044</v>
+        <v>91811</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602684</v>
+        <v>602758</v>
       </c>
       <c r="R59" t="n">
-        <v>7018786</v>
+        <v>7018806</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,60 +6957,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056682</v>
+        <v>129045660</v>
       </c>
       <c r="B60" t="n">
-        <v>91811</v>
+        <v>80044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602751</v>
+        <v>602684</v>
       </c>
       <c r="R60" t="n">
-        <v>7018603</v>
+        <v>7018786</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,19 +7054,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056690</v>
+        <v>129045323</v>
       </c>
       <c r="B61" t="n">
         <v>91811</v>
@@ -7097,17 +7097,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602758</v>
+        <v>602682</v>
       </c>
       <c r="R61" t="n">
-        <v>7018806</v>
+        <v>7018848</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,12 +7151,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129045225</v>
+        <v>129056720</v>
       </c>
       <c r="B64" t="n">
-        <v>97530</v>
+        <v>80175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,37 +7368,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602705</v>
+        <v>602773</v>
       </c>
       <c r="R64" t="n">
-        <v>7018799</v>
+        <v>7018642</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,22 +7442,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129056720</v>
+        <v>129045225</v>
       </c>
       <c r="B65" t="n">
-        <v>80175</v>
+        <v>97530</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7465,37 +7465,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602773</v>
+        <v>602705</v>
       </c>
       <c r="R65" t="n">
-        <v>7018642</v>
+        <v>7018799</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,12 +7539,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044277</v>
+        <v>129056680</v>
       </c>
       <c r="B67" t="n">
-        <v>91526</v>
+        <v>91981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602759</v>
+        <v>602732</v>
       </c>
       <c r="R67" t="n">
-        <v>7018767</v>
+        <v>7018811</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7733,60 +7733,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045343</v>
+        <v>129056672</v>
       </c>
       <c r="B68" t="n">
-        <v>91937</v>
+        <v>91526</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602684</v>
+        <v>602651</v>
       </c>
       <c r="R68" t="n">
-        <v>7018837</v>
+        <v>7018826</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7816,11 +7816,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7835,22 +7830,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045733</v>
+        <v>129045343</v>
       </c>
       <c r="B69" t="n">
-        <v>80169</v>
+        <v>91937</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7858,21 +7853,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>4217</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602669</v>
+        <v>602684</v>
       </c>
       <c r="R69" t="n">
-        <v>7018781</v>
+        <v>7018837</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7918,6 +7913,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,48 +7944,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056680</v>
+        <v>129045733</v>
       </c>
       <c r="B70" t="n">
-        <v>91981</v>
+        <v>80169</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602732</v>
+        <v>602669</v>
       </c>
       <c r="R70" t="n">
-        <v>7018811</v>
+        <v>7018781</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8029,22 +8029,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056672</v>
+        <v>129056715</v>
       </c>
       <c r="B71" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8052,21 +8052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602651</v>
+        <v>602665</v>
       </c>
       <c r="R71" t="n">
-        <v>7018826</v>
+        <v>7018777</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129050732</v>
+        <v>129056712</v>
       </c>
       <c r="B72" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,37 +8149,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602710</v>
+        <v>602730</v>
       </c>
       <c r="R72" t="n">
-        <v>7018856</v>
+        <v>7018697</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,22 +8223,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056715</v>
+        <v>129044277</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8246,37 +8246,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602665</v>
+        <v>602759</v>
       </c>
       <c r="R73" t="n">
-        <v>7018777</v>
+        <v>7018767</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8320,22 +8320,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056712</v>
+        <v>129050732</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8343,37 +8343,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602730</v>
+        <v>602710</v>
       </c>
       <c r="R74" t="n">
-        <v>7018697</v>
+        <v>7018856</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,44 +8417,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129044345</v>
+        <v>129049465</v>
       </c>
       <c r="B75" t="n">
-        <v>91727</v>
+        <v>80140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602772</v>
+        <v>602650</v>
       </c>
       <c r="R75" t="n">
-        <v>7018759</v>
+        <v>7018649</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129049465</v>
+        <v>129045649</v>
       </c>
       <c r="B76" t="n">
         <v>80140</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602650</v>
+        <v>602688</v>
       </c>
       <c r="R76" t="n">
-        <v>7018649</v>
+        <v>7018774</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129046472</v>
+        <v>129056676</v>
       </c>
       <c r="B77" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8634,37 +8634,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R77" t="n">
-        <v>7018759</v>
+        <v>7018779</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8694,6 +8694,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8708,22 +8713,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129045649</v>
+        <v>129046472</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8731,21 +8736,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8755,10 +8760,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602688</v>
+        <v>602666</v>
       </c>
       <c r="R78" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8817,48 +8822,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056718</v>
+        <v>129044345</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>91727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602758</v>
+        <v>602772</v>
       </c>
       <c r="R79" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8902,22 +8907,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056699</v>
+        <v>129056718</v>
       </c>
       <c r="B80" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8925,21 +8930,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8949,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602729</v>
+        <v>602758</v>
       </c>
       <c r="R80" t="n">
-        <v>7018756</v>
+        <v>7018806</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9011,10 +9016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129056699</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602729</v>
       </c>
       <c r="R81" t="n">
-        <v>7018779</v>
+        <v>7018756</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,32 +9113,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129045508</v>
+        <v>129046057</v>
       </c>
       <c r="B82" t="n">
-        <v>91811</v>
+        <v>80100</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602674</v>
+        <v>602648</v>
       </c>
       <c r="R82" t="n">
-        <v>7018842</v>
+        <v>7018840</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9210,48 +9210,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129048100</v>
+        <v>129058573</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602670</v>
+        <v>602756</v>
       </c>
       <c r="R83" t="n">
-        <v>7018643</v>
+        <v>7018669</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9289,28 +9293,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048233</v>
+        <v>129045508</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,21 +9323,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9342,10 +9347,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602744</v>
+        <v>602674</v>
       </c>
       <c r="R84" t="n">
-        <v>7018615</v>
+        <v>7018842</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9404,32 +9409,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129046057</v>
+        <v>129048233</v>
       </c>
       <c r="B85" t="n">
-        <v>80100</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602648</v>
+        <v>602744</v>
       </c>
       <c r="R85" t="n">
-        <v>7018840</v>
+        <v>7018615</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,49 +9506,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058573</v>
+        <v>129056687</v>
       </c>
       <c r="B86" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602756</v>
+        <v>602733</v>
       </c>
       <c r="R86" t="n">
-        <v>7018669</v>
+        <v>7018822</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9584,7 +9585,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129056687</v>
+        <v>129048100</v>
       </c>
       <c r="B87" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9614,37 +9614,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602733</v>
+        <v>602670</v>
       </c>
       <c r="R87" t="n">
-        <v>7018822</v>
+        <v>7018643</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9688,19 +9688,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056688</v>
+        <v>129044846</v>
       </c>
       <c r="B88" t="n">
         <v>91811</v>
@@ -9731,17 +9731,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602732</v>
+        <v>602719</v>
       </c>
       <c r="R88" t="n">
-        <v>7018811</v>
+        <v>7018813</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056686</v>
+        <v>129056711</v>
       </c>
       <c r="B89" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,21 +9808,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602702</v>
+        <v>602771</v>
       </c>
       <c r="R89" t="n">
-        <v>7018842</v>
+        <v>7018641</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,37 +9905,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R90" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9979,19 +9979,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129044846</v>
+        <v>129056688</v>
       </c>
       <c r="B91" t="n">
         <v>91811</v>
@@ -10022,17 +10022,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602719</v>
+        <v>602732</v>
       </c>
       <c r="R91" t="n">
-        <v>7018813</v>
+        <v>7018811</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129048130</v>
+        <v>129056686</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602704</v>
+        <v>602702</v>
       </c>
       <c r="R92" t="n">
-        <v>7018634</v>
+        <v>7018842</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,22 +10173,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R93" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,19 +10270,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B94" t="n">
         <v>80140</v>
@@ -10313,17 +10313,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R94" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129048547</v>
+        <v>129056683</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,37 +10390,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602747</v>
+        <v>602739</v>
       </c>
       <c r="R95" t="n">
-        <v>7018592</v>
+        <v>7018692</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10464,22 +10464,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129046062</v>
+        <v>129056709</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,37 +10487,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602648</v>
+        <v>602654</v>
       </c>
       <c r="R96" t="n">
-        <v>7018840</v>
+        <v>7018820</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,22 +10561,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056683</v>
+        <v>129056698</v>
       </c>
       <c r="B97" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10584,21 +10584,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602739</v>
+        <v>602735</v>
       </c>
       <c r="R97" t="n">
-        <v>7018692</v>
+        <v>7018716</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10670,10 +10670,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129046720</v>
+        <v>129045623</v>
       </c>
       <c r="B98" t="n">
-        <v>92151</v>
+        <v>98659</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,37 +10681,38 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602747</v>
+        <v>602687</v>
       </c>
       <c r="R98" t="n">
-        <v>7018721</v>
+        <v>7018769</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10746,18 +10747,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10776,10 +10771,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B99" t="n">
-        <v>98659</v>
+        <v>92151</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10787,38 +10782,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R99" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10853,12 +10847,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11075,10 +11075,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129044824</v>
+        <v>129045453</v>
       </c>
       <c r="B102" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602731</v>
+        <v>602673</v>
       </c>
       <c r="R102" t="n">
-        <v>7018789</v>
+        <v>7018844</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044805</v>
+        <v>129044824</v>
       </c>
       <c r="B103" t="n">
         <v>91811</v>
@@ -11207,10 +11207,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602747</v>
+        <v>602731</v>
       </c>
       <c r="R103" t="n">
-        <v>7018784</v>
+        <v>7018789</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11269,10 +11269,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129045681</v>
+        <v>129044805</v>
       </c>
       <c r="B104" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11280,21 +11280,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11304,10 +11304,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602667</v>
+        <v>602747</v>
       </c>
       <c r="R104" t="n">
-        <v>7018779</v>
+        <v>7018784</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11366,10 +11366,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045453</v>
+        <v>129045681</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11377,21 +11377,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11401,10 +11401,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602673</v>
+        <v>602667</v>
       </c>
       <c r="R105" t="n">
-        <v>7018844</v>
+        <v>7018779</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11463,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056684</v>
+        <v>129045582</v>
       </c>
       <c r="B106" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11474,37 +11474,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602651</v>
+        <v>602703</v>
       </c>
       <c r="R106" t="n">
-        <v>7018826</v>
+        <v>7018798</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11548,12 +11548,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129045582</v>
+        <v>129056684</v>
       </c>
       <c r="B111" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11968,37 +11968,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602703</v>
+        <v>602651</v>
       </c>
       <c r="R111" t="n">
-        <v>7018798</v>
+        <v>7018826</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,22 +12042,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044298</v>
+        <v>129044719</v>
       </c>
       <c r="B112" t="n">
-        <v>91981</v>
+        <v>98659</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12065,34 +12065,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602760</v>
+        <v>602727</v>
       </c>
       <c r="R112" t="n">
-        <v>7018767</v>
+        <v>7018795</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12151,42 +12155,47 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129046525</v>
+        <v>129044230</v>
       </c>
       <c r="B113" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602669</v>
+        <v>602777</v>
       </c>
       <c r="R113" t="n">
         <v>7018753</v>
@@ -12222,6 +12231,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12248,7 +12262,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129044230</v>
+        <v>129046367</v>
       </c>
       <c r="B114" t="n">
         <v>57723</v>
@@ -12279,7 +12293,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12288,10 +12302,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602777</v>
+        <v>602644</v>
       </c>
       <c r="R114" t="n">
-        <v>7018753</v>
+        <v>7018800</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12328,7 +12342,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12355,50 +12369,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129046367</v>
+        <v>129044298</v>
       </c>
       <c r="B115" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602644</v>
+        <v>602760</v>
       </c>
       <c r="R115" t="n">
-        <v>7018800</v>
+        <v>7018767</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12431,11 +12440,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12462,49 +12466,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044719</v>
+        <v>129046525</v>
       </c>
       <c r="B116" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602727</v>
+        <v>602669</v>
       </c>
       <c r="R116" t="n">
-        <v>7018795</v>
+        <v>7018753</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129044475</v>
+        <v>129050601</v>
       </c>
       <c r="B118" t="n">
-        <v>91544</v>
+        <v>10964</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,34 +12671,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602766</v>
+        <v>602698</v>
       </c>
       <c r="R118" t="n">
-        <v>7018781</v>
+        <v>7018836</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12733,12 +12737,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12750,17 +12760,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056681</v>
+        <v>129044475</v>
       </c>
       <c r="B119" t="n">
-        <v>91811</v>
+        <v>91544</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,37 +12778,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602736</v>
+        <v>602766</v>
       </c>
       <c r="R119" t="n">
-        <v>7018593</v>
+        <v>7018781</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12842,22 +12852,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129050601</v>
+        <v>129056681</v>
       </c>
       <c r="B120" t="n">
-        <v>10964</v>
+        <v>91811</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12865,41 +12875,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602698</v>
+        <v>602736</v>
       </c>
       <c r="R120" t="n">
-        <v>7018836</v>
+        <v>7018593</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12931,62 +12937,56 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056704</v>
+        <v>129056702</v>
       </c>
       <c r="B121" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602735</v>
+        <v>602649</v>
       </c>
       <c r="R121" t="n">
-        <v>7018692</v>
+        <v>7018829</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13032,11 +13032,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13063,32 +13058,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056702</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13098,10 +13093,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602649</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018829</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13134,6 +13129,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13160,48 +13160,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129044962</v>
+        <v>129056700</v>
       </c>
       <c r="B123" t="n">
-        <v>91491</v>
+        <v>80140</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602750</v>
+        <v>602684</v>
       </c>
       <c r="R123" t="n">
-        <v>7018799</v>
+        <v>7018776</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13245,61 +13245,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129046716</v>
+        <v>129050404</v>
       </c>
       <c r="B124" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602747</v>
+        <v>602672</v>
       </c>
       <c r="R124" t="n">
-        <v>7018722</v>
+        <v>7018808</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -13358,48 +13354,52 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056689</v>
+        <v>129046716</v>
       </c>
       <c r="B125" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602754</v>
+        <v>602747</v>
       </c>
       <c r="R125" t="n">
-        <v>7018806</v>
+        <v>7018722</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13443,19 +13443,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056668</v>
+        <v>129044962</v>
       </c>
       <c r="B126" t="n">
         <v>91491</v>
@@ -13486,17 +13486,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602738</v>
+        <v>602750</v>
       </c>
       <c r="R126" t="n">
-        <v>7018795</v>
+        <v>7018799</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,22 +13540,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056700</v>
+        <v>129056689</v>
       </c>
       <c r="B127" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13563,21 +13563,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13587,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602684</v>
+        <v>602754</v>
       </c>
       <c r="R127" t="n">
-        <v>7018776</v>
+        <v>7018806</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13649,10 +13649,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129050404</v>
+        <v>129056668</v>
       </c>
       <c r="B128" t="n">
-        <v>80169</v>
+        <v>91491</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13660,37 +13660,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602672</v>
+        <v>602738</v>
       </c>
       <c r="R128" t="n">
-        <v>7018808</v>
+        <v>7018795</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,44 +13734,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129045756</v>
+        <v>129045554</v>
       </c>
       <c r="B129" t="n">
-        <v>80100</v>
+        <v>80140</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>602663</v>
+        <v>602696</v>
       </c>
       <c r="R129" t="n">
         <v>7018818</v>
@@ -13843,32 +13843,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129050334</v>
+        <v>129045756</v>
       </c>
       <c r="B130" t="n">
-        <v>80140</v>
+        <v>80100</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602671</v>
+        <v>602663</v>
       </c>
       <c r="R130" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129045554</v>
+        <v>129050334</v>
       </c>
       <c r="B131" t="n">
         <v>80140</v>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R131" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14037,7 +14037,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045677</v>
+        <v>129045512</v>
       </c>
       <c r="B132" t="n">
         <v>91526</v>
@@ -14072,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602684</v>
+        <v>602682</v>
       </c>
       <c r="R132" t="n">
-        <v>7018786</v>
+        <v>7018827</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14134,7 +14134,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129045512</v>
+        <v>129045677</v>
       </c>
       <c r="B133" t="n">
         <v>91526</v>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R133" t="n">
-        <v>7018827</v>
+        <v>7018786</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14231,10 +14231,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129046455</v>
+        <v>129056667</v>
       </c>
       <c r="B134" t="n">
-        <v>79035</v>
+        <v>96905</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,37 +14242,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602667</v>
+        <v>602672</v>
       </c>
       <c r="R134" t="n">
-        <v>7018757</v>
+        <v>7018807</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14316,19 +14316,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129044406</v>
+        <v>129056694</v>
       </c>
       <c r="B135" t="n">
         <v>80140</v>
@@ -14359,17 +14359,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602756</v>
+        <v>602656</v>
       </c>
       <c r="R135" t="n">
-        <v>7018769</v>
+        <v>7018656</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14413,12 +14413,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14522,52 +14522,43 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129046891</v>
+        <v>129056692</v>
       </c>
       <c r="B137" t="n">
-        <v>98659</v>
+        <v>10964</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602726</v>
+        <v>602687</v>
       </c>
       <c r="R137" t="n">
-        <v>7018723</v>
+        <v>7018836</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14611,60 +14602,64 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056667</v>
+        <v>129046891</v>
       </c>
       <c r="B138" t="n">
-        <v>96905</v>
+        <v>98659</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602672</v>
+        <v>602726</v>
       </c>
       <c r="R138" t="n">
-        <v>7018807</v>
+        <v>7018723</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14708,22 +14703,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056694</v>
+        <v>129046455</v>
       </c>
       <c r="B139" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14731,37 +14726,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602656</v>
+        <v>602667</v>
       </c>
       <c r="R139" t="n">
-        <v>7018656</v>
+        <v>7018757</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14805,22 +14800,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056692</v>
+        <v>129044406</v>
       </c>
       <c r="B140" t="n">
-        <v>10964</v>
+        <v>80140</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14828,32 +14823,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602687</v>
+        <v>602756</v>
       </c>
       <c r="R140" t="n">
-        <v>7018836</v>
+        <v>7018769</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14897,22 +14897,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129056696</v>
+        <v>129046813</v>
       </c>
       <c r="B141" t="n">
-        <v>80140</v>
+        <v>91086</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,37 +14920,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602779</v>
+        <v>602732</v>
       </c>
       <c r="R141" t="n">
-        <v>7018639</v>
+        <v>7018701</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14994,65 +14994,60 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129048944</v>
+        <v>129056679</v>
       </c>
       <c r="B142" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602734</v>
+        <v>602737</v>
       </c>
       <c r="R142" t="n">
-        <v>7018579</v>
+        <v>7018593</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15082,11 +15077,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15101,22 +15091,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B143" t="n">
-        <v>91086</v>
+        <v>80140</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15124,37 +15114,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R143" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15198,19 +15188,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056695</v>
+        <v>129056696</v>
       </c>
       <c r="B144" t="n">
         <v>80140</v>
@@ -15245,10 +15235,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602754</v>
+        <v>602779</v>
       </c>
       <c r="R144" t="n">
-        <v>7018633</v>
+        <v>7018639</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15307,10 +15297,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056705</v>
+        <v>129048944</v>
       </c>
       <c r="B145" t="n">
-        <v>56904</v>
+        <v>57723</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15318,16 +15308,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15336,19 +15326,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602730</v>
+        <v>602734</v>
       </c>
       <c r="R145" t="n">
-        <v>7018719</v>
+        <v>7018579</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15382,7 +15377,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färsk spillning</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15397,44 +15392,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056679</v>
+        <v>129056705</v>
       </c>
       <c r="B146" t="n">
-        <v>91981</v>
+        <v>56904</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15444,10 +15439,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602737</v>
+        <v>602730</v>
       </c>
       <c r="R146" t="n">
-        <v>7018593</v>
+        <v>7018719</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15480,6 +15475,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15506,45 +15506,49 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129048489</v>
+        <v>129045069</v>
       </c>
       <c r="B147" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602748</v>
+        <v>602751</v>
       </c>
       <c r="R147" t="n">
-        <v>7018591</v>
+        <v>7018815</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15603,7 +15607,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B148" t="n">
         <v>98659</v>
@@ -15642,10 +15646,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R148" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15704,49 +15708,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129046445</v>
+        <v>129048489</v>
       </c>
       <c r="B149" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602669</v>
+        <v>602748</v>
       </c>
       <c r="R149" t="n">
-        <v>7018754</v>
+        <v>7018591</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129056716</v>
+        <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15816,37 +15816,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602754</v>
+        <v>602637</v>
       </c>
       <c r="R150" t="n">
-        <v>7018801</v>
+        <v>7018802</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15890,22 +15890,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046382</v>
+        <v>129046543</v>
       </c>
       <c r="B151" t="n">
-        <v>91811</v>
+        <v>90558</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602637</v>
+        <v>602686</v>
       </c>
       <c r="R151" t="n">
-        <v>7018802</v>
+        <v>7018745</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15999,10 +15999,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129046543</v>
+        <v>129056716</v>
       </c>
       <c r="B152" t="n">
-        <v>90558</v>
+        <v>79035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16010,37 +16010,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602686</v>
+        <v>602754</v>
       </c>
       <c r="R152" t="n">
-        <v>7018745</v>
+        <v>7018801</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16084,12 +16084,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16193,32 +16193,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129045378</v>
+        <v>129044275</v>
       </c>
       <c r="B154" t="n">
-        <v>92226</v>
+        <v>91811</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602682</v>
+        <v>602766</v>
       </c>
       <c r="R154" t="n">
-        <v>7018833</v>
+        <v>7018767</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,32 +16290,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129044275</v>
+        <v>129050391</v>
       </c>
       <c r="B155" t="n">
-        <v>91811</v>
+        <v>80044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16325,10 +16325,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602766</v>
+        <v>602671</v>
       </c>
       <c r="R155" t="n">
-        <v>7018767</v>
+        <v>7018809</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16387,52 +16387,48 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129048151</v>
+        <v>129056714</v>
       </c>
       <c r="B156" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602715</v>
+        <v>602678</v>
       </c>
       <c r="R156" t="n">
-        <v>7018634</v>
+        <v>7018771</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16476,57 +16472,61 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129050391</v>
+        <v>129048151</v>
       </c>
       <c r="B157" t="n">
-        <v>80044</v>
+        <v>98659</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602671</v>
+        <v>602715</v>
       </c>
       <c r="R157" t="n">
-        <v>7018809</v>
+        <v>7018634</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16585,48 +16585,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129056714</v>
+        <v>129045378</v>
       </c>
       <c r="B158" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602678</v>
+        <v>602682</v>
       </c>
       <c r="R158" t="n">
-        <v>7018771</v>
+        <v>7018833</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16670,12 +16670,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -16774,52 +16774,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129058444</v>
+        <v>129045867</v>
       </c>
       <c r="B160" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602760</v>
+        <v>602663</v>
       </c>
       <c r="R160" t="n">
-        <v>7018673</v>
+        <v>7018805</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16857,64 +16853,67 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129047010</v>
+        <v>129044553</v>
       </c>
       <c r="B161" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602728</v>
+        <v>602758</v>
       </c>
       <c r="R161" t="n">
-        <v>7018716</v>
+        <v>7018769</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16973,48 +16972,52 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129045867</v>
+        <v>129058444</v>
       </c>
       <c r="B162" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R162" t="n">
-        <v>7018805</v>
+        <v>7018673</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17052,67 +17055,64 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B163" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R163" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17268,10 +17268,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129046627</v>
+        <v>129048297</v>
       </c>
       <c r="B165" t="n">
-        <v>78792</v>
+        <v>91811</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,21 +17279,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17303,10 +17303,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602705</v>
+        <v>602752</v>
       </c>
       <c r="R165" t="n">
-        <v>7018763</v>
+        <v>7018614</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17365,7 +17365,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129048297</v>
+        <v>129044893</v>
       </c>
       <c r="B166" t="n">
         <v>91811</v>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602752</v>
+        <v>602729</v>
       </c>
       <c r="R166" t="n">
-        <v>7018614</v>
+        <v>7018798</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,10 +17462,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129044893</v>
+        <v>129056666</v>
       </c>
       <c r="B167" t="n">
-        <v>91811</v>
+        <v>96905</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,37 +17473,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602729</v>
+        <v>602756</v>
       </c>
       <c r="R167" t="n">
-        <v>7018798</v>
+        <v>7018643</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17547,65 +17547,60 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129046592</v>
+        <v>129056678</v>
       </c>
       <c r="B168" t="n">
-        <v>57723</v>
+        <v>80044</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602704</v>
+        <v>602672</v>
       </c>
       <c r="R168" t="n">
-        <v>7018751</v>
+        <v>7018832</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17635,11 +17630,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17654,19 +17644,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129048918</v>
+        <v>129046592</v>
       </c>
       <c r="B169" t="n">
         <v>57723</v>
@@ -17706,10 +17696,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602737</v>
+        <v>602704</v>
       </c>
       <c r="R169" t="n">
-        <v>7018577</v>
+        <v>7018751</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17746,7 +17736,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17773,10 +17763,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056666</v>
+        <v>129048918</v>
       </c>
       <c r="B170" t="n">
-        <v>96905</v>
+        <v>57723</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17784,37 +17774,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602756</v>
+        <v>602737</v>
       </c>
       <c r="R170" t="n">
-        <v>7018643</v>
+        <v>7018577</v>
       </c>
       <c r="S170" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17844,6 +17839,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17858,60 +17858,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056678</v>
+        <v>129046627</v>
       </c>
       <c r="B171" t="n">
-        <v>80044</v>
+        <v>78792</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602672</v>
+        <v>602705</v>
       </c>
       <c r="R171" t="n">
-        <v>7018832</v>
+        <v>7018763</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,7 +6775,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129056682</v>
+        <v>129045323</v>
       </c>
       <c r="B58" t="n">
         <v>91811</v>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602751</v>
+        <v>602682</v>
       </c>
       <c r="R58" t="n">
-        <v>7018603</v>
+        <v>7018848</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,19 +6860,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056690</v>
+        <v>129056682</v>
       </c>
       <c r="B59" t="n">
         <v>91811</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602758</v>
+        <v>602751</v>
       </c>
       <c r="R59" t="n">
-        <v>7018806</v>
+        <v>7018603</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6969,48 +6969,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129045660</v>
+        <v>129056690</v>
       </c>
       <c r="B60" t="n">
-        <v>80044</v>
+        <v>91811</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602684</v>
+        <v>602758</v>
       </c>
       <c r="R60" t="n">
-        <v>7018786</v>
+        <v>7018806</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,44 +7054,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045323</v>
+        <v>129045660</v>
       </c>
       <c r="B61" t="n">
-        <v>91811</v>
+        <v>80044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R61" t="n">
-        <v>7018848</v>
+        <v>7018786</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7163,48 +7163,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B62" t="n">
-        <v>91811</v>
+        <v>80175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,44 +7248,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048001</v>
+        <v>129048977</v>
       </c>
       <c r="B63" t="n">
-        <v>91981</v>
+        <v>91811</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602696</v>
+        <v>602712</v>
       </c>
       <c r="R63" t="n">
-        <v>7018662</v>
+        <v>7018600</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,48 +7357,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129056720</v>
+        <v>129048001</v>
       </c>
       <c r="B64" t="n">
-        <v>80175</v>
+        <v>91981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602773</v>
+        <v>602696</v>
       </c>
       <c r="R64" t="n">
-        <v>7018642</v>
+        <v>7018662</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,12 +7442,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129056680</v>
+        <v>129045343</v>
       </c>
       <c r="B67" t="n">
-        <v>91981</v>
+        <v>91937</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602732</v>
+        <v>602684</v>
       </c>
       <c r="R67" t="n">
-        <v>7018811</v>
+        <v>7018837</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7719,6 +7719,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7733,60 +7738,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129056672</v>
+        <v>129045733</v>
       </c>
       <c r="B68" t="n">
-        <v>91526</v>
+        <v>80169</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602651</v>
+        <v>602669</v>
       </c>
       <c r="R68" t="n">
-        <v>7018826</v>
+        <v>7018781</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7830,44 +7835,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045343</v>
+        <v>129044277</v>
       </c>
       <c r="B69" t="n">
-        <v>91937</v>
+        <v>91526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602684</v>
+        <v>602759</v>
       </c>
       <c r="R69" t="n">
-        <v>7018837</v>
+        <v>7018767</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7913,11 +7918,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,32 +7944,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129045733</v>
+        <v>129050732</v>
       </c>
       <c r="B70" t="n">
-        <v>80169</v>
+        <v>91811</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602669</v>
+        <v>602710</v>
       </c>
       <c r="R70" t="n">
-        <v>7018781</v>
+        <v>7018856</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8041,32 +8041,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>91981</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R71" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056712</v>
+        <v>129056672</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,21 +8149,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R72" t="n">
-        <v>7018697</v>
+        <v>7018826</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8235,10 +8235,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129044277</v>
+        <v>129056715</v>
       </c>
       <c r="B73" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8246,37 +8246,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602759</v>
+        <v>602665</v>
       </c>
       <c r="R73" t="n">
-        <v>7018767</v>
+        <v>7018777</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8320,22 +8320,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129050732</v>
+        <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8343,37 +8343,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602710</v>
+        <v>602730</v>
       </c>
       <c r="R74" t="n">
-        <v>7018856</v>
+        <v>7018697</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,22 +8417,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129049465</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,21 +8440,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602650</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
-        <v>7018649</v>
+        <v>7018759</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8526,32 +8526,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129045649</v>
+        <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>80140</v>
+        <v>91727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602688</v>
+        <v>602772</v>
       </c>
       <c r="R76" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129056676</v>
+        <v>129049465</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8634,37 +8634,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602667</v>
+        <v>602650</v>
       </c>
       <c r="R77" t="n">
-        <v>7018779</v>
+        <v>7018649</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8694,11 +8694,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8713,22 +8708,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129046472</v>
+        <v>129045649</v>
       </c>
       <c r="B78" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8736,21 +8731,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8760,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602666</v>
+        <v>602688</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8822,48 +8817,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129044345</v>
+        <v>129056718</v>
       </c>
       <c r="B79" t="n">
-        <v>91727</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602772</v>
+        <v>602758</v>
       </c>
       <c r="R79" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8907,22 +8902,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056718</v>
+        <v>129056699</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8930,21 +8925,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8954,10 +8949,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602758</v>
+        <v>602729</v>
       </c>
       <c r="R80" t="n">
-        <v>7018806</v>
+        <v>7018756</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9016,10 +9011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056699</v>
+        <v>129056676</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,21 +9022,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9051,10 +9046,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602729</v>
+        <v>602667</v>
       </c>
       <c r="R81" t="n">
-        <v>7018756</v>
+        <v>7018779</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9087,6 +9082,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9797,10 +9797,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R89" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,22 +9882,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129048130</v>
+        <v>129056686</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,37 +9905,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602704</v>
+        <v>602702</v>
       </c>
       <c r="R90" t="n">
-        <v>7018634</v>
+        <v>7018842</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9979,12 +9979,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129056686</v>
+        <v>129056711</v>
       </c>
       <c r="B92" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,21 +10099,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602702</v>
+        <v>602771</v>
       </c>
       <c r="R92" t="n">
-        <v>7018842</v>
+        <v>7018641</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045681</v>
+        <v>129056693</v>
       </c>
       <c r="B105" t="n">
         <v>80140</v>
@@ -11397,17 +11397,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602667</v>
+        <v>602670</v>
       </c>
       <c r="R105" t="n">
-        <v>7018779</v>
+        <v>7018818</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11437,6 +11437,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11451,19 +11456,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129045582</v>
+        <v>129056697</v>
       </c>
       <c r="B106" t="n">
         <v>80140</v>
@@ -11494,17 +11499,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602703</v>
+        <v>602730</v>
       </c>
       <c r="R106" t="n">
-        <v>7018798</v>
+        <v>7018719</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11548,22 +11553,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056671</v>
+        <v>129056684</v>
       </c>
       <c r="B107" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11571,21 +11576,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11595,10 +11600,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602735</v>
+        <v>602651</v>
       </c>
       <c r="R107" t="n">
-        <v>7018592</v>
+        <v>7018826</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11657,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056693</v>
+        <v>129045681</v>
       </c>
       <c r="B108" t="n">
         <v>80140</v>
@@ -11688,17 +11693,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602670</v>
+        <v>602667</v>
       </c>
       <c r="R108" t="n">
-        <v>7018818</v>
+        <v>7018779</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11728,11 +11733,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11747,19 +11747,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056697</v>
+        <v>129045582</v>
       </c>
       <c r="B109" t="n">
         <v>80140</v>
@@ -11790,17 +11790,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602730</v>
+        <v>602703</v>
       </c>
       <c r="R109" t="n">
-        <v>7018719</v>
+        <v>7018798</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11844,64 +11844,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129050244</v>
+        <v>129056671</v>
       </c>
       <c r="B110" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602665</v>
+        <v>602735</v>
       </c>
       <c r="R110" t="n">
-        <v>7018784</v>
+        <v>7018592</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11945,60 +11941,64 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129056684</v>
+        <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602651</v>
+        <v>602665</v>
       </c>
       <c r="R111" t="n">
-        <v>7018826</v>
+        <v>7018784</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,12 +12042,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13160,32 +13160,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129056700</v>
+        <v>129056668</v>
       </c>
       <c r="B123" t="n">
-        <v>80140</v>
+        <v>91491</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13195,10 +13195,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602684</v>
+        <v>602738</v>
       </c>
       <c r="R123" t="n">
-        <v>7018776</v>
+        <v>7018795</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13257,48 +13257,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129050404</v>
+        <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>80169</v>
+        <v>91811</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602672</v>
+        <v>602754</v>
       </c>
       <c r="R124" t="n">
-        <v>7018808</v>
+        <v>7018806</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13342,61 +13342,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129046716</v>
+        <v>129044962</v>
       </c>
       <c r="B125" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602747</v>
+        <v>602750</v>
       </c>
       <c r="R125" t="n">
-        <v>7018722</v>
+        <v>7018799</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13455,48 +13451,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129044962</v>
+        <v>129056700</v>
       </c>
       <c r="B126" t="n">
-        <v>91491</v>
+        <v>80140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602750</v>
+        <v>602684</v>
       </c>
       <c r="R126" t="n">
-        <v>7018799</v>
+        <v>7018776</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,60 +13536,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056689</v>
+        <v>129050404</v>
       </c>
       <c r="B127" t="n">
-        <v>91811</v>
+        <v>80169</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602754</v>
+        <v>602672</v>
       </c>
       <c r="R127" t="n">
-        <v>7018806</v>
+        <v>7018808</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,60 +13633,64 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056668</v>
+        <v>129046716</v>
       </c>
       <c r="B128" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602738</v>
+        <v>602747</v>
       </c>
       <c r="R128" t="n">
-        <v>7018795</v>
+        <v>7018722</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,12 +13734,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045512</v>
+        <v>129044406</v>
       </c>
       <c r="B132" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,21 +14048,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14072,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602682</v>
+        <v>602756</v>
       </c>
       <c r="R132" t="n">
-        <v>7018827</v>
+        <v>7018769</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14134,10 +14134,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129045677</v>
+        <v>129056667</v>
       </c>
       <c r="B133" t="n">
-        <v>91526</v>
+        <v>96905</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14145,37 +14145,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018786</v>
+        <v>7018807</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14219,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129056667</v>
+        <v>129045512</v>
       </c>
       <c r="B134" t="n">
-        <v>96905</v>
+        <v>91526</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,37 +14242,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R134" t="n">
-        <v>7018807</v>
+        <v>7018827</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14316,22 +14316,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129056694</v>
+        <v>129045677</v>
       </c>
       <c r="B135" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14339,37 +14339,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602656</v>
+        <v>602684</v>
       </c>
       <c r="R135" t="n">
-        <v>7018656</v>
+        <v>7018786</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14413,60 +14413,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056675</v>
+        <v>129046455</v>
       </c>
       <c r="B136" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602672</v>
+        <v>602667</v>
       </c>
       <c r="R136" t="n">
-        <v>7018832</v>
+        <v>7018757</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,22 +14510,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056692</v>
+        <v>129056694</v>
       </c>
       <c r="B137" t="n">
-        <v>10964</v>
+        <v>80140</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14533,16 +14533,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14552,10 +14557,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602687</v>
+        <v>602656</v>
       </c>
       <c r="R137" t="n">
-        <v>7018836</v>
+        <v>7018656</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14614,52 +14619,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129046891</v>
+        <v>129056675</v>
       </c>
       <c r="B138" t="n">
-        <v>98659</v>
+        <v>92226</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602726</v>
+        <v>602672</v>
       </c>
       <c r="R138" t="n">
-        <v>7018723</v>
+        <v>7018832</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14703,22 +14704,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129046455</v>
+        <v>129056692</v>
       </c>
       <c r="B139" t="n">
-        <v>79035</v>
+        <v>10964</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14726,37 +14727,32 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602667</v>
+        <v>602687</v>
       </c>
       <c r="R139" t="n">
-        <v>7018757</v>
+        <v>7018836</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14800,57 +14796,61 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B140" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R140" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -15006,32 +15006,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056679</v>
+        <v>129056695</v>
       </c>
       <c r="B142" t="n">
-        <v>91981</v>
+        <v>80140</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602737</v>
+        <v>602754</v>
       </c>
       <c r="R142" t="n">
-        <v>7018593</v>
+        <v>7018633</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15103,7 +15103,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056695</v>
+        <v>129056696</v>
       </c>
       <c r="B143" t="n">
         <v>80140</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602754</v>
+        <v>602779</v>
       </c>
       <c r="R143" t="n">
-        <v>7018633</v>
+        <v>7018639</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15200,10 +15200,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056696</v>
+        <v>129048944</v>
       </c>
       <c r="B144" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15211,37 +15211,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602779</v>
+        <v>602734</v>
       </c>
       <c r="R144" t="n">
-        <v>7018639</v>
+        <v>7018579</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15271,6 +15276,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15285,22 +15295,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129048944</v>
+        <v>129056705</v>
       </c>
       <c r="B145" t="n">
-        <v>57723</v>
+        <v>56904</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15308,16 +15318,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15326,24 +15336,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602734</v>
+        <v>602730</v>
       </c>
       <c r="R145" t="n">
-        <v>7018579</v>
+        <v>7018719</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15377,7 +15382,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15392,44 +15397,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056705</v>
+        <v>129056679</v>
       </c>
       <c r="B146" t="n">
-        <v>56904</v>
+        <v>91981</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15439,10 +15444,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602730</v>
+        <v>602737</v>
       </c>
       <c r="R146" t="n">
-        <v>7018719</v>
+        <v>7018593</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15475,11 +15480,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16774,10 +16774,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129045867</v>
+        <v>129056685</v>
       </c>
       <c r="B160" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,37 +16785,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602663</v>
+        <v>602683</v>
       </c>
       <c r="R160" t="n">
-        <v>7018805</v>
+        <v>7018835</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16859,12 +16859,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129056685</v>
+        <v>129045867</v>
       </c>
       <c r="B164" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17182,37 +17182,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602683</v>
+        <v>602663</v>
       </c>
       <c r="R164" t="n">
-        <v>7018835</v>
+        <v>7018805</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17256,12 +17256,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,32 +6775,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045323</v>
+        <v>129045660</v>
       </c>
       <c r="B58" t="n">
-        <v>91811</v>
+        <v>80044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R58" t="n">
-        <v>7018848</v>
+        <v>7018786</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056682</v>
+        <v>129056690</v>
       </c>
       <c r="B59" t="n">
         <v>91811</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602751</v>
+        <v>602758</v>
       </c>
       <c r="R59" t="n">
-        <v>7018603</v>
+        <v>7018806</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056690</v>
+        <v>129056682</v>
       </c>
       <c r="B60" t="n">
         <v>91811</v>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602758</v>
+        <v>602751</v>
       </c>
       <c r="R60" t="n">
-        <v>7018806</v>
+        <v>7018603</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,32 +7066,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045660</v>
+        <v>129045323</v>
       </c>
       <c r="B61" t="n">
-        <v>80044</v>
+        <v>91811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602684</v>
+        <v>602682</v>
       </c>
       <c r="R61" t="n">
-        <v>7018786</v>
+        <v>7018848</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7163,10 +7163,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129056720</v>
+        <v>129045225</v>
       </c>
       <c r="B62" t="n">
-        <v>80175</v>
+        <v>97530</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7174,37 +7174,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602773</v>
+        <v>602705</v>
       </c>
       <c r="R62" t="n">
-        <v>7018642</v>
+        <v>7018799</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,44 +7248,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048977</v>
+        <v>129050367</v>
       </c>
       <c r="B63" t="n">
-        <v>91811</v>
+        <v>80100</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602712</v>
+        <v>602671</v>
       </c>
       <c r="R63" t="n">
-        <v>7018600</v>
+        <v>7018809</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,48 +7357,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129048001</v>
+        <v>129056720</v>
       </c>
       <c r="B64" t="n">
-        <v>91981</v>
+        <v>80175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602696</v>
+        <v>602773</v>
       </c>
       <c r="R64" t="n">
-        <v>7018662</v>
+        <v>7018642</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,44 +7442,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B65" t="n">
-        <v>97530</v>
+        <v>91811</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R65" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129050367</v>
+        <v>129048001</v>
       </c>
       <c r="B66" t="n">
-        <v>80100</v>
+        <v>91981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R66" t="n">
-        <v>7018809</v>
+        <v>7018662</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7750,48 +7750,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045733</v>
+        <v>129056715</v>
       </c>
       <c r="B68" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602669</v>
+        <v>602665</v>
       </c>
       <c r="R68" t="n">
-        <v>7018781</v>
+        <v>7018777</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7835,12 +7835,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7944,48 +7944,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129050732</v>
+        <v>129056680</v>
       </c>
       <c r="B70" t="n">
-        <v>91811</v>
+        <v>91981</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602710</v>
+        <v>602732</v>
       </c>
       <c r="R70" t="n">
-        <v>7018856</v>
+        <v>7018811</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8029,44 +8029,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056680</v>
+        <v>129056672</v>
       </c>
       <c r="B71" t="n">
-        <v>91981</v>
+        <v>91526</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602732</v>
+        <v>602651</v>
       </c>
       <c r="R71" t="n">
-        <v>7018811</v>
+        <v>7018826</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056672</v>
+        <v>129050732</v>
       </c>
       <c r="B72" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,37 +8149,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602651</v>
+        <v>602710</v>
       </c>
       <c r="R72" t="n">
-        <v>7018826</v>
+        <v>7018856</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,19 +8223,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056715</v>
+        <v>129056712</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602665</v>
+        <v>602730</v>
       </c>
       <c r="R73" t="n">
-        <v>7018777</v>
+        <v>7018697</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8332,48 +8332,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056712</v>
+        <v>129045733</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602730</v>
+        <v>602669</v>
       </c>
       <c r="R74" t="n">
-        <v>7018697</v>
+        <v>7018781</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,44 +8417,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129044345</v>
       </c>
       <c r="B75" t="n">
-        <v>91811</v>
+        <v>91727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602772</v>
       </c>
       <c r="R75" t="n">
         <v>7018759</v>
@@ -8526,48 +8526,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129044345</v>
+        <v>129056699</v>
       </c>
       <c r="B76" t="n">
-        <v>91727</v>
+        <v>80140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602772</v>
+        <v>602729</v>
       </c>
       <c r="R76" t="n">
-        <v>7018759</v>
+        <v>7018756</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8611,22 +8611,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129049465</v>
+        <v>129056676</v>
       </c>
       <c r="B77" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8634,37 +8634,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602650</v>
+        <v>602667</v>
       </c>
       <c r="R77" t="n">
-        <v>7018649</v>
+        <v>7018779</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8694,6 +8694,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8708,22 +8713,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129045649</v>
+        <v>129046472</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8731,21 +8736,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8755,10 +8760,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602688</v>
+        <v>602666</v>
       </c>
       <c r="R78" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8914,7 +8919,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056699</v>
+        <v>129049465</v>
       </c>
       <c r="B80" t="n">
         <v>80140</v>
@@ -8945,17 +8950,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602729</v>
+        <v>602650</v>
       </c>
       <c r="R80" t="n">
-        <v>7018756</v>
+        <v>7018649</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,22 +9004,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129045649</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,37 +9027,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602688</v>
       </c>
       <c r="R81" t="n">
-        <v>7018779</v>
+        <v>7018774</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9101,60 +9101,60 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129046057</v>
+        <v>129056687</v>
       </c>
       <c r="B82" t="n">
-        <v>80100</v>
+        <v>91811</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602648</v>
+        <v>602733</v>
       </c>
       <c r="R82" t="n">
-        <v>7018840</v>
+        <v>7018822</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,64 +9198,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058573</v>
+        <v>129048100</v>
       </c>
       <c r="B83" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602756</v>
+        <v>602670</v>
       </c>
       <c r="R83" t="n">
-        <v>7018669</v>
+        <v>7018643</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9293,67 +9289,70 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129045508</v>
+        <v>129058573</v>
       </c>
       <c r="B84" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602674</v>
+        <v>602756</v>
       </c>
       <c r="R84" t="n">
-        <v>7018842</v>
+        <v>7018669</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9391,50 +9390,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129048233</v>
+        <v>129046057</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>80100</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602744</v>
+        <v>602648</v>
       </c>
       <c r="R85" t="n">
-        <v>7018615</v>
+        <v>7018840</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129056687</v>
+        <v>129045508</v>
       </c>
       <c r="B86" t="n">
         <v>91811</v>
@@ -9537,17 +9537,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602733</v>
+        <v>602674</v>
       </c>
       <c r="R86" t="n">
-        <v>7018822</v>
+        <v>7018842</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129048100</v>
+        <v>129048233</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602670</v>
+        <v>602744</v>
       </c>
       <c r="R87" t="n">
-        <v>7018643</v>
+        <v>7018615</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129044846</v>
+        <v>129056711</v>
       </c>
       <c r="B88" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,37 +9711,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602719</v>
+        <v>602771</v>
       </c>
       <c r="R88" t="n">
-        <v>7018813</v>
+        <v>7018641</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129048130</v>
+        <v>129056688</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602704</v>
+        <v>602732</v>
       </c>
       <c r="R89" t="n">
-        <v>7018634</v>
+        <v>7018811</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,12 +9882,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129056688</v>
+        <v>129044846</v>
       </c>
       <c r="B91" t="n">
         <v>91811</v>
@@ -10022,17 +10022,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602732</v>
+        <v>602719</v>
       </c>
       <c r="R91" t="n">
-        <v>7018811</v>
+        <v>7018813</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R92" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,22 +10173,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129046062</v>
+        <v>129056683</v>
       </c>
       <c r="B93" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602648</v>
+        <v>602739</v>
       </c>
       <c r="R93" t="n">
-        <v>7018840</v>
+        <v>7018692</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129048547</v>
+        <v>129056709</v>
       </c>
       <c r="B94" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,37 +10293,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602747</v>
+        <v>602654</v>
       </c>
       <c r="R94" t="n">
-        <v>7018592</v>
+        <v>7018820</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056683</v>
+        <v>129056698</v>
       </c>
       <c r="B95" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602739</v>
+        <v>602735</v>
       </c>
       <c r="R95" t="n">
-        <v>7018692</v>
+        <v>7018716</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,10 +10476,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B96" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,37 +10487,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R96" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,19 +10561,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B97" t="n">
         <v>80140</v>
@@ -10604,17 +10604,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R97" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,22 +10658,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B98" t="n">
-        <v>98659</v>
+        <v>92151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,38 +10681,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R98" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10747,12 +10746,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10771,32 +10776,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129046720</v>
+        <v>129058560</v>
       </c>
       <c r="B99" t="n">
-        <v>92151</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10805,17 +10810,17 @@
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602747</v>
+        <v>602760</v>
       </c>
       <c r="R99" t="n">
-        <v>7018721</v>
+        <v>7018673</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10845,11 +10850,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10865,19 +10865,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058560</v>
+        <v>129056713</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10906,19 +10906,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602760</v>
+        <v>602690</v>
       </c>
       <c r="R100" t="n">
-        <v>7018673</v>
+        <v>7018768</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10959,7 +10956,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10978,48 +10974,52 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129056713</v>
+        <v>129045623</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602690</v>
+        <v>602687</v>
       </c>
       <c r="R101" t="n">
-        <v>7018768</v>
+        <v>7018769</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11063,57 +11063,61 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045453</v>
+        <v>129050244</v>
       </c>
       <c r="B102" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602673</v>
+        <v>602665</v>
       </c>
       <c r="R102" t="n">
-        <v>7018844</v>
+        <v>7018784</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11172,10 +11176,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044824</v>
+        <v>129056693</v>
       </c>
       <c r="B103" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11183,37 +11187,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602731</v>
+        <v>602670</v>
       </c>
       <c r="R103" t="n">
-        <v>7018789</v>
+        <v>7018818</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11243,6 +11247,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11257,22 +11266,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044805</v>
+        <v>129056697</v>
       </c>
       <c r="B104" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11280,37 +11289,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602747</v>
+        <v>602730</v>
       </c>
       <c r="R104" t="n">
-        <v>7018784</v>
+        <v>7018719</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11354,22 +11363,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129056693</v>
+        <v>129056671</v>
       </c>
       <c r="B105" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11377,21 +11386,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11401,10 +11410,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602670</v>
+        <v>602735</v>
       </c>
       <c r="R105" t="n">
-        <v>7018818</v>
+        <v>7018592</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11437,11 +11446,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11468,10 +11472,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056697</v>
+        <v>129056684</v>
       </c>
       <c r="B106" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11479,21 +11483,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11503,10 +11507,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R106" t="n">
-        <v>7018719</v>
+        <v>7018826</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11565,7 +11569,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056684</v>
+        <v>129044824</v>
       </c>
       <c r="B107" t="n">
         <v>91811</v>
@@ -11596,17 +11600,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602651</v>
+        <v>602731</v>
       </c>
       <c r="R107" t="n">
-        <v>7018826</v>
+        <v>7018789</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11650,22 +11654,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129045681</v>
+        <v>129044805</v>
       </c>
       <c r="B108" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,21 +11677,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11697,10 +11701,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602667</v>
+        <v>602747</v>
       </c>
       <c r="R108" t="n">
-        <v>7018779</v>
+        <v>7018784</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11759,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129045582</v>
+        <v>129045453</v>
       </c>
       <c r="B109" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11770,21 +11774,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11794,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602703</v>
+        <v>602673</v>
       </c>
       <c r="R109" t="n">
-        <v>7018798</v>
+        <v>7018844</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11856,10 +11860,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056671</v>
+        <v>129045582</v>
       </c>
       <c r="B110" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11867,37 +11871,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602735</v>
+        <v>602703</v>
       </c>
       <c r="R110" t="n">
-        <v>7018592</v>
+        <v>7018798</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11941,61 +11945,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129050244</v>
+        <v>129045681</v>
       </c>
       <c r="B111" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602665</v>
+        <v>602667</v>
       </c>
       <c r="R111" t="n">
-        <v>7018784</v>
+        <v>7018779</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12054,10 +12054,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044719</v>
+        <v>129044298</v>
       </c>
       <c r="B112" t="n">
-        <v>98659</v>
+        <v>91981</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12065,38 +12065,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602727</v>
+        <v>602760</v>
       </c>
       <c r="R112" t="n">
-        <v>7018795</v>
+        <v>7018767</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12155,47 +12151,42 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129044230</v>
+        <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602777</v>
+        <v>602669</v>
       </c>
       <c r="R113" t="n">
         <v>7018753</v>
@@ -12231,11 +12222,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12262,10 +12248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129046367</v>
+        <v>129056708</v>
       </c>
       <c r="B114" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12273,42 +12259,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602644</v>
+        <v>602663</v>
       </c>
       <c r="R114" t="n">
-        <v>7018800</v>
+        <v>7018823</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12338,11 +12319,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12357,57 +12333,62 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129044298</v>
+        <v>129046367</v>
       </c>
       <c r="B115" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602760</v>
+        <v>602644</v>
       </c>
       <c r="R115" t="n">
-        <v>7018767</v>
+        <v>7018800</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12440,6 +12421,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12466,42 +12452,47 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129046525</v>
+        <v>129044230</v>
       </c>
       <c r="B116" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602669</v>
+        <v>602777</v>
       </c>
       <c r="R116" t="n">
         <v>7018753</v>
@@ -12537,6 +12528,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12563,48 +12559,52 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129056708</v>
+        <v>129044719</v>
       </c>
       <c r="B117" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602663</v>
+        <v>602727</v>
       </c>
       <c r="R117" t="n">
-        <v>7018823</v>
+        <v>7018795</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12648,22 +12648,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129050601</v>
+        <v>129056681</v>
       </c>
       <c r="B118" t="n">
-        <v>10964</v>
+        <v>91811</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,41 +12671,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602698</v>
+        <v>602736</v>
       </c>
       <c r="R118" t="n">
-        <v>7018836</v>
+        <v>7018593</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12737,40 +12733,34 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129044475</v>
+        <v>129056702</v>
       </c>
       <c r="B119" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12778,37 +12768,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602766</v>
+        <v>602649</v>
       </c>
       <c r="R119" t="n">
-        <v>7018781</v>
+        <v>7018829</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12852,22 +12842,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056681</v>
+        <v>129044475</v>
       </c>
       <c r="B120" t="n">
-        <v>91811</v>
+        <v>91544</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12875,37 +12865,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602736</v>
+        <v>602766</v>
       </c>
       <c r="R120" t="n">
-        <v>7018593</v>
+        <v>7018781</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12949,44 +12939,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056702</v>
+        <v>129056704</v>
       </c>
       <c r="B121" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12996,10 +12986,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602649</v>
+        <v>602735</v>
       </c>
       <c r="R121" t="n">
-        <v>7018829</v>
+        <v>7018692</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13032,6 +13022,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13058,48 +13053,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B122" t="n">
-        <v>98659</v>
+        <v>10964</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R122" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13133,7 +13132,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13142,28 +13141,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129056668</v>
+        <v>129050404</v>
       </c>
       <c r="B123" t="n">
-        <v>91491</v>
+        <v>80169</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13171,37 +13171,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602738</v>
+        <v>602672</v>
       </c>
       <c r="R123" t="n">
-        <v>7018795</v>
+        <v>7018808</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13245,44 +13245,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056689</v>
+        <v>129056668</v>
       </c>
       <c r="B124" t="n">
-        <v>91811</v>
+        <v>91491</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13292,10 +13292,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602754</v>
+        <v>602738</v>
       </c>
       <c r="R124" t="n">
-        <v>7018806</v>
+        <v>7018795</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13354,45 +13354,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129044962</v>
+        <v>129046716</v>
       </c>
       <c r="B125" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602750</v>
+        <v>602747</v>
       </c>
       <c r="R125" t="n">
-        <v>7018799</v>
+        <v>7018722</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13451,10 +13455,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056700</v>
+        <v>129056689</v>
       </c>
       <c r="B126" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13462,21 +13466,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13486,10 +13490,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602684</v>
+        <v>602754</v>
       </c>
       <c r="R126" t="n">
-        <v>7018776</v>
+        <v>7018806</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13548,10 +13552,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129050404</v>
+        <v>129044962</v>
       </c>
       <c r="B127" t="n">
-        <v>80169</v>
+        <v>91491</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13559,21 +13563,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13583,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602672</v>
+        <v>602750</v>
       </c>
       <c r="R127" t="n">
-        <v>7018808</v>
+        <v>7018799</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -13645,52 +13649,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129046716</v>
+        <v>129056700</v>
       </c>
       <c r="B128" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602747</v>
+        <v>602684</v>
       </c>
       <c r="R128" t="n">
-        <v>7018722</v>
+        <v>7018776</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,12 +13734,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13843,32 +13843,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B130" t="n">
-        <v>80100</v>
+        <v>80140</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R130" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13940,32 +13940,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129050334</v>
+        <v>129045756</v>
       </c>
       <c r="B131" t="n">
-        <v>80140</v>
+        <v>80100</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602671</v>
+        <v>602663</v>
       </c>
       <c r="R131" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129044406</v>
+        <v>129056667</v>
       </c>
       <c r="B132" t="n">
-        <v>80140</v>
+        <v>96905</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R132" t="n">
-        <v>7018769</v>
+        <v>7018807</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,44 +14122,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056667</v>
+        <v>129056675</v>
       </c>
       <c r="B133" t="n">
-        <v>96905</v>
+        <v>92226</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14172,7 +14172,7 @@
         <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018807</v>
+        <v>7018832</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14425,45 +14425,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129046455</v>
+        <v>129046891</v>
       </c>
       <c r="B136" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602667</v>
+        <v>602726</v>
       </c>
       <c r="R136" t="n">
-        <v>7018757</v>
+        <v>7018723</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14619,48 +14623,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056675</v>
+        <v>129044406</v>
       </c>
       <c r="B138" t="n">
-        <v>92226</v>
+        <v>80140</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R138" t="n">
-        <v>7018832</v>
+        <v>7018769</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14704,22 +14708,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056692</v>
+        <v>129046455</v>
       </c>
       <c r="B139" t="n">
-        <v>10964</v>
+        <v>79035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14727,32 +14731,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>101449</v>
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602687</v>
+        <v>602667</v>
       </c>
       <c r="R139" t="n">
-        <v>7018836</v>
+        <v>7018757</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14796,64 +14805,55 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129046891</v>
+        <v>129056692</v>
       </c>
       <c r="B140" t="n">
-        <v>98659</v>
+        <v>10964</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602726</v>
+        <v>602687</v>
       </c>
       <c r="R140" t="n">
-        <v>7018723</v>
+        <v>7018836</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14897,60 +14897,60 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129046813</v>
+        <v>129056679</v>
       </c>
       <c r="B141" t="n">
-        <v>91086</v>
+        <v>91981</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>937</v>
+        <v>1209</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602732</v>
+        <v>602737</v>
       </c>
       <c r="R141" t="n">
-        <v>7018701</v>
+        <v>7018593</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14994,22 +14994,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056695</v>
+        <v>129046813</v>
       </c>
       <c r="B142" t="n">
-        <v>80140</v>
+        <v>91086</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15017,37 +15017,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602754</v>
+        <v>602732</v>
       </c>
       <c r="R142" t="n">
-        <v>7018633</v>
+        <v>7018701</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15091,19 +15091,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B143" t="n">
         <v>80140</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R143" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15200,10 +15200,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B144" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15211,42 +15211,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R144" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15276,11 +15271,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15295,22 +15285,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056705</v>
+        <v>129048944</v>
       </c>
       <c r="B145" t="n">
-        <v>56904</v>
+        <v>57723</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15318,16 +15308,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15336,19 +15326,24 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602730</v>
+        <v>602734</v>
       </c>
       <c r="R145" t="n">
-        <v>7018719</v>
+        <v>7018579</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15382,7 +15377,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färsk spillning</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15397,44 +15392,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056679</v>
+        <v>129056705</v>
       </c>
       <c r="B146" t="n">
-        <v>91981</v>
+        <v>56904</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15444,10 +15439,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602737</v>
+        <v>602730</v>
       </c>
       <c r="R146" t="n">
-        <v>7018593</v>
+        <v>7018719</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15480,6 +15475,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15506,49 +15506,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129045069</v>
+        <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602751</v>
+        <v>602748</v>
       </c>
       <c r="R147" t="n">
-        <v>7018815</v>
+        <v>7018591</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15607,7 +15603,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
         <v>98659</v>
@@ -15646,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15708,45 +15704,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129048489</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602748</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018591</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046382</v>
+        <v>129046543</v>
       </c>
       <c r="B150" t="n">
-        <v>91811</v>
+        <v>90558</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15816,21 +15816,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15840,10 +15840,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602637</v>
+        <v>602686</v>
       </c>
       <c r="R150" t="n">
-        <v>7018802</v>
+        <v>7018745</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15902,10 +15902,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B151" t="n">
-        <v>90558</v>
+        <v>91811</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R151" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16193,45 +16193,49 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129044275</v>
+        <v>129048151</v>
       </c>
       <c r="B154" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602766</v>
+        <v>602715</v>
       </c>
       <c r="R154" t="n">
-        <v>7018767</v>
+        <v>7018634</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,48 +16294,43 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129050391</v>
+        <v>129056691</v>
       </c>
       <c r="B155" t="n">
-        <v>80044</v>
+        <v>10964</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602671</v>
+        <v>602659</v>
       </c>
       <c r="R155" t="n">
-        <v>7018809</v>
+        <v>7018825</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16375,22 +16374,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129056714</v>
+        <v>129044275</v>
       </c>
       <c r="B156" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16398,37 +16397,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602678</v>
+        <v>602766</v>
       </c>
       <c r="R156" t="n">
-        <v>7018771</v>
+        <v>7018767</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16472,61 +16471,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B157" t="n">
-        <v>98659</v>
+        <v>80044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R157" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16682,10 +16677,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056691</v>
+        <v>129056714</v>
       </c>
       <c r="B159" t="n">
-        <v>10964</v>
+        <v>79035</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16693,16 +16688,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>101449</v>
+        <v>6425</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16712,10 +16712,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602659</v>
+        <v>602678</v>
       </c>
       <c r="R159" t="n">
-        <v>7018825</v>
+        <v>7018771</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16871,49 +16871,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B161" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R161" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16972,52 +16968,48 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129058444</v>
+        <v>129045867</v>
       </c>
       <c r="B162" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602760</v>
+        <v>602663</v>
       </c>
       <c r="R162" t="n">
-        <v>7018673</v>
+        <v>7018805</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17055,67 +17047,70 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129047010</v>
+        <v>129058444</v>
       </c>
       <c r="B163" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602728</v>
+        <v>602760</v>
       </c>
       <c r="R163" t="n">
-        <v>7018716</v>
+        <v>7018673</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17153,63 +17148,68 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129045867</v>
+        <v>129044553</v>
       </c>
       <c r="B164" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602663</v>
+        <v>602758</v>
       </c>
       <c r="R164" t="n">
-        <v>7018805</v>
+        <v>7018769</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -17268,10 +17268,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129048297</v>
+        <v>129056666</v>
       </c>
       <c r="B165" t="n">
-        <v>91811</v>
+        <v>96905</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,37 +17279,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602752</v>
+        <v>602756</v>
       </c>
       <c r="R165" t="n">
-        <v>7018614</v>
+        <v>7018643</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17353,22 +17353,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129044893</v>
+        <v>129046592</v>
       </c>
       <c r="B166" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17376,34 +17376,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602729</v>
+        <v>602704</v>
       </c>
       <c r="R166" t="n">
-        <v>7018798</v>
+        <v>7018751</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17436,6 +17441,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17462,10 +17472,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129056666</v>
+        <v>129048918</v>
       </c>
       <c r="B167" t="n">
-        <v>96905</v>
+        <v>57723</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,37 +17483,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602756</v>
+        <v>602737</v>
       </c>
       <c r="R167" t="n">
-        <v>7018643</v>
+        <v>7018577</v>
       </c>
       <c r="S167" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17533,6 +17548,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17547,60 +17567,60 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129056678</v>
+        <v>129048297</v>
       </c>
       <c r="B168" t="n">
-        <v>80044</v>
+        <v>91811</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602672</v>
+        <v>602752</v>
       </c>
       <c r="R168" t="n">
-        <v>7018832</v>
+        <v>7018614</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17644,22 +17664,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129046592</v>
+        <v>129044893</v>
       </c>
       <c r="B169" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17667,39 +17687,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602704</v>
+        <v>602729</v>
       </c>
       <c r="R169" t="n">
-        <v>7018751</v>
+        <v>7018798</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17732,11 +17747,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17763,10 +17773,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129048918</v>
+        <v>129046627</v>
       </c>
       <c r="B170" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17774,39 +17784,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602737</v>
+        <v>602705</v>
       </c>
       <c r="R170" t="n">
-        <v>7018577</v>
+        <v>7018763</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17839,11 +17844,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17870,48 +17870,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129046627</v>
+        <v>129056678</v>
       </c>
       <c r="B171" t="n">
-        <v>78792</v>
+        <v>80044</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602705</v>
+        <v>602672</v>
       </c>
       <c r="R171" t="n">
-        <v>7018763</v>
+        <v>7018832</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,32 +6775,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045660</v>
+        <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>80044</v>
+        <v>91818</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602684</v>
+        <v>602682</v>
       </c>
       <c r="R58" t="n">
-        <v>7018786</v>
+        <v>7018848</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6872,48 +6872,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056690</v>
+        <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>91811</v>
+        <v>80048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602758</v>
+        <v>602684</v>
       </c>
       <c r="R59" t="n">
-        <v>7018806</v>
+        <v>7018786</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,12 +6957,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6972,7 +6972,7 @@
         <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045323</v>
+        <v>129056690</v>
       </c>
       <c r="B61" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,17 +7097,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602682</v>
+        <v>602758</v>
       </c>
       <c r="R61" t="n">
-        <v>7018848</v>
+        <v>7018806</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,44 +7151,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B62" t="n">
-        <v>97530</v>
+        <v>91818</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R62" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129050367</v>
+        <v>129048001</v>
       </c>
       <c r="B63" t="n">
-        <v>80100</v>
+        <v>91988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R63" t="n">
-        <v>7018809</v>
+        <v>7018662</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129056720</v>
+        <v>129045225</v>
       </c>
       <c r="B64" t="n">
-        <v>80175</v>
+        <v>97540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,37 +7368,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602773</v>
+        <v>602705</v>
       </c>
       <c r="R64" t="n">
-        <v>7018642</v>
+        <v>7018799</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,60 +7442,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B65" t="n">
-        <v>91811</v>
+        <v>80179</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R65" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,44 +7539,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129048001</v>
+        <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>91981</v>
+        <v>80104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R66" t="n">
-        <v>7018662</v>
+        <v>7018809</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7651,7 +7651,7 @@
         <v>129045343</v>
       </c>
       <c r="B67" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7750,48 +7750,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129056715</v>
+        <v>129045733</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>80173</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602665</v>
+        <v>602669</v>
       </c>
       <c r="R68" t="n">
-        <v>7018777</v>
+        <v>7018781</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7835,60 +7835,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129044277</v>
+        <v>129056680</v>
       </c>
       <c r="B69" t="n">
-        <v>91526</v>
+        <v>91988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602759</v>
+        <v>602732</v>
       </c>
       <c r="R69" t="n">
-        <v>7018767</v>
+        <v>7018811</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7932,44 +7932,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056680</v>
+        <v>129056715</v>
       </c>
       <c r="B70" t="n">
-        <v>91981</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602732</v>
+        <v>602665</v>
       </c>
       <c r="R70" t="n">
-        <v>7018811</v>
+        <v>7018777</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056672</v>
+        <v>129056712</v>
       </c>
       <c r="B71" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8052,21 +8052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602651</v>
+        <v>602730</v>
       </c>
       <c r="R71" t="n">
-        <v>7018826</v>
+        <v>7018697</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129050732</v>
+        <v>129044277</v>
       </c>
       <c r="B72" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,21 +8149,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602710</v>
+        <v>602759</v>
       </c>
       <c r="R72" t="n">
-        <v>7018856</v>
+        <v>7018767</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8235,10 +8235,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056712</v>
+        <v>129050732</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8246,37 +8246,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602730</v>
+        <v>602710</v>
       </c>
       <c r="R73" t="n">
-        <v>7018697</v>
+        <v>7018856</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8320,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129045733</v>
+        <v>129056672</v>
       </c>
       <c r="B74" t="n">
-        <v>80169</v>
+        <v>91533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602669</v>
+        <v>602651</v>
       </c>
       <c r="R74" t="n">
-        <v>7018781</v>
+        <v>7018826</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,44 +8417,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129044345</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>91727</v>
+        <v>91818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602772</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
         <v>7018759</v>
@@ -8526,48 +8526,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129056699</v>
+        <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>80140</v>
+        <v>91734</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602729</v>
+        <v>602772</v>
       </c>
       <c r="R76" t="n">
-        <v>7018756</v>
+        <v>7018759</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8611,22 +8611,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129056676</v>
+        <v>129049465</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8634,37 +8634,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602667</v>
+        <v>602650</v>
       </c>
       <c r="R77" t="n">
-        <v>7018779</v>
+        <v>7018649</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8694,11 +8694,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8713,22 +8708,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129046472</v>
+        <v>129045649</v>
       </c>
       <c r="B78" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8736,21 +8731,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8760,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602666</v>
+        <v>602688</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8825,7 +8820,7 @@
         <v>129056718</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8919,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129049465</v>
+        <v>129056699</v>
       </c>
       <c r="B80" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8950,17 +8945,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602650</v>
+        <v>602729</v>
       </c>
       <c r="R80" t="n">
-        <v>7018649</v>
+        <v>7018756</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9004,22 +8999,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129045649</v>
+        <v>129056676</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,37 +9022,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602688</v>
+        <v>602667</v>
       </c>
       <c r="R81" t="n">
-        <v>7018774</v>
+        <v>7018778</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9087,6 +9082,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9101,12 +9101,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9116,7 +9116,7 @@
         <v>129056687</v>
       </c>
       <c r="B82" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9210,48 +9210,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129048100</v>
+        <v>129058573</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602670</v>
+        <v>602756</v>
       </c>
       <c r="R83" t="n">
-        <v>7018643</v>
+        <v>7018669</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9289,70 +9293,67 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129058573</v>
+        <v>129045508</v>
       </c>
       <c r="B84" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602756</v>
+        <v>602674</v>
       </c>
       <c r="R84" t="n">
-        <v>7018669</v>
+        <v>7018842</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9390,51 +9391,50 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129046057</v>
+        <v>129048233</v>
       </c>
       <c r="B85" t="n">
-        <v>80100</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602648</v>
+        <v>602744</v>
       </c>
       <c r="R85" t="n">
-        <v>7018840</v>
+        <v>7018615</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9506,10 +9506,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129045508</v>
+        <v>129048100</v>
       </c>
       <c r="B86" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9517,21 +9517,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602674</v>
+        <v>602670</v>
       </c>
       <c r="R86" t="n">
-        <v>7018842</v>
+        <v>7018643</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9603,32 +9603,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129048233</v>
+        <v>129046057</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602744</v>
+        <v>602648</v>
       </c>
       <c r="R87" t="n">
-        <v>7018615</v>
+        <v>7018840</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056711</v>
+        <v>129044846</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,37 +9711,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602771</v>
+        <v>602719</v>
       </c>
       <c r="R88" t="n">
-        <v>7018641</v>
+        <v>7018813</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056688</v>
+        <v>129048130</v>
       </c>
       <c r="B89" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602732</v>
+        <v>602704</v>
       </c>
       <c r="R89" t="n">
-        <v>7018811</v>
+        <v>7018634</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,12 +9882,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9897,7 +9897,7 @@
         <v>129056686</v>
       </c>
       <c r="B90" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129044846</v>
+        <v>129056688</v>
       </c>
       <c r="B91" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10022,17 +10022,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602719</v>
+        <v>602732</v>
       </c>
       <c r="R91" t="n">
-        <v>7018813</v>
+        <v>7018811</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129048130</v>
+        <v>129056711</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602704</v>
+        <v>602771</v>
       </c>
       <c r="R92" t="n">
-        <v>7018634</v>
+        <v>7018641</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,22 +10173,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056683</v>
+        <v>129056709</v>
       </c>
       <c r="B93" t="n">
-        <v>91811</v>
+        <v>91551</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,21 +10196,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602739</v>
+        <v>602654</v>
       </c>
       <c r="R93" t="n">
-        <v>7018692</v>
+        <v>7018820</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10282,10 +10282,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B94" t="n">
-        <v>91544</v>
+        <v>91818</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,21 +10293,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R94" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10382,7 +10382,7 @@
         <v>129056698</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>129046062</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>129048547</v>
       </c>
       <c r="B97" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10670,32 +10670,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129046720</v>
+        <v>129058560</v>
       </c>
       <c r="B98" t="n">
-        <v>92151</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10704,17 +10704,17 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602747</v>
+        <v>602760</v>
       </c>
       <c r="R98" t="n">
-        <v>7018721</v>
+        <v>7018673</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10744,11 +10744,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10764,22 +10759,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058560</v>
+        <v>129056713</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10805,19 +10800,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602760</v>
+        <v>602690</v>
       </c>
       <c r="R99" t="n">
-        <v>7018673</v>
+        <v>7018768</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10858,7 +10850,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10877,48 +10868,52 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129056713</v>
+        <v>129045623</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602690</v>
+        <v>602687</v>
       </c>
       <c r="R100" t="n">
-        <v>7018768</v>
+        <v>7018769</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10962,22 +10957,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B101" t="n">
-        <v>98659</v>
+        <v>92158</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10985,38 +10980,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R101" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11051,12 +11045,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11075,52 +11075,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129050244</v>
+        <v>129056671</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602665</v>
+        <v>602735</v>
       </c>
       <c r="R102" t="n">
-        <v>7018784</v>
+        <v>7018592</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11164,12 +11160,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11179,7 +11175,7 @@
         <v>129056693</v>
       </c>
       <c r="B103" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11281,7 +11277,7 @@
         <v>129056697</v>
       </c>
       <c r="B104" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11375,48 +11371,52 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129056671</v>
+        <v>129050244</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602735</v>
+        <v>602665</v>
       </c>
       <c r="R105" t="n">
-        <v>7018592</v>
+        <v>7018784</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11460,22 +11460,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056684</v>
+        <v>129044824</v>
       </c>
       <c r="B106" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11503,17 +11503,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602651</v>
+        <v>602731</v>
       </c>
       <c r="R106" t="n">
-        <v>7018826</v>
+        <v>7018789</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11557,22 +11557,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044824</v>
+        <v>129044805</v>
       </c>
       <c r="B107" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602731</v>
+        <v>602747</v>
       </c>
       <c r="R107" t="n">
-        <v>7018789</v>
+        <v>7018784</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129044805</v>
+        <v>129045453</v>
       </c>
       <c r="B108" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602747</v>
+        <v>602673</v>
       </c>
       <c r="R108" t="n">
-        <v>7018784</v>
+        <v>7018844</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129045453</v>
+        <v>129045681</v>
       </c>
       <c r="B109" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602673</v>
+        <v>602667</v>
       </c>
       <c r="R109" t="n">
-        <v>7018844</v>
+        <v>7018779</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>129045582</v>
       </c>
       <c r="B110" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11957,10 +11957,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129045681</v>
+        <v>129056684</v>
       </c>
       <c r="B111" t="n">
-        <v>80140</v>
+        <v>91818</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11968,37 +11968,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602667</v>
+        <v>602651</v>
       </c>
       <c r="R111" t="n">
-        <v>7018779</v>
+        <v>7018826</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,12 +12042,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
         <v>129044298</v>
       </c>
       <c r="B112" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129056708</v>
+        <v>129044230</v>
       </c>
       <c r="B114" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12259,37 +12259,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602663</v>
+        <v>602777</v>
       </c>
       <c r="R114" t="n">
-        <v>7018823</v>
+        <v>7018753</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12319,6 +12324,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12333,12 +12343,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12348,7 +12358,7 @@
         <v>129046367</v>
       </c>
       <c r="B115" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12452,38 +12462,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044230</v>
+        <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12492,10 +12501,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602777</v>
+        <v>602727</v>
       </c>
       <c r="R116" t="n">
-        <v>7018753</v>
+        <v>7018795</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12528,11 +12537,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12559,52 +12563,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129044719</v>
+        <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>98659</v>
+        <v>91551</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602727</v>
+        <v>602663</v>
       </c>
       <c r="R117" t="n">
-        <v>7018795</v>
+        <v>7018823</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12648,22 +12648,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129056681</v>
+        <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>91811</v>
+        <v>91551</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,37 +12671,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602736</v>
+        <v>602766</v>
       </c>
       <c r="R118" t="n">
-        <v>7018593</v>
+        <v>7018781</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12745,22 +12745,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056702</v>
+        <v>129056681</v>
       </c>
       <c r="B119" t="n">
-        <v>80140</v>
+        <v>91818</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,21 +12768,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12792,10 +12792,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602649</v>
+        <v>602736</v>
       </c>
       <c r="R119" t="n">
-        <v>7018829</v>
+        <v>7018593</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12854,10 +12854,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129044475</v>
+        <v>129056702</v>
       </c>
       <c r="B120" t="n">
-        <v>91544</v>
+        <v>80144</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12865,37 +12865,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602766</v>
+        <v>602649</v>
       </c>
       <c r="R120" t="n">
-        <v>7018781</v>
+        <v>7018829</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12939,60 +12939,64 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B121" t="n">
-        <v>98659</v>
+        <v>10964</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R121" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13026,7 +13030,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13035,70 +13039,67 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129050601</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>10964</v>
+        <v>98669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602698</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018836</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13132,7 +13133,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Under bark, granlåga</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13141,29 +13142,28 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129050404</v>
+        <v>129044962</v>
       </c>
       <c r="B123" t="n">
-        <v>80169</v>
+        <v>91497</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13171,21 +13171,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13195,10 +13195,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602672</v>
+        <v>602750</v>
       </c>
       <c r="R123" t="n">
-        <v>7018808</v>
+        <v>7018799</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13257,48 +13257,52 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056668</v>
+        <v>129046716</v>
       </c>
       <c r="B124" t="n">
-        <v>91491</v>
+        <v>98669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602738</v>
+        <v>602747</v>
       </c>
       <c r="R124" t="n">
-        <v>7018795</v>
+        <v>7018722</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13342,64 +13346,60 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129046716</v>
+        <v>129056689</v>
       </c>
       <c r="B125" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602747</v>
+        <v>602754</v>
       </c>
       <c r="R125" t="n">
-        <v>7018722</v>
+        <v>7018806</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13443,22 +13443,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B126" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13466,21 +13466,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R126" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13552,10 +13552,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129044962</v>
+        <v>129050404</v>
       </c>
       <c r="B127" t="n">
-        <v>91491</v>
+        <v>80173</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13563,21 +13563,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13587,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602750</v>
+        <v>602672</v>
       </c>
       <c r="R127" t="n">
-        <v>7018799</v>
+        <v>7018808</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -13649,32 +13649,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056700</v>
+        <v>129056668</v>
       </c>
       <c r="B128" t="n">
-        <v>80140</v>
+        <v>91497</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602684</v>
+        <v>602738</v>
       </c>
       <c r="R128" t="n">
-        <v>7018776</v>
+        <v>7018795</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13749,7 +13749,7 @@
         <v>129045554</v>
       </c>
       <c r="B129" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>129050334</v>
       </c>
       <c r="B130" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>129045756</v>
       </c>
       <c r="B131" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129056667</v>
+        <v>129045677</v>
       </c>
       <c r="B132" t="n">
-        <v>96905</v>
+        <v>91533</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R132" t="n">
-        <v>7018807</v>
+        <v>7018786</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,60 +14122,60 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056675</v>
+        <v>129045512</v>
       </c>
       <c r="B133" t="n">
-        <v>92226</v>
+        <v>91533</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R133" t="n">
-        <v>7018832</v>
+        <v>7018827</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14219,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129045512</v>
+        <v>129046455</v>
       </c>
       <c r="B134" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602682</v>
+        <v>602667</v>
       </c>
       <c r="R134" t="n">
-        <v>7018827</v>
+        <v>7018757</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14328,10 +14328,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129045677</v>
+        <v>129044406</v>
       </c>
       <c r="B135" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14339,21 +14339,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14363,10 +14363,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602684</v>
+        <v>602756</v>
       </c>
       <c r="R135" t="n">
-        <v>7018786</v>
+        <v>7018769</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14425,52 +14425,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129046891</v>
+        <v>129056694</v>
       </c>
       <c r="B136" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602726</v>
+        <v>602656</v>
       </c>
       <c r="R136" t="n">
-        <v>7018723</v>
+        <v>7018656</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14514,44 +14510,44 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056694</v>
+        <v>129056675</v>
       </c>
       <c r="B137" t="n">
-        <v>80140</v>
+        <v>92233</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14561,10 +14557,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602656</v>
+        <v>602672</v>
       </c>
       <c r="R137" t="n">
-        <v>7018656</v>
+        <v>7018832</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14623,45 +14619,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B138" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R138" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14720,10 +14720,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129046455</v>
+        <v>129056667</v>
       </c>
       <c r="B139" t="n">
-        <v>79035</v>
+        <v>96915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14731,37 +14731,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602667</v>
+        <v>602672</v>
       </c>
       <c r="R139" t="n">
-        <v>7018757</v>
+        <v>7018807</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14805,12 +14805,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -14909,48 +14909,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129056679</v>
+        <v>129048944</v>
       </c>
       <c r="B141" t="n">
-        <v>91981</v>
+        <v>57725</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602737</v>
+        <v>602734</v>
       </c>
       <c r="R141" t="n">
-        <v>7018593</v>
+        <v>7018579</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14980,6 +14985,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14994,60 +15004,60 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129046813</v>
+        <v>129056679</v>
       </c>
       <c r="B142" t="n">
-        <v>91086</v>
+        <v>91988</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>937</v>
+        <v>1209</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602732</v>
+        <v>602737</v>
       </c>
       <c r="R142" t="n">
-        <v>7018701</v>
+        <v>7018593</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15091,22 +15101,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056695</v>
+        <v>129046813</v>
       </c>
       <c r="B143" t="n">
-        <v>80140</v>
+        <v>91090</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15114,37 +15124,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602754</v>
+        <v>602732</v>
       </c>
       <c r="R143" t="n">
-        <v>7018633</v>
+        <v>7018701</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15188,22 +15198,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B144" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15235,10 +15245,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R144" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15297,10 +15307,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B145" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15308,42 +15318,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R145" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15373,11 +15378,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15392,12 +15392,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15407,7 +15407,7 @@
         <v>129056705</v>
       </c>
       <c r="B146" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>129046543</v>
       </c>
       <c r="B150" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>129046382</v>
       </c>
       <c r="B151" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15999,48 +15999,48 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129056716</v>
+        <v>129044697</v>
       </c>
       <c r="B152" t="n">
-        <v>79035</v>
+        <v>80104</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602754</v>
+        <v>602730</v>
       </c>
       <c r="R152" t="n">
-        <v>7018801</v>
+        <v>7018771</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16084,60 +16084,60 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129044697</v>
+        <v>129056716</v>
       </c>
       <c r="B153" t="n">
-        <v>80100</v>
+        <v>79039</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602730</v>
+        <v>602754</v>
       </c>
       <c r="R153" t="n">
-        <v>7018771</v>
+        <v>7018801</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16181,61 +16181,57 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B154" t="n">
-        <v>98659</v>
+        <v>80048</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R154" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16294,10 +16290,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129056691</v>
+        <v>129056714</v>
       </c>
       <c r="B155" t="n">
-        <v>10964</v>
+        <v>79039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16305,16 +16301,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>101449</v>
+        <v>6425</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16324,10 +16325,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602659</v>
+        <v>602678</v>
       </c>
       <c r="R155" t="n">
-        <v>7018825</v>
+        <v>7018771</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16389,7 +16390,7 @@
         <v>129044275</v>
       </c>
       <c r="B156" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16483,10 +16484,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129050391</v>
+        <v>129045378</v>
       </c>
       <c r="B157" t="n">
-        <v>80044</v>
+        <v>92233</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16494,21 +16495,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16518,10 +16519,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602671</v>
+        <v>602682</v>
       </c>
       <c r="R157" t="n">
-        <v>7018809</v>
+        <v>7018833</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16580,45 +16581,49 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129045378</v>
+        <v>129048151</v>
       </c>
       <c r="B158" t="n">
-        <v>92226</v>
+        <v>98669</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602682</v>
+        <v>602715</v>
       </c>
       <c r="R158" t="n">
-        <v>7018833</v>
+        <v>7018634</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16677,10 +16682,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056714</v>
+        <v>129056691</v>
       </c>
       <c r="B159" t="n">
-        <v>79035</v>
+        <v>10964</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16688,21 +16693,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16712,10 +16712,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602678</v>
+        <v>602659</v>
       </c>
       <c r="R159" t="n">
-        <v>7018771</v>
+        <v>7018825</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16774,10 +16774,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129056685</v>
+        <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,37 +16785,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602683</v>
+        <v>602728</v>
       </c>
       <c r="R160" t="n">
-        <v>7018835</v>
+        <v>7018716</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16859,22 +16859,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129047010</v>
+        <v>129045867</v>
       </c>
       <c r="B161" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16882,21 +16882,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16906,10 +16906,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602728</v>
+        <v>602663</v>
       </c>
       <c r="R161" t="n">
-        <v>7018716</v>
+        <v>7018805</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16968,45 +16968,49 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129045867</v>
+        <v>129044553</v>
       </c>
       <c r="B162" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602663</v>
+        <v>602758</v>
       </c>
       <c r="R162" t="n">
-        <v>7018805</v>
+        <v>7018769</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -17065,49 +17069,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129058444</v>
+        <v>129056685</v>
       </c>
       <c r="B163" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602760</v>
+        <v>602683</v>
       </c>
       <c r="R163" t="n">
-        <v>7018673</v>
+        <v>7018835</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17148,7 +17148,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17167,10 +17166,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129044553</v>
+        <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17195,24 +17194,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602758</v>
+        <v>602760</v>
       </c>
       <c r="R164" t="n">
-        <v>7018769</v>
+        <v>7018673</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17250,18 +17249,19 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17271,7 +17271,7 @@
         <v>129056666</v>
       </c>
       <c r="B165" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17365,53 +17365,48 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129046592</v>
+        <v>129056678</v>
       </c>
       <c r="B166" t="n">
-        <v>57723</v>
+        <v>80048</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602704</v>
+        <v>602672</v>
       </c>
       <c r="R166" t="n">
-        <v>7018751</v>
+        <v>7018832</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17441,11 +17436,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17460,22 +17450,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129048918</v>
+        <v>129048297</v>
       </c>
       <c r="B167" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17483,39 +17473,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602737</v>
+        <v>602752</v>
       </c>
       <c r="R167" t="n">
-        <v>7018577</v>
+        <v>7018614</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17548,11 +17533,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17579,10 +17559,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129048297</v>
+        <v>129044893</v>
       </c>
       <c r="B168" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17614,10 +17594,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602752</v>
+        <v>602729</v>
       </c>
       <c r="R168" t="n">
-        <v>7018614</v>
+        <v>7018798</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17676,10 +17656,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129044893</v>
+        <v>129048918</v>
       </c>
       <c r="B169" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17687,34 +17667,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602729</v>
+        <v>602737</v>
       </c>
       <c r="R169" t="n">
-        <v>7018798</v>
+        <v>7018577</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17747,6 +17732,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17773,10 +17763,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129046627</v>
+        <v>129046592</v>
       </c>
       <c r="B170" t="n">
-        <v>78792</v>
+        <v>57725</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17784,34 +17774,39 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602705</v>
+        <v>602704</v>
       </c>
       <c r="R170" t="n">
-        <v>7018763</v>
+        <v>7018751</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17844,6 +17839,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17870,48 +17870,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056678</v>
+        <v>129046627</v>
       </c>
       <c r="B171" t="n">
-        <v>80044</v>
+        <v>78796</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602672</v>
+        <v>602705</v>
       </c>
       <c r="R171" t="n">
-        <v>7018832</v>
+        <v>7018763</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -7163,32 +7163,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129048001</v>
       </c>
       <c r="B62" t="n">
-        <v>91818</v>
+        <v>91988</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602696</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018662</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,48 +7260,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048001</v>
+        <v>129056720</v>
       </c>
       <c r="B63" t="n">
-        <v>91988</v>
+        <v>80179</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602696</v>
+        <v>602773</v>
       </c>
       <c r="R63" t="n">
-        <v>7018662</v>
+        <v>7018642</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129045225</v>
+        <v>129050367</v>
       </c>
       <c r="B64" t="n">
-        <v>97540</v>
+        <v>80104</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602705</v>
+        <v>602671</v>
       </c>
       <c r="R64" t="n">
-        <v>7018799</v>
+        <v>7018809</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129056720</v>
+        <v>129048977</v>
       </c>
       <c r="B65" t="n">
-        <v>80179</v>
+        <v>91818</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602773</v>
+        <v>602712</v>
       </c>
       <c r="R65" t="n">
-        <v>7018642</v>
+        <v>7018600</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,22 +7539,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129050367</v>
+        <v>129045225</v>
       </c>
       <c r="B66" t="n">
-        <v>80104</v>
+        <v>97540</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7562,21 +7562,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602671</v>
+        <v>602705</v>
       </c>
       <c r="R66" t="n">
-        <v>7018809</v>
+        <v>7018799</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9113,7 +9113,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129056687</v>
+        <v>129045508</v>
       </c>
       <c r="B82" t="n">
         <v>91818</v>
@@ -9144,17 +9144,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602733</v>
+        <v>602674</v>
       </c>
       <c r="R82" t="n">
-        <v>7018822</v>
+        <v>7018842</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,64 +9198,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058573</v>
+        <v>129048233</v>
       </c>
       <c r="B83" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602756</v>
+        <v>602744</v>
       </c>
       <c r="R83" t="n">
-        <v>7018669</v>
+        <v>7018615</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9293,29 +9289,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129045508</v>
+        <v>129048100</v>
       </c>
       <c r="B84" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9323,21 +9318,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9347,10 +9342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602674</v>
+        <v>602670</v>
       </c>
       <c r="R84" t="n">
-        <v>7018842</v>
+        <v>7018643</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9409,32 +9404,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129048233</v>
+        <v>129046057</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>80104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9444,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602744</v>
+        <v>602648</v>
       </c>
       <c r="R85" t="n">
-        <v>7018615</v>
+        <v>7018840</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9506,10 +9501,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129048100</v>
+        <v>129056687</v>
       </c>
       <c r="B86" t="n">
-        <v>80144</v>
+        <v>91818</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9517,37 +9512,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602670</v>
+        <v>602733</v>
       </c>
       <c r="R86" t="n">
-        <v>7018643</v>
+        <v>7018822</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9591,60 +9586,64 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129046057</v>
+        <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>98669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602648</v>
+        <v>602756</v>
       </c>
       <c r="R87" t="n">
-        <v>7018840</v>
+        <v>7018669</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9682,25 +9681,26 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129044846</v>
+        <v>129056686</v>
       </c>
       <c r="B88" t="n">
         <v>91818</v>
@@ -9731,17 +9731,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602719</v>
+        <v>602702</v>
       </c>
       <c r="R88" t="n">
-        <v>7018813</v>
+        <v>7018842</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129048130</v>
+        <v>129056688</v>
       </c>
       <c r="B89" t="n">
-        <v>80144</v>
+        <v>91818</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602704</v>
+        <v>602732</v>
       </c>
       <c r="R89" t="n">
-        <v>7018634</v>
+        <v>7018811</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,22 +9882,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056686</v>
+        <v>129056711</v>
       </c>
       <c r="B90" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602702</v>
+        <v>602771</v>
       </c>
       <c r="R90" t="n">
-        <v>7018842</v>
+        <v>7018641</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129056688</v>
+        <v>129044846</v>
       </c>
       <c r="B91" t="n">
         <v>91818</v>
@@ -10022,17 +10022,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602732</v>
+        <v>602719</v>
       </c>
       <c r="R91" t="n">
-        <v>7018811</v>
+        <v>7018813</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R92" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,12 +10173,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -12054,32 +12054,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044298</v>
+        <v>129046525</v>
       </c>
       <c r="B112" t="n">
-        <v>91988</v>
+        <v>91497</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12089,10 +12089,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602760</v>
+        <v>602669</v>
       </c>
       <c r="R112" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12151,45 +12151,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129046525</v>
+        <v>129044719</v>
       </c>
       <c r="B113" t="n">
-        <v>91497</v>
+        <v>98669</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602669</v>
+        <v>602727</v>
       </c>
       <c r="R113" t="n">
-        <v>7018753</v>
+        <v>7018795</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12248,10 +12252,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129044230</v>
+        <v>129056708</v>
       </c>
       <c r="B114" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12259,42 +12263,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602777</v>
+        <v>602663</v>
       </c>
       <c r="R114" t="n">
-        <v>7018753</v>
+        <v>7018823</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12324,11 +12323,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12343,62 +12337,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129046367</v>
+        <v>129044298</v>
       </c>
       <c r="B115" t="n">
-        <v>57725</v>
+        <v>91988</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602644</v>
+        <v>602760</v>
       </c>
       <c r="R115" t="n">
-        <v>7018800</v>
+        <v>7018767</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12431,11 +12420,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12462,37 +12446,38 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044719</v>
+        <v>129044230</v>
       </c>
       <c r="B116" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12501,10 +12486,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602727</v>
+        <v>602777</v>
       </c>
       <c r="R116" t="n">
-        <v>7018795</v>
+        <v>7018753</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12537,6 +12522,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12563,10 +12553,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129056708</v>
+        <v>129046367</v>
       </c>
       <c r="B117" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12574,37 +12564,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602663</v>
+        <v>602644</v>
       </c>
       <c r="R117" t="n">
-        <v>7018823</v>
+        <v>7018800</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12634,6 +12629,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12648,12 +12648,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13257,52 +13257,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129046716</v>
+        <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>98669</v>
+        <v>91818</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602747</v>
+        <v>602754</v>
       </c>
       <c r="R124" t="n">
-        <v>7018722</v>
+        <v>7018806</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13346,22 +13342,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B125" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13369,21 +13365,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13393,10 +13389,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R125" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13455,48 +13451,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056700</v>
+        <v>129050404</v>
       </c>
       <c r="B126" t="n">
-        <v>80144</v>
+        <v>80173</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R126" t="n">
-        <v>7018776</v>
+        <v>7018808</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,22 +13536,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129050404</v>
+        <v>129056668</v>
       </c>
       <c r="B127" t="n">
-        <v>80173</v>
+        <v>91497</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13563,37 +13559,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602672</v>
+        <v>602738</v>
       </c>
       <c r="R127" t="n">
-        <v>7018808</v>
+        <v>7018795</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,60 +13633,64 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056668</v>
+        <v>129046716</v>
       </c>
       <c r="B128" t="n">
-        <v>91497</v>
+        <v>98669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602738</v>
+        <v>602747</v>
       </c>
       <c r="R128" t="n">
-        <v>7018795</v>
+        <v>7018722</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,12 +13734,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15113,10 +15113,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B143" t="n">
-        <v>91090</v>
+        <v>80144</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15124,37 +15124,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R143" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15198,19 +15198,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056695</v>
+        <v>129056696</v>
       </c>
       <c r="B144" t="n">
         <v>80144</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602754</v>
+        <v>602779</v>
       </c>
       <c r="R144" t="n">
-        <v>7018633</v>
+        <v>7018639</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056696</v>
+        <v>129046813</v>
       </c>
       <c r="B145" t="n">
-        <v>80144</v>
+        <v>91090</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15318,37 +15318,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602779</v>
+        <v>602732</v>
       </c>
       <c r="R145" t="n">
-        <v>7018639</v>
+        <v>7018701</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15392,12 +15392,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>129056690</v>
       </c>
       <c r="B61" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7163,32 +7163,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048001</v>
+        <v>129048977</v>
       </c>
       <c r="B62" t="n">
-        <v>91988</v>
+        <v>91825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602696</v>
+        <v>602712</v>
       </c>
       <c r="R62" t="n">
-        <v>7018662</v>
+        <v>7018600</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,48 +7260,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129056720</v>
+        <v>129048001</v>
       </c>
       <c r="B63" t="n">
-        <v>80179</v>
+        <v>91995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602773</v>
+        <v>602696</v>
       </c>
       <c r="R63" t="n">
-        <v>7018642</v>
+        <v>7018662</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129050367</v>
+        <v>129045225</v>
       </c>
       <c r="B64" t="n">
-        <v>80104</v>
+        <v>97547</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602671</v>
+        <v>602705</v>
       </c>
       <c r="R64" t="n">
-        <v>7018809</v>
+        <v>7018799</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B65" t="n">
-        <v>91818</v>
+        <v>80179</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R65" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,22 +7539,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129045225</v>
+        <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>97540</v>
+        <v>80104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7562,21 +7562,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602705</v>
+        <v>602671</v>
       </c>
       <c r="R66" t="n">
-        <v>7018799</v>
+        <v>7018809</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7651,7 +7651,7 @@
         <v>129045343</v>
       </c>
       <c r="B67" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7750,32 +7750,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045733</v>
+        <v>129050732</v>
       </c>
       <c r="B68" t="n">
-        <v>80173</v>
+        <v>91825</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602669</v>
+        <v>602710</v>
       </c>
       <c r="R68" t="n">
-        <v>7018781</v>
+        <v>7018856</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7850,7 +7850,7 @@
         <v>129056680</v>
       </c>
       <c r="B69" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056715</v>
+        <v>129056672</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7955,21 +7955,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602665</v>
+        <v>602651</v>
       </c>
       <c r="R70" t="n">
-        <v>7018777</v>
+        <v>7018826</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056712</v>
+        <v>129056715</v>
       </c>
       <c r="B71" t="n">
         <v>79039</v>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602730</v>
+        <v>602665</v>
       </c>
       <c r="R71" t="n">
-        <v>7018697</v>
+        <v>7018777</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129044277</v>
+        <v>129056712</v>
       </c>
       <c r="B72" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,37 +8149,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602759</v>
+        <v>602730</v>
       </c>
       <c r="R72" t="n">
-        <v>7018767</v>
+        <v>7018697</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,44 +8223,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129050732</v>
+        <v>129045733</v>
       </c>
       <c r="B73" t="n">
-        <v>91818</v>
+        <v>80173</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602710</v>
+        <v>602669</v>
       </c>
       <c r="R73" t="n">
-        <v>7018856</v>
+        <v>7018781</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056672</v>
+        <v>129044277</v>
       </c>
       <c r="B74" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8363,17 +8363,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602651</v>
+        <v>602759</v>
       </c>
       <c r="R74" t="n">
-        <v>7018826</v>
+        <v>7018767</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,12 +8417,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
         <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056718</v>
+        <v>129056676</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602758</v>
+        <v>602667</v>
       </c>
       <c r="R79" t="n">
-        <v>7018806</v>
+        <v>7018779</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8888,6 +8888,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9011,10 +9016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129056718</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602758</v>
       </c>
       <c r="R81" t="n">
-        <v>7018778</v>
+        <v>7018806</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129045508</v>
+        <v>129056687</v>
       </c>
       <c r="B82" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9144,17 +9144,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602674</v>
+        <v>602733</v>
       </c>
       <c r="R82" t="n">
-        <v>7018842</v>
+        <v>7018822</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,60 +9198,64 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129048233</v>
+        <v>129058573</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602744</v>
+        <v>602756</v>
       </c>
       <c r="R83" t="n">
-        <v>7018615</v>
+        <v>7018669</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9289,28 +9293,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048100</v>
+        <v>129045508</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>91825</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,21 +9323,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9342,10 +9347,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602670</v>
+        <v>602674</v>
       </c>
       <c r="R84" t="n">
-        <v>7018643</v>
+        <v>7018842</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9404,32 +9409,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129046057</v>
+        <v>129048233</v>
       </c>
       <c r="B85" t="n">
-        <v>80104</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602648</v>
+        <v>602744</v>
       </c>
       <c r="R85" t="n">
-        <v>7018840</v>
+        <v>7018615</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,48 +9506,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129056687</v>
+        <v>129046057</v>
       </c>
       <c r="B86" t="n">
-        <v>91818</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602733</v>
+        <v>602648</v>
       </c>
       <c r="R86" t="n">
-        <v>7018822</v>
+        <v>7018840</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9586,64 +9591,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058573</v>
+        <v>129048100</v>
       </c>
       <c r="B87" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602756</v>
+        <v>602670</v>
       </c>
       <c r="R87" t="n">
-        <v>7018669</v>
+        <v>7018643</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9681,29 +9682,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056686</v>
+        <v>129044846</v>
       </c>
       <c r="B88" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9731,17 +9731,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602702</v>
+        <v>602719</v>
       </c>
       <c r="R88" t="n">
-        <v>7018842</v>
+        <v>7018813</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056688</v>
+        <v>129056686</v>
       </c>
       <c r="B89" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602732</v>
+        <v>602702</v>
       </c>
       <c r="R89" t="n">
-        <v>7018811</v>
+        <v>7018842</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056711</v>
+        <v>129056688</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602771</v>
+        <v>602732</v>
       </c>
       <c r="R90" t="n">
-        <v>7018641</v>
+        <v>7018811</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129044846</v>
+        <v>129056711</v>
       </c>
       <c r="B91" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,37 +10002,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602719</v>
+        <v>602771</v>
       </c>
       <c r="R91" t="n">
-        <v>7018813</v>
+        <v>7018641</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,12 +10076,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R93" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056683</v>
+        <v>129048547</v>
       </c>
       <c r="B94" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,37 +10293,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602739</v>
+        <v>602747</v>
       </c>
       <c r="R94" t="n">
-        <v>7018692</v>
+        <v>7018592</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056698</v>
+        <v>129056683</v>
       </c>
       <c r="B95" t="n">
-        <v>80144</v>
+        <v>91825</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602735</v>
+        <v>602739</v>
       </c>
       <c r="R95" t="n">
-        <v>7018716</v>
+        <v>7018692</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,10 +10476,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129046062</v>
+        <v>129056709</v>
       </c>
       <c r="B96" t="n">
-        <v>80144</v>
+        <v>91558</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,37 +10487,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602648</v>
+        <v>602654</v>
       </c>
       <c r="R96" t="n">
-        <v>7018840</v>
+        <v>7018820</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,19 +10561,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B97" t="n">
         <v>80144</v>
@@ -10604,17 +10604,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R97" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,63 +10658,64 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058560</v>
+        <v>129045623</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602760</v>
+        <v>602687</v>
       </c>
       <c r="R98" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10752,67 +10753,69 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129056713</v>
+        <v>129046720</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>92165</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602690</v>
+        <v>602747</v>
       </c>
       <c r="R99" t="n">
-        <v>7018768</v>
+        <v>7018721</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10844,76 +10847,78 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129045623</v>
+        <v>129056713</v>
       </c>
       <c r="B100" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602687</v>
+        <v>602690</v>
       </c>
       <c r="R100" t="n">
-        <v>7018769</v>
+        <v>7018768</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10957,44 +10962,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129046720</v>
+        <v>129058560</v>
       </c>
       <c r="B101" t="n">
-        <v>92158</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11003,17 +11008,17 @@
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602747</v>
+        <v>602760</v>
       </c>
       <c r="R101" t="n">
-        <v>7018721</v>
+        <v>7018673</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11043,11 +11048,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11063,22 +11063,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129056671</v>
+        <v>129045453</v>
       </c>
       <c r="B102" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11106,17 +11106,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602735</v>
+        <v>602673</v>
       </c>
       <c r="R102" t="n">
-        <v>7018592</v>
+        <v>7018844</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11160,22 +11160,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129056693</v>
+        <v>129044824</v>
       </c>
       <c r="B103" t="n">
-        <v>80144</v>
+        <v>91825</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11183,37 +11183,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602670</v>
+        <v>602731</v>
       </c>
       <c r="R103" t="n">
-        <v>7018818</v>
+        <v>7018789</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11243,11 +11243,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11262,22 +11257,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129056697</v>
+        <v>129044805</v>
       </c>
       <c r="B104" t="n">
-        <v>80144</v>
+        <v>91825</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11285,37 +11280,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602730</v>
+        <v>602747</v>
       </c>
       <c r="R104" t="n">
-        <v>7018719</v>
+        <v>7018784</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11359,61 +11354,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129050244</v>
+        <v>129045582</v>
       </c>
       <c r="B105" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602665</v>
+        <v>602703</v>
       </c>
       <c r="R105" t="n">
-        <v>7018784</v>
+        <v>7018798</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11472,10 +11463,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129044824</v>
+        <v>129045681</v>
       </c>
       <c r="B106" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11483,21 +11474,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11507,10 +11498,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602731</v>
+        <v>602667</v>
       </c>
       <c r="R106" t="n">
-        <v>7018789</v>
+        <v>7018779</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11569,10 +11560,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044805</v>
+        <v>129056684</v>
       </c>
       <c r="B107" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11600,17 +11591,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602747</v>
+        <v>602651</v>
       </c>
       <c r="R107" t="n">
-        <v>7018784</v>
+        <v>7018826</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11654,22 +11645,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129045453</v>
+        <v>129056671</v>
       </c>
       <c r="B108" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11697,17 +11688,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602673</v>
+        <v>602735</v>
       </c>
       <c r="R108" t="n">
-        <v>7018844</v>
+        <v>7018592</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11751,19 +11742,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129045681</v>
+        <v>129056697</v>
       </c>
       <c r="B109" t="n">
         <v>80144</v>
@@ -11794,17 +11785,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602667</v>
+        <v>602730</v>
       </c>
       <c r="R109" t="n">
-        <v>7018779</v>
+        <v>7018719</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11848,19 +11839,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129045582</v>
+        <v>129056693</v>
       </c>
       <c r="B110" t="n">
         <v>80144</v>
@@ -11891,17 +11882,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602703</v>
+        <v>602670</v>
       </c>
       <c r="R110" t="n">
-        <v>7018798</v>
+        <v>7018818</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11931,6 +11922,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11945,60 +11941,64 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129056684</v>
+        <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602651</v>
+        <v>602665</v>
       </c>
       <c r="R111" t="n">
-        <v>7018826</v>
+        <v>7018784</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,60 +12042,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129046525</v>
+        <v>129056708</v>
       </c>
       <c r="B112" t="n">
-        <v>91497</v>
+        <v>91558</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602669</v>
+        <v>602663</v>
       </c>
       <c r="R112" t="n">
-        <v>7018753</v>
+        <v>7018823</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12139,22 +12139,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129044719</v>
+        <v>129044298</v>
       </c>
       <c r="B113" t="n">
-        <v>98669</v>
+        <v>91995</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12162,38 +12162,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602727</v>
+        <v>602760</v>
       </c>
       <c r="R113" t="n">
-        <v>7018795</v>
+        <v>7018767</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12252,48 +12248,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129056708</v>
+        <v>129046525</v>
       </c>
       <c r="B114" t="n">
-        <v>91551</v>
+        <v>91504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602663</v>
+        <v>602669</v>
       </c>
       <c r="R114" t="n">
-        <v>7018823</v>
+        <v>7018753</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12337,57 +12333,62 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129044298</v>
+        <v>129044230</v>
       </c>
       <c r="B115" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602760</v>
+        <v>602777</v>
       </c>
       <c r="R115" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12420,6 +12421,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12446,7 +12452,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044230</v>
+        <v>129046367</v>
       </c>
       <c r="B116" t="n">
         <v>57725</v>
@@ -12477,7 +12483,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12486,10 +12492,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602777</v>
+        <v>602644</v>
       </c>
       <c r="R116" t="n">
-        <v>7018753</v>
+        <v>7018800</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12526,7 +12532,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12553,38 +12559,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129046367</v>
+        <v>129044719</v>
       </c>
       <c r="B117" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -12593,10 +12598,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602644</v>
+        <v>602727</v>
       </c>
       <c r="R117" t="n">
-        <v>7018800</v>
+        <v>7018795</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12629,11 +12634,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12663,7 +12663,7 @@
         <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12757,10 +12757,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B119" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,21 +12768,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12792,10 +12792,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R119" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12854,10 +12854,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056702</v>
+        <v>129050601</v>
       </c>
       <c r="B120" t="n">
-        <v>80144</v>
+        <v>10964</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12865,37 +12865,41 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602649</v>
+        <v>602698</v>
       </c>
       <c r="R120" t="n">
-        <v>7018829</v>
+        <v>7018836</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12927,34 +12931,40 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129050601</v>
+        <v>129056681</v>
       </c>
       <c r="B121" t="n">
-        <v>10964</v>
+        <v>91825</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12962,41 +12972,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602698</v>
+        <v>602736</v>
       </c>
       <c r="R121" t="n">
-        <v>7018836</v>
+        <v>7018593</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13028,30 +13034,24 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
         <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13160,45 +13160,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129044962</v>
+        <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>91497</v>
+        <v>98676</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602750</v>
+        <v>602747</v>
       </c>
       <c r="R123" t="n">
-        <v>7018799</v>
+        <v>7018722</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13260,7 +13264,7 @@
         <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13354,32 +13358,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056700</v>
+        <v>129056668</v>
       </c>
       <c r="B125" t="n">
-        <v>80144</v>
+        <v>91504</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13389,10 +13393,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602684</v>
+        <v>602738</v>
       </c>
       <c r="R125" t="n">
-        <v>7018776</v>
+        <v>7018795</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13548,32 +13552,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056668</v>
+        <v>129056700</v>
       </c>
       <c r="B127" t="n">
-        <v>91497</v>
+        <v>80144</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13583,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602738</v>
+        <v>602684</v>
       </c>
       <c r="R127" t="n">
-        <v>7018795</v>
+        <v>7018776</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13645,49 +13649,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129046716</v>
+        <v>129044962</v>
       </c>
       <c r="B128" t="n">
-        <v>98669</v>
+        <v>91504</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602747</v>
+        <v>602750</v>
       </c>
       <c r="R128" t="n">
-        <v>7018722</v>
+        <v>7018799</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13843,32 +13843,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129050334</v>
+        <v>129045756</v>
       </c>
       <c r="B130" t="n">
-        <v>80144</v>
+        <v>80104</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602671</v>
+        <v>602663</v>
       </c>
       <c r="R130" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13940,32 +13940,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B131" t="n">
-        <v>80104</v>
+        <v>80144</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R131" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045677</v>
+        <v>129056667</v>
       </c>
       <c r="B132" t="n">
-        <v>91533</v>
+        <v>96922</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R132" t="n">
-        <v>7018786</v>
+        <v>7018807</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,22 +14122,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129045512</v>
+        <v>129056694</v>
       </c>
       <c r="B133" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14145,37 +14145,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602682</v>
+        <v>602656</v>
       </c>
       <c r="R133" t="n">
-        <v>7018827</v>
+        <v>7018656</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14219,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129046455</v>
+        <v>129056692</v>
       </c>
       <c r="B134" t="n">
-        <v>79039</v>
+        <v>10964</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,37 +14242,32 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602667</v>
+        <v>602687</v>
       </c>
       <c r="R134" t="n">
-        <v>7018757</v>
+        <v>7018836</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14316,12 +14311,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14425,10 +14420,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056694</v>
+        <v>129045512</v>
       </c>
       <c r="B136" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14436,37 +14431,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602656</v>
+        <v>602682</v>
       </c>
       <c r="R136" t="n">
-        <v>7018656</v>
+        <v>7018827</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,60 +14505,60 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056675</v>
+        <v>129045677</v>
       </c>
       <c r="B137" t="n">
-        <v>92233</v>
+        <v>91540</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R137" t="n">
-        <v>7018832</v>
+        <v>7018786</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14607,61 +14602,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129046891</v>
+        <v>129046455</v>
       </c>
       <c r="B138" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602726</v>
+        <v>602667</v>
       </c>
       <c r="R138" t="n">
-        <v>7018723</v>
+        <v>7018757</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14720,48 +14711,52 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056667</v>
+        <v>129046891</v>
       </c>
       <c r="B139" t="n">
-        <v>96915</v>
+        <v>98676</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602672</v>
+        <v>602726</v>
       </c>
       <c r="R139" t="n">
-        <v>7018807</v>
+        <v>7018723</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14805,39 +14800,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056692</v>
+        <v>129056675</v>
       </c>
       <c r="B140" t="n">
-        <v>10964</v>
+        <v>92240</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101449</v>
+        <v>3298</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602687</v>
+        <v>602672</v>
       </c>
       <c r="R140" t="n">
-        <v>7018836</v>
+        <v>7018832</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14909,10 +14909,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129048944</v>
+        <v>129046813</v>
       </c>
       <c r="B141" t="n">
-        <v>57725</v>
+        <v>91097</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,39 +14920,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>937</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602734</v>
+        <v>602732</v>
       </c>
       <c r="R141" t="n">
-        <v>7018579</v>
+        <v>7018701</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14985,11 +14980,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15016,48 +15006,53 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056679</v>
+        <v>129048944</v>
       </c>
       <c r="B142" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602737</v>
+        <v>602734</v>
       </c>
       <c r="R142" t="n">
-        <v>7018593</v>
+        <v>7018579</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15087,6 +15082,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15101,44 +15101,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B143" t="n">
-        <v>80144</v>
+        <v>91995</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15148,10 +15148,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R143" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B145" t="n">
-        <v>91090</v>
+        <v>80144</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15318,37 +15318,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R145" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15392,12 +15392,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15603,10 +15603,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B148" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15642,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R148" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15704,10 +15704,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B149" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15743,10 +15743,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R149" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>90562</v>
+        <v>91825</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15816,21 +15816,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15840,10 +15840,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R150" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15902,10 +15902,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046382</v>
+        <v>129046543</v>
       </c>
       <c r="B151" t="n">
-        <v>91818</v>
+        <v>90569</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,21 +15913,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602637</v>
+        <v>602686</v>
       </c>
       <c r="R151" t="n">
-        <v>7018802</v>
+        <v>7018745</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16193,32 +16193,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129050391</v>
+        <v>129044275</v>
       </c>
       <c r="B154" t="n">
-        <v>80048</v>
+        <v>91825</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602671</v>
+        <v>602766</v>
       </c>
       <c r="R154" t="n">
-        <v>7018809</v>
+        <v>7018767</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,48 +16290,48 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129056714</v>
+        <v>129045378</v>
       </c>
       <c r="B155" t="n">
-        <v>79039</v>
+        <v>92240</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602678</v>
+        <v>602682</v>
       </c>
       <c r="R155" t="n">
-        <v>7018771</v>
+        <v>7018833</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16375,57 +16375,61 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129044275</v>
+        <v>129048151</v>
       </c>
       <c r="B156" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602766</v>
+        <v>602715</v>
       </c>
       <c r="R156" t="n">
-        <v>7018767</v>
+        <v>7018634</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16484,48 +16488,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129045378</v>
+        <v>129056714</v>
       </c>
       <c r="B157" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602682</v>
+        <v>602678</v>
       </c>
       <c r="R157" t="n">
-        <v>7018833</v>
+        <v>7018771</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16569,61 +16573,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B158" t="n">
-        <v>98669</v>
+        <v>80048</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R158" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16777,7 +16777,7 @@
         <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>129044553</v>
       </c>
       <c r="B162" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>129056685</v>
       </c>
       <c r="B163" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17268,10 +17268,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129056666</v>
+        <v>129048297</v>
       </c>
       <c r="B165" t="n">
-        <v>96915</v>
+        <v>91825</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,37 +17279,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602756</v>
+        <v>602752</v>
       </c>
       <c r="R165" t="n">
-        <v>7018643</v>
+        <v>7018614</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17353,60 +17353,60 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129056678</v>
+        <v>129044893</v>
       </c>
       <c r="B166" t="n">
-        <v>80048</v>
+        <v>91825</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602672</v>
+        <v>602729</v>
       </c>
       <c r="R166" t="n">
-        <v>7018832</v>
+        <v>7018798</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17450,22 +17450,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B167" t="n">
-        <v>91818</v>
+        <v>78796</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,21 +17473,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R167" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17559,10 +17559,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129044893</v>
+        <v>129046592</v>
       </c>
       <c r="B168" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17570,34 +17570,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602729</v>
+        <v>602704</v>
       </c>
       <c r="R168" t="n">
-        <v>7018798</v>
+        <v>7018751</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17630,6 +17635,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17763,10 +17773,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129046592</v>
+        <v>129056666</v>
       </c>
       <c r="B170" t="n">
-        <v>57725</v>
+        <v>96922</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17774,42 +17784,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602704</v>
+        <v>602756</v>
       </c>
       <c r="R170" t="n">
-        <v>7018751</v>
+        <v>7018643</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17839,11 +17844,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17858,60 +17858,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129046627</v>
+        <v>129056678</v>
       </c>
       <c r="B171" t="n">
-        <v>78796</v>
+        <v>80048</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602705</v>
+        <v>602672</v>
       </c>
       <c r="R171" t="n">
-        <v>7018763</v>
+        <v>7018832</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,10 +6775,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045323</v>
+        <v>129056690</v>
       </c>
       <c r="B58" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602682</v>
+        <v>602758</v>
       </c>
       <c r="R58" t="n">
-        <v>7018848</v>
+        <v>7018806</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,60 +6860,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045660</v>
+        <v>129056682</v>
       </c>
       <c r="B59" t="n">
-        <v>80048</v>
+        <v>91827</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602684</v>
+        <v>602751</v>
       </c>
       <c r="R59" t="n">
-        <v>7018786</v>
+        <v>7018603</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,60 +6957,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056682</v>
+        <v>129045660</v>
       </c>
       <c r="B60" t="n">
-        <v>91825</v>
+        <v>80050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602751</v>
+        <v>602684</v>
       </c>
       <c r="R60" t="n">
-        <v>7018603</v>
+        <v>7018786</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,22 +7054,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056690</v>
+        <v>129045323</v>
       </c>
       <c r="B61" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,17 +7097,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602758</v>
+        <v>602682</v>
       </c>
       <c r="R61" t="n">
-        <v>7018806</v>
+        <v>7018848</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,44 +7151,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129045225</v>
       </c>
       <c r="B62" t="n">
-        <v>91825</v>
+        <v>97549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602705</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018799</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048001</v>
+        <v>129050367</v>
       </c>
       <c r="B63" t="n">
-        <v>91995</v>
+        <v>80106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R63" t="n">
-        <v>7018662</v>
+        <v>7018809</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,32 +7357,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B64" t="n">
-        <v>97547</v>
+        <v>91827</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R64" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7457,7 +7457,7 @@
         <v>129056720</v>
       </c>
       <c r="B65" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129050367</v>
+        <v>129048001</v>
       </c>
       <c r="B66" t="n">
-        <v>80104</v>
+        <v>91997</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R66" t="n">
-        <v>7018809</v>
+        <v>7018662</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045343</v>
+        <v>129056680</v>
       </c>
       <c r="B67" t="n">
-        <v>91951</v>
+        <v>91997</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4217</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602684</v>
+        <v>602732</v>
       </c>
       <c r="R67" t="n">
-        <v>7018837</v>
+        <v>7018811</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7719,11 +7719,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7738,22 +7733,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129050732</v>
+        <v>129056672</v>
       </c>
       <c r="B68" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,37 +7756,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602710</v>
+        <v>602651</v>
       </c>
       <c r="R68" t="n">
-        <v>7018856</v>
+        <v>7018826</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7835,60 +7830,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129056680</v>
+        <v>129050732</v>
       </c>
       <c r="B69" t="n">
-        <v>91995</v>
+        <v>91827</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602732</v>
+        <v>602710</v>
       </c>
       <c r="R69" t="n">
-        <v>7018811</v>
+        <v>7018856</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7932,22 +7927,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056672</v>
+        <v>129056712</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7955,21 +7950,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7974,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602651</v>
+        <v>602730</v>
       </c>
       <c r="R70" t="n">
-        <v>7018826</v>
+        <v>7018697</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8044,7 +8039,7 @@
         <v>129056715</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8138,10 +8133,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056712</v>
+        <v>129044277</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,37 +8144,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602730</v>
+        <v>602759</v>
       </c>
       <c r="R72" t="n">
-        <v>7018697</v>
+        <v>7018767</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,12 +8218,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8238,7 +8233,7 @@
         <v>129045733</v>
       </c>
       <c r="B73" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8332,32 +8327,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129044277</v>
+        <v>129045343</v>
       </c>
       <c r="B74" t="n">
-        <v>91540</v>
+        <v>91953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8367,10 +8362,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602759</v>
+        <v>602684</v>
       </c>
       <c r="R74" t="n">
-        <v>7018767</v>
+        <v>7018837</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8403,6 +8398,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8429,10 +8429,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129056676</v>
       </c>
       <c r="B75" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,37 +8440,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R75" t="n">
-        <v>7018759</v>
+        <v>7018778</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,6 +8500,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8514,60 +8519,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129044345</v>
+        <v>129056718</v>
       </c>
       <c r="B76" t="n">
-        <v>91741</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602772</v>
+        <v>602758</v>
       </c>
       <c r="R76" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8611,22 +8616,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129049465</v>
+        <v>129056699</v>
       </c>
       <c r="B77" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8654,17 +8659,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602650</v>
+        <v>602729</v>
       </c>
       <c r="R77" t="n">
-        <v>7018649</v>
+        <v>7018756</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8708,44 +8713,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129045649</v>
+        <v>129044345</v>
       </c>
       <c r="B78" t="n">
-        <v>80144</v>
+        <v>91743</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8755,10 +8760,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602688</v>
+        <v>602772</v>
       </c>
       <c r="R78" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8817,10 +8822,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056676</v>
+        <v>129049465</v>
       </c>
       <c r="B79" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,37 +8833,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602667</v>
+        <v>602650</v>
       </c>
       <c r="R79" t="n">
-        <v>7018779</v>
+        <v>7018649</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8888,11 +8893,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,22 +8907,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056699</v>
+        <v>129045649</v>
       </c>
       <c r="B80" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8950,17 +8950,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602729</v>
+        <v>602688</v>
       </c>
       <c r="R80" t="n">
-        <v>7018756</v>
+        <v>7018774</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9004,22 +9004,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056718</v>
+        <v>129046472</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,37 +9027,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602758</v>
+        <v>602666</v>
       </c>
       <c r="R81" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9101,12 +9101,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9116,7 +9116,7 @@
         <v>129056687</v>
       </c>
       <c r="B82" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>129058573</v>
       </c>
       <c r="B83" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129045508</v>
+        <v>129048233</v>
       </c>
       <c r="B84" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9323,21 +9323,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602674</v>
+        <v>602744</v>
       </c>
       <c r="R84" t="n">
-        <v>7018842</v>
+        <v>7018615</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129048233</v>
+        <v>129048100</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9420,21 +9420,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602744</v>
+        <v>602670</v>
       </c>
       <c r="R85" t="n">
-        <v>7018615</v>
+        <v>7018643</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129046057</v>
+        <v>129045508</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>91827</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602648</v>
+        <v>602674</v>
       </c>
       <c r="R86" t="n">
-        <v>7018840</v>
+        <v>7018842</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9603,32 +9603,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129048100</v>
+        <v>129046057</v>
       </c>
       <c r="B87" t="n">
-        <v>80144</v>
+        <v>80106</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602670</v>
+        <v>602648</v>
       </c>
       <c r="R87" t="n">
-        <v>7018643</v>
+        <v>7018840</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129044846</v>
+        <v>129056688</v>
       </c>
       <c r="B88" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9731,17 +9731,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602719</v>
+        <v>602732</v>
       </c>
       <c r="R88" t="n">
-        <v>7018813</v>
+        <v>7018811</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,12 +9785,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
         <v>129056686</v>
       </c>
       <c r="B89" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056688</v>
+        <v>129056711</v>
       </c>
       <c r="B90" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602732</v>
+        <v>602771</v>
       </c>
       <c r="R90" t="n">
-        <v>7018811</v>
+        <v>7018641</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,37 +10002,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R91" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129048130</v>
+        <v>129044846</v>
       </c>
       <c r="B92" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,21 +10099,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602704</v>
+        <v>602719</v>
       </c>
       <c r="R92" t="n">
-        <v>7018634</v>
+        <v>7018813</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129046062</v>
+        <v>129056683</v>
       </c>
       <c r="B93" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602648</v>
+        <v>602739</v>
       </c>
       <c r="R93" t="n">
-        <v>7018840</v>
+        <v>7018692</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129048547</v>
+        <v>129056709</v>
       </c>
       <c r="B94" t="n">
-        <v>80144</v>
+        <v>91560</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,37 +10293,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602747</v>
+        <v>602654</v>
       </c>
       <c r="R94" t="n">
-        <v>7018592</v>
+        <v>7018820</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056683</v>
+        <v>129056698</v>
       </c>
       <c r="B95" t="n">
-        <v>91825</v>
+        <v>80146</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602739</v>
+        <v>602735</v>
       </c>
       <c r="R95" t="n">
-        <v>7018692</v>
+        <v>7018716</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,10 +10476,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B96" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,37 +10487,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R96" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,22 +10561,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B97" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10604,17 +10604,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R97" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,64 +10658,63 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045623</v>
+        <v>129058560</v>
       </c>
       <c r="B98" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602687</v>
+        <v>602760</v>
       </c>
       <c r="R98" t="n">
-        <v>7018769</v>
+        <v>7018673</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10753,69 +10752,67 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129046720</v>
+        <v>129056713</v>
       </c>
       <c r="B99" t="n">
-        <v>92165</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602747</v>
+        <v>602690</v>
       </c>
       <c r="R99" t="n">
-        <v>7018721</v>
+        <v>7018768</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10847,78 +10844,75 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129056713</v>
+        <v>129046720</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>92167</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602690</v>
+        <v>602747</v>
       </c>
       <c r="R100" t="n">
-        <v>7018768</v>
+        <v>7018721</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10950,75 +10944,82 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129058560</v>
+        <v>129045623</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602760</v>
+        <v>602687</v>
       </c>
       <c r="R101" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11056,29 +11057,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045453</v>
+        <v>129056684</v>
       </c>
       <c r="B102" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11086,37 +11086,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602673</v>
+        <v>602651</v>
       </c>
       <c r="R102" t="n">
-        <v>7018844</v>
+        <v>7018826</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11160,22 +11160,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044824</v>
+        <v>129056671</v>
       </c>
       <c r="B103" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11183,37 +11183,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602731</v>
+        <v>602735</v>
       </c>
       <c r="R103" t="n">
-        <v>7018789</v>
+        <v>7018592</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11257,54 +11257,58 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044805</v>
+        <v>129050244</v>
       </c>
       <c r="B104" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602747</v>
+        <v>602665</v>
       </c>
       <c r="R104" t="n">
         <v>7018784</v>
@@ -11366,10 +11370,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045582</v>
+        <v>129045681</v>
       </c>
       <c r="B105" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11401,10 +11405,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602703</v>
+        <v>602667</v>
       </c>
       <c r="R105" t="n">
-        <v>7018798</v>
+        <v>7018778</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11463,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129045681</v>
+        <v>129056697</v>
       </c>
       <c r="B106" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11494,17 +11498,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602667</v>
+        <v>602730</v>
       </c>
       <c r="R106" t="n">
-        <v>7018779</v>
+        <v>7018719</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11548,22 +11552,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056684</v>
+        <v>129056693</v>
       </c>
       <c r="B107" t="n">
-        <v>91825</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11571,21 +11575,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11595,10 +11599,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602651</v>
+        <v>602670</v>
       </c>
       <c r="R107" t="n">
-        <v>7018826</v>
+        <v>7018818</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11631,6 +11635,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11657,10 +11666,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056671</v>
+        <v>129045453</v>
       </c>
       <c r="B108" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11688,17 +11697,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602735</v>
+        <v>602673</v>
       </c>
       <c r="R108" t="n">
-        <v>7018592</v>
+        <v>7018844</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11742,22 +11751,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056697</v>
+        <v>129044824</v>
       </c>
       <c r="B109" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11765,37 +11774,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602730</v>
+        <v>602731</v>
       </c>
       <c r="R109" t="n">
-        <v>7018719</v>
+        <v>7018789</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11839,22 +11848,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056693</v>
+        <v>129044805</v>
       </c>
       <c r="B110" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11862,37 +11871,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602670</v>
+        <v>602747</v>
       </c>
       <c r="R110" t="n">
-        <v>7018818</v>
+        <v>7018784</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11922,11 +11931,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11941,61 +11945,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129050244</v>
+        <v>129045582</v>
       </c>
       <c r="B111" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602665</v>
+        <v>602703</v>
       </c>
       <c r="R111" t="n">
-        <v>7018784</v>
+        <v>7018798</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12057,7 +12057,7 @@
         <v>129056708</v>
       </c>
       <c r="B112" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12151,45 +12151,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129044298</v>
+        <v>129044230</v>
       </c>
       <c r="B113" t="n">
-        <v>91995</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602760</v>
+        <v>602777</v>
       </c>
       <c r="R113" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12222,6 +12227,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12248,45 +12258,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129046525</v>
+        <v>129046367</v>
       </c>
       <c r="B114" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602669</v>
+        <v>602644</v>
       </c>
       <c r="R114" t="n">
-        <v>7018753</v>
+        <v>7018800</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12319,6 +12334,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12345,47 +12365,42 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129044230</v>
+        <v>129046525</v>
       </c>
       <c r="B115" t="n">
-        <v>57725</v>
+        <v>91506</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602777</v>
+        <v>602669</v>
       </c>
       <c r="R115" t="n">
         <v>7018753</v>
@@ -12421,11 +12436,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12452,50 +12462,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129046367</v>
+        <v>129044298</v>
       </c>
       <c r="B116" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602644</v>
+        <v>602760</v>
       </c>
       <c r="R116" t="n">
-        <v>7018800</v>
+        <v>7018767</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12528,11 +12533,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12562,7 +12562,7 @@
         <v>129044719</v>
       </c>
       <c r="B117" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129044475</v>
+        <v>129056681</v>
       </c>
       <c r="B118" t="n">
-        <v>91558</v>
+        <v>91827</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,37 +12671,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602766</v>
+        <v>602736</v>
       </c>
       <c r="R118" t="n">
-        <v>7018781</v>
+        <v>7018593</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12745,12 +12745,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12760,7 +12760,7 @@
         <v>129056702</v>
       </c>
       <c r="B119" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12854,52 +12854,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129050601</v>
+        <v>129056704</v>
       </c>
       <c r="B120" t="n">
-        <v>10964</v>
+        <v>98678</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602698</v>
+        <v>602735</v>
       </c>
       <c r="R120" t="n">
-        <v>7018836</v>
+        <v>7018692</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12933,7 +12929,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Under bark, granlåga</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12942,29 +12938,28 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056681</v>
+        <v>129050601</v>
       </c>
       <c r="B121" t="n">
-        <v>91825</v>
+        <v>10964</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12972,37 +12967,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602736</v>
+        <v>602698</v>
       </c>
       <c r="R121" t="n">
-        <v>7018593</v>
+        <v>7018836</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13034,72 +13033,78 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056704</v>
+        <v>129044475</v>
       </c>
       <c r="B122" t="n">
-        <v>98676</v>
+        <v>91560</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602735</v>
+        <v>602766</v>
       </c>
       <c r="R122" t="n">
-        <v>7018692</v>
+        <v>7018781</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13129,11 +13134,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13148,64 +13148,60 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129046716</v>
+        <v>129056689</v>
       </c>
       <c r="B123" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602747</v>
+        <v>602754</v>
       </c>
       <c r="R123" t="n">
-        <v>7018722</v>
+        <v>7018806</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13249,44 +13245,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056689</v>
+        <v>129056668</v>
       </c>
       <c r="B124" t="n">
-        <v>91825</v>
+        <v>91506</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13296,10 +13292,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602754</v>
+        <v>602738</v>
       </c>
       <c r="R124" t="n">
-        <v>7018806</v>
+        <v>7018795</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13358,10 +13354,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056668</v>
+        <v>129050404</v>
       </c>
       <c r="B125" t="n">
-        <v>91504</v>
+        <v>80175</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13369,37 +13365,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602738</v>
+        <v>602672</v>
       </c>
       <c r="R125" t="n">
-        <v>7018795</v>
+        <v>7018808</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13443,60 +13439,60 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129050404</v>
+        <v>129056700</v>
       </c>
       <c r="B126" t="n">
-        <v>80173</v>
+        <v>80146</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R126" t="n">
-        <v>7018808</v>
+        <v>7018776</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,60 +13536,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056700</v>
+        <v>129044962</v>
       </c>
       <c r="B127" t="n">
-        <v>80144</v>
+        <v>91506</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602684</v>
+        <v>602750</v>
       </c>
       <c r="R127" t="n">
-        <v>7018776</v>
+        <v>7018799</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,57 +13633,61 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129044962</v>
+        <v>129046716</v>
       </c>
       <c r="B128" t="n">
-        <v>91504</v>
+        <v>98678</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602750</v>
+        <v>602747</v>
       </c>
       <c r="R128" t="n">
-        <v>7018799</v>
+        <v>7018722</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13746,10 +13746,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129045554</v>
+        <v>129050334</v>
       </c>
       <c r="B129" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13781,10 +13781,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R129" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13846,7 +13846,7 @@
         <v>129045756</v>
       </c>
       <c r="B130" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129050334</v>
+        <v>129045554</v>
       </c>
       <c r="B131" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R131" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129056667</v>
+        <v>129045512</v>
       </c>
       <c r="B132" t="n">
-        <v>96922</v>
+        <v>91542</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,37 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R132" t="n">
-        <v>7018807</v>
+        <v>7018827</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,44 +14122,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056694</v>
+        <v>129056675</v>
       </c>
       <c r="B133" t="n">
-        <v>80144</v>
+        <v>92242</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602656</v>
+        <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018656</v>
+        <v>7018832</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14231,10 +14231,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129056692</v>
+        <v>129056694</v>
       </c>
       <c r="B134" t="n">
-        <v>10964</v>
+        <v>80146</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,16 +14242,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14261,10 +14266,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602687</v>
+        <v>602656</v>
       </c>
       <c r="R134" t="n">
-        <v>7018836</v>
+        <v>7018656</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14323,10 +14328,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129044406</v>
+        <v>129056667</v>
       </c>
       <c r="B135" t="n">
-        <v>80144</v>
+        <v>96924</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14334,37 +14339,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R135" t="n">
-        <v>7018769</v>
+        <v>7018807</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14408,22 +14413,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129045512</v>
+        <v>129056692</v>
       </c>
       <c r="B136" t="n">
-        <v>91540</v>
+        <v>10964</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14431,37 +14436,32 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602682</v>
+        <v>602687</v>
       </c>
       <c r="R136" t="n">
-        <v>7018827</v>
+        <v>7018836</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14505,22 +14505,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129045677</v>
+        <v>129046455</v>
       </c>
       <c r="B137" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14528,21 +14528,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14552,10 +14552,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602684</v>
+        <v>602667</v>
       </c>
       <c r="R137" t="n">
-        <v>7018786</v>
+        <v>7018757</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14614,10 +14614,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129046455</v>
+        <v>129044406</v>
       </c>
       <c r="B138" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14625,21 +14625,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602667</v>
+        <v>602756</v>
       </c>
       <c r="R138" t="n">
-        <v>7018757</v>
+        <v>7018769</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14711,49 +14711,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129046891</v>
+        <v>129045677</v>
       </c>
       <c r="B139" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602726</v>
+        <v>602684</v>
       </c>
       <c r="R139" t="n">
-        <v>7018723</v>
+        <v>7018786</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14812,48 +14808,52 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056675</v>
+        <v>129046891</v>
       </c>
       <c r="B140" t="n">
-        <v>92240</v>
+        <v>98678</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602672</v>
+        <v>602726</v>
       </c>
       <c r="R140" t="n">
-        <v>7018832</v>
+        <v>7018723</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14897,22 +14897,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B141" t="n">
-        <v>91097</v>
+        <v>80146</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,37 +14920,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R141" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14994,22 +14994,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129048944</v>
+        <v>129046813</v>
       </c>
       <c r="B142" t="n">
-        <v>57725</v>
+        <v>91099</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15017,39 +15017,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>937</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602734</v>
+        <v>602732</v>
       </c>
       <c r="R142" t="n">
-        <v>7018579</v>
+        <v>7018701</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -15082,11 +15077,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15113,48 +15103,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056679</v>
+        <v>129048944</v>
       </c>
       <c r="B143" t="n">
-        <v>91995</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602737</v>
+        <v>602734</v>
       </c>
       <c r="R143" t="n">
-        <v>7018593</v>
+        <v>7018579</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15184,6 +15179,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15198,44 +15198,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056696</v>
+        <v>129056679</v>
       </c>
       <c r="B144" t="n">
-        <v>80144</v>
+        <v>91997</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602779</v>
+        <v>602737</v>
       </c>
       <c r="R144" t="n">
-        <v>7018639</v>
+        <v>7018593</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056695</v>
+        <v>129056696</v>
       </c>
       <c r="B145" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15342,10 +15342,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602754</v>
+        <v>602779</v>
       </c>
       <c r="R145" t="n">
-        <v>7018633</v>
+        <v>7018639</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15407,7 +15407,7 @@
         <v>129056705</v>
       </c>
       <c r="B146" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15603,10 +15603,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15642,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15704,10 +15704,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15743,10 +15743,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,32 +15805,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046382</v>
+        <v>129044697</v>
       </c>
       <c r="B150" t="n">
-        <v>91825</v>
+        <v>80106</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15840,10 +15840,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602637</v>
+        <v>602730</v>
       </c>
       <c r="R150" t="n">
-        <v>7018802</v>
+        <v>7018771</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15902,10 +15902,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046543</v>
+        <v>129056716</v>
       </c>
       <c r="B151" t="n">
-        <v>90569</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,37 +15913,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602686</v>
+        <v>602754</v>
       </c>
       <c r="R151" t="n">
-        <v>7018745</v>
+        <v>7018801</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15987,44 +15987,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129044697</v>
+        <v>129046382</v>
       </c>
       <c r="B152" t="n">
-        <v>80104</v>
+        <v>91827</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602730</v>
+        <v>602637</v>
       </c>
       <c r="R152" t="n">
-        <v>7018771</v>
+        <v>7018802</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129056716</v>
+        <v>129046543</v>
       </c>
       <c r="B153" t="n">
-        <v>79039</v>
+        <v>90571</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16107,37 +16107,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602754</v>
+        <v>602686</v>
       </c>
       <c r="R153" t="n">
-        <v>7018801</v>
+        <v>7018745</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16181,44 +16181,44 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129044275</v>
+        <v>129045378</v>
       </c>
       <c r="B154" t="n">
-        <v>91825</v>
+        <v>92242</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602766</v>
+        <v>602682</v>
       </c>
       <c r="R154" t="n">
-        <v>7018767</v>
+        <v>7018833</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,48 +16290,43 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129045378</v>
+        <v>129056691</v>
       </c>
       <c r="B155" t="n">
-        <v>92240</v>
+        <v>10964</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602682</v>
+        <v>602659</v>
       </c>
       <c r="R155" t="n">
-        <v>7018833</v>
+        <v>7018825</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16375,64 +16370,60 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129048151</v>
+        <v>129056714</v>
       </c>
       <c r="B156" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602715</v>
+        <v>602678</v>
       </c>
       <c r="R156" t="n">
-        <v>7018634</v>
+        <v>7018771</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16476,60 +16467,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129056714</v>
+        <v>129050391</v>
       </c>
       <c r="B157" t="n">
-        <v>79039</v>
+        <v>80050</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602678</v>
+        <v>602671</v>
       </c>
       <c r="R157" t="n">
-        <v>7018771</v>
+        <v>7018809</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16573,44 +16564,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129050391</v>
+        <v>129044275</v>
       </c>
       <c r="B158" t="n">
-        <v>80048</v>
+        <v>91827</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16620,10 +16611,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602671</v>
+        <v>602766</v>
       </c>
       <c r="R158" t="n">
-        <v>7018809</v>
+        <v>7018767</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16682,43 +16673,52 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056691</v>
+        <v>129048151</v>
       </c>
       <c r="B159" t="n">
-        <v>10964</v>
+        <v>98678</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602659</v>
+        <v>602715</v>
       </c>
       <c r="R159" t="n">
-        <v>7018825</v>
+        <v>7018634</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16762,22 +16762,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129047010</v>
+        <v>129045867</v>
       </c>
       <c r="B160" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,21 +16785,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602728</v>
+        <v>602663</v>
       </c>
       <c r="R160" t="n">
-        <v>7018716</v>
+        <v>7018805</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16871,45 +16871,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129045867</v>
+        <v>129044553</v>
       </c>
       <c r="B161" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602663</v>
+        <v>602758</v>
       </c>
       <c r="R161" t="n">
-        <v>7018805</v>
+        <v>7018769</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16968,49 +16972,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B162" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R162" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -17069,45 +17069,49 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129056685</v>
+        <v>129058444</v>
       </c>
       <c r="B163" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602683</v>
+        <v>602760</v>
       </c>
       <c r="R163" t="n">
-        <v>7018835</v>
+        <v>7018673</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17148,6 +17152,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17166,49 +17171,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129058444</v>
+        <v>129056685</v>
       </c>
       <c r="B164" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602760</v>
+        <v>602683</v>
       </c>
       <c r="R164" t="n">
-        <v>7018673</v>
+        <v>7018835</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17249,7 +17250,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17268,10 +17268,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B165" t="n">
-        <v>91825</v>
+        <v>78798</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,21 +17279,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17303,10 +17303,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R165" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17365,10 +17365,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129044893</v>
+        <v>129048297</v>
       </c>
       <c r="B166" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602729</v>
+        <v>602752</v>
       </c>
       <c r="R166" t="n">
-        <v>7018798</v>
+        <v>7018614</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,10 +17462,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129046627</v>
+        <v>129056666</v>
       </c>
       <c r="B167" t="n">
-        <v>78796</v>
+        <v>96924</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,37 +17473,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602705</v>
+        <v>602756</v>
       </c>
       <c r="R167" t="n">
-        <v>7018763</v>
+        <v>7018643</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17547,65 +17547,60 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129046592</v>
+        <v>129056678</v>
       </c>
       <c r="B168" t="n">
-        <v>57725</v>
+        <v>80050</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602704</v>
+        <v>602672</v>
       </c>
       <c r="R168" t="n">
-        <v>7018751</v>
+        <v>7018832</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17635,11 +17630,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17654,22 +17644,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129048918</v>
+        <v>129044893</v>
       </c>
       <c r="B169" t="n">
-        <v>57725</v>
+        <v>91827</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17677,39 +17667,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602737</v>
+        <v>602729</v>
       </c>
       <c r="R169" t="n">
-        <v>7018577</v>
+        <v>7018798</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17742,11 +17727,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17773,10 +17753,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056666</v>
+        <v>129046592</v>
       </c>
       <c r="B170" t="n">
-        <v>96922</v>
+        <v>57727</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17784,37 +17764,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602756</v>
+        <v>602704</v>
       </c>
       <c r="R170" t="n">
-        <v>7018643</v>
+        <v>7018751</v>
       </c>
       <c r="S170" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17844,6 +17829,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17858,60 +17848,65 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056678</v>
+        <v>129048918</v>
       </c>
       <c r="B171" t="n">
-        <v>80048</v>
+        <v>57727</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602672</v>
+        <v>602737</v>
       </c>
       <c r="R171" t="n">
-        <v>7018832</v>
+        <v>7018577</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17941,6 +17936,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,7 +6775,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129056690</v>
+        <v>129045323</v>
       </c>
       <c r="B58" t="n">
         <v>91827</v>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602758</v>
+        <v>602682</v>
       </c>
       <c r="R58" t="n">
-        <v>7018806</v>
+        <v>7018848</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,19 +6860,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056682</v>
+        <v>129056690</v>
       </c>
       <c r="B59" t="n">
         <v>91827</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602751</v>
+        <v>602758</v>
       </c>
       <c r="R59" t="n">
-        <v>7018603</v>
+        <v>7018806</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6969,48 +6969,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129045660</v>
+        <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>80050</v>
+        <v>91827</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602684</v>
+        <v>602751</v>
       </c>
       <c r="R60" t="n">
-        <v>7018786</v>
+        <v>7018603</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,44 +7054,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045323</v>
+        <v>129045660</v>
       </c>
       <c r="B61" t="n">
-        <v>91827</v>
+        <v>80050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R61" t="n">
-        <v>7018848</v>
+        <v>7018786</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7163,32 +7163,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129045225</v>
+        <v>129048001</v>
       </c>
       <c r="B62" t="n">
-        <v>97549</v>
+        <v>91997</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602705</v>
+        <v>602696</v>
       </c>
       <c r="R62" t="n">
-        <v>7018799</v>
+        <v>7018662</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129050367</v>
+        <v>129048977</v>
       </c>
       <c r="B63" t="n">
-        <v>80106</v>
+        <v>91827</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602671</v>
+        <v>602712</v>
       </c>
       <c r="R63" t="n">
-        <v>7018809</v>
+        <v>7018600</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,48 +7357,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B64" t="n">
-        <v>91827</v>
+        <v>80181</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R64" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,22 +7442,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129056720</v>
+        <v>129045225</v>
       </c>
       <c r="B65" t="n">
-        <v>80181</v>
+        <v>97549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7465,37 +7465,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602773</v>
+        <v>602705</v>
       </c>
       <c r="R65" t="n">
-        <v>7018642</v>
+        <v>7018799</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,44 +7539,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129048001</v>
+        <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>91997</v>
+        <v>80106</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R66" t="n">
-        <v>7018662</v>
+        <v>7018809</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129056680</v>
+        <v>129045343</v>
       </c>
       <c r="B67" t="n">
-        <v>91997</v>
+        <v>91953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602732</v>
+        <v>602684</v>
       </c>
       <c r="R67" t="n">
-        <v>7018811</v>
+        <v>7018837</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7719,6 +7719,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7733,12 +7738,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7939,10 +7944,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056712</v>
+        <v>129044277</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7950,37 +7955,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602730</v>
+        <v>602759</v>
       </c>
       <c r="R70" t="n">
-        <v>7018697</v>
+        <v>7018767</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8024,44 +8029,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8071,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R71" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8133,32 +8138,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129044277</v>
+        <v>129045733</v>
       </c>
       <c r="B72" t="n">
-        <v>91542</v>
+        <v>80175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8168,10 +8173,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602759</v>
+        <v>602669</v>
       </c>
       <c r="R72" t="n">
-        <v>7018767</v>
+        <v>7018781</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8230,48 +8235,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129045733</v>
+        <v>129056715</v>
       </c>
       <c r="B73" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602669</v>
+        <v>602665</v>
       </c>
       <c r="R73" t="n">
-        <v>7018781</v>
+        <v>7018777</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8315,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129045343</v>
+        <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>91953</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602684</v>
+        <v>602730</v>
       </c>
       <c r="R74" t="n">
-        <v>7018837</v>
+        <v>7018697</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8398,11 +8403,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8417,22 +8417,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129056676</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,37 +8440,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602667</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
-        <v>7018778</v>
+        <v>7018759</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,11 +8500,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8519,60 +8514,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129056718</v>
+        <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>91743</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602758</v>
+        <v>602772</v>
       </c>
       <c r="R76" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8616,19 +8611,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129056699</v>
+        <v>129045649</v>
       </c>
       <c r="B77" t="n">
         <v>80146</v>
@@ -8659,17 +8654,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602729</v>
+        <v>602688</v>
       </c>
       <c r="R77" t="n">
-        <v>7018756</v>
+        <v>7018774</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8713,44 +8708,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129044345</v>
+        <v>129049465</v>
       </c>
       <c r="B78" t="n">
-        <v>91743</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8760,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602772</v>
+        <v>602650</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018649</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8822,10 +8817,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129049465</v>
+        <v>129056718</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8833,37 +8828,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602650</v>
+        <v>602758</v>
       </c>
       <c r="R79" t="n">
-        <v>7018649</v>
+        <v>7018806</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8907,19 +8902,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129045649</v>
+        <v>129056699</v>
       </c>
       <c r="B80" t="n">
         <v>80146</v>
@@ -8950,17 +8945,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602688</v>
+        <v>602729</v>
       </c>
       <c r="R80" t="n">
-        <v>7018774</v>
+        <v>7018756</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9004,22 +8999,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129046472</v>
+        <v>129056676</v>
       </c>
       <c r="B81" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,37 +9022,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R81" t="n">
-        <v>7018759</v>
+        <v>7018779</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9087,6 +9082,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9101,19 +9101,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129056687</v>
+        <v>129045508</v>
       </c>
       <c r="B82" t="n">
         <v>91827</v>
@@ -9144,17 +9144,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602733</v>
+        <v>602674</v>
       </c>
       <c r="R82" t="n">
-        <v>7018822</v>
+        <v>7018842</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,61 +9198,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058573</v>
+        <v>129056687</v>
       </c>
       <c r="B83" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602756</v>
+        <v>602733</v>
       </c>
       <c r="R83" t="n">
-        <v>7018669</v>
+        <v>7018822</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9293,7 +9289,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9506,32 +9501,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129045508</v>
+        <v>129046057</v>
       </c>
       <c r="B86" t="n">
-        <v>91827</v>
+        <v>80106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9541,10 +9536,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602674</v>
+        <v>602648</v>
       </c>
       <c r="R86" t="n">
-        <v>7018842</v>
+        <v>7018840</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9603,48 +9598,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129046057</v>
+        <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>80106</v>
+        <v>98678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602648</v>
+        <v>602756</v>
       </c>
       <c r="R87" t="n">
-        <v>7018840</v>
+        <v>7018669</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9682,25 +9681,26 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056688</v>
+        <v>129044846</v>
       </c>
       <c r="B88" t="n">
         <v>91827</v>
@@ -9731,17 +9731,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602732</v>
+        <v>602719</v>
       </c>
       <c r="R88" t="n">
-        <v>7018811</v>
+        <v>7018813</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,19 +9785,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056686</v>
+        <v>129056688</v>
       </c>
       <c r="B89" t="n">
         <v>91827</v>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602702</v>
+        <v>602732</v>
       </c>
       <c r="R89" t="n">
-        <v>7018842</v>
+        <v>7018811</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056711</v>
+        <v>129056686</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602771</v>
+        <v>602702</v>
       </c>
       <c r="R90" t="n">
-        <v>7018641</v>
+        <v>7018842</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129044846</v>
+        <v>129056711</v>
       </c>
       <c r="B92" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602719</v>
+        <v>602771</v>
       </c>
       <c r="R92" t="n">
-        <v>7018813</v>
+        <v>7018641</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,22 +10173,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056683</v>
+        <v>129056709</v>
       </c>
       <c r="B93" t="n">
-        <v>91827</v>
+        <v>91560</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,21 +10196,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602739</v>
+        <v>602654</v>
       </c>
       <c r="R93" t="n">
-        <v>7018692</v>
+        <v>7018820</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10282,10 +10282,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B94" t="n">
-        <v>91560</v>
+        <v>91827</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,21 +10293,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R94" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10379,7 +10379,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B95" t="n">
         <v>80146</v>
@@ -10410,17 +10410,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R95" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10464,12 +10464,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10604,17 +10604,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R97" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,12 +10658,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11075,10 +11075,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129056684</v>
+        <v>129045453</v>
       </c>
       <c r="B102" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11086,37 +11086,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602651</v>
+        <v>602673</v>
       </c>
       <c r="R102" t="n">
-        <v>7018826</v>
+        <v>7018844</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11160,22 +11160,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129056671</v>
+        <v>129044824</v>
       </c>
       <c r="B103" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11183,37 +11183,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602735</v>
+        <v>602731</v>
       </c>
       <c r="R103" t="n">
-        <v>7018592</v>
+        <v>7018789</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11257,58 +11257,54 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129050244</v>
+        <v>129044805</v>
       </c>
       <c r="B104" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602665</v>
+        <v>602747</v>
       </c>
       <c r="R104" t="n">
         <v>7018784</v>
@@ -11370,10 +11366,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045681</v>
+        <v>129056684</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>91827</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11381,37 +11377,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602667</v>
+        <v>602651</v>
       </c>
       <c r="R105" t="n">
-        <v>7018778</v>
+        <v>7018826</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11455,22 +11451,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056697</v>
+        <v>129056671</v>
       </c>
       <c r="B106" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11478,21 +11474,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11502,10 +11498,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602730</v>
+        <v>602735</v>
       </c>
       <c r="R106" t="n">
-        <v>7018719</v>
+        <v>7018592</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11564,7 +11560,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056693</v>
+        <v>129045681</v>
       </c>
       <c r="B107" t="n">
         <v>80146</v>
@@ -11595,17 +11591,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602670</v>
+        <v>602667</v>
       </c>
       <c r="R107" t="n">
-        <v>7018818</v>
+        <v>7018779</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11635,11 +11631,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11654,22 +11645,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129045453</v>
+        <v>129045582</v>
       </c>
       <c r="B108" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11677,21 +11668,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11701,10 +11692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602673</v>
+        <v>602703</v>
       </c>
       <c r="R108" t="n">
-        <v>7018844</v>
+        <v>7018798</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11763,10 +11754,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129044824</v>
+        <v>129056693</v>
       </c>
       <c r="B109" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,37 +11765,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602731</v>
+        <v>602670</v>
       </c>
       <c r="R109" t="n">
-        <v>7018789</v>
+        <v>7018818</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11834,6 +11825,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11848,22 +11844,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044805</v>
+        <v>129056697</v>
       </c>
       <c r="B110" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11871,37 +11867,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602747</v>
+        <v>602730</v>
       </c>
       <c r="R110" t="n">
-        <v>7018784</v>
+        <v>7018719</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11945,57 +11941,61 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129045582</v>
+        <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602703</v>
+        <v>602665</v>
       </c>
       <c r="R111" t="n">
-        <v>7018798</v>
+        <v>7018784</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12365,32 +12365,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129046525</v>
+        <v>129044298</v>
       </c>
       <c r="B115" t="n">
-        <v>91506</v>
+        <v>91997</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12400,10 +12400,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602669</v>
+        <v>602760</v>
       </c>
       <c r="R115" t="n">
-        <v>7018753</v>
+        <v>7018767</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12462,32 +12462,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129044298</v>
+        <v>129046525</v>
       </c>
       <c r="B116" t="n">
-        <v>91997</v>
+        <v>91506</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12497,10 +12497,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602760</v>
+        <v>602669</v>
       </c>
       <c r="R116" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12854,48 +12854,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056704</v>
+        <v>129044475</v>
       </c>
       <c r="B120" t="n">
-        <v>98678</v>
+        <v>91560</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602735</v>
+        <v>602766</v>
       </c>
       <c r="R120" t="n">
-        <v>7018692</v>
+        <v>7018781</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12925,11 +12925,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12944,12 +12939,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13063,48 +13058,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129044475</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>91560</v>
+        <v>98678</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602766</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018781</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13134,6 +13129,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13148,60 +13148,64 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129056689</v>
+        <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602754</v>
+        <v>602747</v>
       </c>
       <c r="R123" t="n">
-        <v>7018806</v>
+        <v>7018722</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13245,44 +13249,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056668</v>
+        <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>91506</v>
+        <v>91827</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13292,10 +13296,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602738</v>
+        <v>602754</v>
       </c>
       <c r="R124" t="n">
-        <v>7018795</v>
+        <v>7018806</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13354,10 +13358,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129050404</v>
+        <v>129044962</v>
       </c>
       <c r="B125" t="n">
-        <v>80175</v>
+        <v>91506</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13365,21 +13369,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13389,10 +13393,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602672</v>
+        <v>602750</v>
       </c>
       <c r="R125" t="n">
-        <v>7018808</v>
+        <v>7018799</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13548,10 +13552,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129044962</v>
+        <v>129050404</v>
       </c>
       <c r="B127" t="n">
-        <v>91506</v>
+        <v>80175</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13559,21 +13563,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13583,10 +13587,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602750</v>
+        <v>602672</v>
       </c>
       <c r="R127" t="n">
-        <v>7018799</v>
+        <v>7018808</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -13645,52 +13649,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129046716</v>
+        <v>129056668</v>
       </c>
       <c r="B128" t="n">
-        <v>98678</v>
+        <v>91506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602747</v>
+        <v>602738</v>
       </c>
       <c r="R128" t="n">
-        <v>7018722</v>
+        <v>7018795</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,19 +13734,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129050334</v>
+        <v>129045554</v>
       </c>
       <c r="B129" t="n">
         <v>80146</v>
@@ -13781,10 +13781,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R129" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -13843,32 +13843,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B130" t="n">
-        <v>80106</v>
+        <v>80146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R130" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13940,32 +13940,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129045554</v>
+        <v>129045756</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602696</v>
+        <v>602663</v>
       </c>
       <c r="R131" t="n">
         <v>7018818</v>
@@ -14037,48 +14037,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045512</v>
+        <v>129056675</v>
       </c>
       <c r="B132" t="n">
-        <v>91542</v>
+        <v>92242</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602682</v>
+        <v>602672</v>
       </c>
       <c r="R132" t="n">
-        <v>7018827</v>
+        <v>7018832</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14122,44 +14122,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056675</v>
+        <v>129056667</v>
       </c>
       <c r="B133" t="n">
-        <v>92242</v>
+        <v>96924</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14172,7 +14172,7 @@
         <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018832</v>
+        <v>7018807</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14231,10 +14231,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129056694</v>
+        <v>129056692</v>
       </c>
       <c r="B134" t="n">
-        <v>80146</v>
+        <v>10964</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,21 +14242,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14266,10 +14261,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602656</v>
+        <v>602687</v>
       </c>
       <c r="R134" t="n">
-        <v>7018656</v>
+        <v>7018836</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14328,10 +14323,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129056667</v>
+        <v>129045677</v>
       </c>
       <c r="B135" t="n">
-        <v>96924</v>
+        <v>91542</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14339,37 +14334,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R135" t="n">
-        <v>7018807</v>
+        <v>7018786</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14413,22 +14408,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056692</v>
+        <v>129045512</v>
       </c>
       <c r="B136" t="n">
-        <v>10964</v>
+        <v>91542</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14436,32 +14431,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602687</v>
+        <v>602682</v>
       </c>
       <c r="R136" t="n">
-        <v>7018836</v>
+        <v>7018827</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129045677</v>
+        <v>129056694</v>
       </c>
       <c r="B139" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14722,37 +14722,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602684</v>
+        <v>602656</v>
       </c>
       <c r="R139" t="n">
-        <v>7018786</v>
+        <v>7018656</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14796,12 +14796,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -14909,32 +14909,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B141" t="n">
-        <v>80146</v>
+        <v>91997</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14944,10 +14944,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R141" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15006,10 +15006,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129046813</v>
+        <v>129056695</v>
       </c>
       <c r="B142" t="n">
-        <v>91099</v>
+        <v>80146</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15017,37 +15017,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602732</v>
+        <v>602754</v>
       </c>
       <c r="R142" t="n">
-        <v>7018701</v>
+        <v>7018633</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15091,22 +15091,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15114,42 +15114,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R143" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15179,11 +15174,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15198,44 +15188,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056679</v>
+        <v>129056705</v>
       </c>
       <c r="B144" t="n">
-        <v>91997</v>
+        <v>56908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15245,10 +15235,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602737</v>
+        <v>602730</v>
       </c>
       <c r="R144" t="n">
-        <v>7018593</v>
+        <v>7018719</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15281,6 +15271,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15307,10 +15302,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056696</v>
+        <v>129046813</v>
       </c>
       <c r="B145" t="n">
-        <v>80146</v>
+        <v>91099</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15318,37 +15313,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602779</v>
+        <v>602732</v>
       </c>
       <c r="R145" t="n">
-        <v>7018639</v>
+        <v>7018701</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15392,22 +15387,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056705</v>
+        <v>129048944</v>
       </c>
       <c r="B146" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15415,16 +15410,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15433,19 +15428,24 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602730</v>
+        <v>602734</v>
       </c>
       <c r="R146" t="n">
-        <v>7018719</v>
+        <v>7018579</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färsk spillning</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15494,12 +15494,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15805,48 +15805,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129044697</v>
+        <v>129056716</v>
       </c>
       <c r="B150" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602730</v>
+        <v>602754</v>
       </c>
       <c r="R150" t="n">
-        <v>7018771</v>
+        <v>7018801</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15890,60 +15890,60 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129056716</v>
+        <v>129044697</v>
       </c>
       <c r="B151" t="n">
-        <v>79041</v>
+        <v>80106</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602754</v>
+        <v>602730</v>
       </c>
       <c r="R151" t="n">
-        <v>7018801</v>
+        <v>7018771</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15987,22 +15987,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129046382</v>
+        <v>129046543</v>
       </c>
       <c r="B152" t="n">
-        <v>91827</v>
+        <v>90571</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16010,21 +16010,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602637</v>
+        <v>602686</v>
       </c>
       <c r="R152" t="n">
-        <v>7018802</v>
+        <v>7018745</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B153" t="n">
-        <v>90571</v>
+        <v>91827</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16107,21 +16107,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16131,10 +16131,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R153" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16193,10 +16193,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129045378</v>
+        <v>129050391</v>
       </c>
       <c r="B154" t="n">
-        <v>92242</v>
+        <v>80050</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16204,21 +16204,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602682</v>
+        <v>602671</v>
       </c>
       <c r="R154" t="n">
-        <v>7018833</v>
+        <v>7018809</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,43 +16290,52 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129056691</v>
+        <v>129048151</v>
       </c>
       <c r="B155" t="n">
-        <v>10964</v>
+        <v>98678</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602659</v>
+        <v>602715</v>
       </c>
       <c r="R155" t="n">
-        <v>7018825</v>
+        <v>7018634</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16370,60 +16379,60 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129056714</v>
+        <v>129045378</v>
       </c>
       <c r="B156" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602678</v>
+        <v>602682</v>
       </c>
       <c r="R156" t="n">
-        <v>7018771</v>
+        <v>7018833</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16467,44 +16476,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129050391</v>
+        <v>129044275</v>
       </c>
       <c r="B157" t="n">
-        <v>80050</v>
+        <v>91827</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16514,10 +16523,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602671</v>
+        <v>602766</v>
       </c>
       <c r="R157" t="n">
-        <v>7018809</v>
+        <v>7018767</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16576,10 +16585,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129044275</v>
+        <v>129056714</v>
       </c>
       <c r="B158" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16587,37 +16596,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602766</v>
+        <v>602678</v>
       </c>
       <c r="R158" t="n">
-        <v>7018767</v>
+        <v>7018771</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16661,64 +16670,55 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129048151</v>
+        <v>129056691</v>
       </c>
       <c r="B159" t="n">
-        <v>98678</v>
+        <v>10964</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602715</v>
+        <v>602659</v>
       </c>
       <c r="R159" t="n">
-        <v>7018634</v>
+        <v>7018825</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16762,57 +16762,61 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129045867</v>
+        <v>129044553</v>
       </c>
       <c r="B160" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602663</v>
+        <v>602758</v>
       </c>
       <c r="R160" t="n">
-        <v>7018805</v>
+        <v>7018769</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16871,49 +16875,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B161" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R161" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16972,10 +16972,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129047010</v>
+        <v>129056685</v>
       </c>
       <c r="B162" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16983,37 +16983,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602728</v>
+        <v>602683</v>
       </c>
       <c r="R162" t="n">
-        <v>7018716</v>
+        <v>7018835</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17057,12 +17057,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129056685</v>
+        <v>129045867</v>
       </c>
       <c r="B164" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17182,37 +17182,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602683</v>
+        <v>602663</v>
       </c>
       <c r="R164" t="n">
-        <v>7018835</v>
+        <v>7018805</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17256,22 +17256,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129046627</v>
+        <v>129056666</v>
       </c>
       <c r="B165" t="n">
-        <v>78798</v>
+        <v>96924</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17279,37 +17279,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602705</v>
+        <v>602756</v>
       </c>
       <c r="R165" t="n">
-        <v>7018763</v>
+        <v>7018643</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17353,22 +17353,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B166" t="n">
-        <v>91827</v>
+        <v>78798</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R166" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,32 +17462,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129056666</v>
+        <v>129056678</v>
       </c>
       <c r="B167" t="n">
-        <v>96924</v>
+        <v>80050</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R167" t="n">
-        <v>7018643</v>
+        <v>7018832</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17559,48 +17559,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129056678</v>
+        <v>129048297</v>
       </c>
       <c r="B168" t="n">
-        <v>80050</v>
+        <v>91827</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602672</v>
+        <v>602752</v>
       </c>
       <c r="R168" t="n">
-        <v>7018832</v>
+        <v>7018614</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17644,12 +17644,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -8429,32 +8429,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129044345</v>
       </c>
       <c r="B75" t="n">
-        <v>91827</v>
+        <v>91743</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602772</v>
       </c>
       <c r="R75" t="n">
         <v>7018759</v>
@@ -8526,32 +8526,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129044345</v>
+        <v>129045649</v>
       </c>
       <c r="B76" t="n">
-        <v>91743</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602772</v>
+        <v>602688</v>
       </c>
       <c r="R76" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129045649</v>
+        <v>129049465</v>
       </c>
       <c r="B77" t="n">
         <v>80146</v>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602688</v>
+        <v>602650</v>
       </c>
       <c r="R77" t="n">
-        <v>7018774</v>
+        <v>7018649</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8720,10 +8720,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129049465</v>
+        <v>129056718</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8731,37 +8731,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602650</v>
+        <v>602758</v>
       </c>
       <c r="R78" t="n">
-        <v>7018649</v>
+        <v>7018806</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056718</v>
+        <v>129056699</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602758</v>
+        <v>602729</v>
       </c>
       <c r="R79" t="n">
-        <v>7018806</v>
+        <v>7018756</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056699</v>
+        <v>129046472</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>91827</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8925,37 +8925,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602729</v>
+        <v>602666</v>
       </c>
       <c r="R80" t="n">
-        <v>7018756</v>
+        <v>7018759</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,12 +8999,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10379,7 +10379,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B95" t="n">
         <v>80146</v>
@@ -10410,17 +10410,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R95" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10464,19 +10464,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129046062</v>
+        <v>129048547</v>
       </c>
       <c r="B96" t="n">
         <v>80146</v>
@@ -10511,10 +10511,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602648</v>
+        <v>602747</v>
       </c>
       <c r="R96" t="n">
-        <v>7018840</v>
+        <v>7018592</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10573,7 +10573,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056698</v>
+        <v>129046062</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10604,17 +10604,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602735</v>
+        <v>602648</v>
       </c>
       <c r="R97" t="n">
-        <v>7018716</v>
+        <v>7018840</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,12 +10658,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B118" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,21 +12671,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12695,10 +12695,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R118" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12757,10 +12757,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056702</v>
+        <v>129050601</v>
       </c>
       <c r="B119" t="n">
-        <v>80146</v>
+        <v>10964</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,37 +12768,41 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602649</v>
+        <v>602698</v>
       </c>
       <c r="R119" t="n">
-        <v>7018829</v>
+        <v>7018836</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12830,34 +12834,40 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129044475</v>
+        <v>129056681</v>
       </c>
       <c r="B120" t="n">
-        <v>91560</v>
+        <v>91827</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12865,37 +12875,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602766</v>
+        <v>602736</v>
       </c>
       <c r="R120" t="n">
-        <v>7018781</v>
+        <v>7018593</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12939,22 +12949,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129050601</v>
+        <v>129044475</v>
       </c>
       <c r="B121" t="n">
-        <v>10964</v>
+        <v>91560</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12962,38 +12972,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>101449</v>
+        <v>5432</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602698</v>
+        <v>602766</v>
       </c>
       <c r="R121" t="n">
-        <v>7018836</v>
+        <v>7018781</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13028,18 +13034,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14037,32 +14037,27 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129056675</v>
+        <v>129056692</v>
       </c>
       <c r="B132" t="n">
-        <v>92242</v>
+        <v>10964</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14072,10 +14067,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602672</v>
+        <v>602687</v>
       </c>
       <c r="R132" t="n">
-        <v>7018832</v>
+        <v>7018836</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14134,10 +14129,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129056667</v>
+        <v>129045677</v>
       </c>
       <c r="B133" t="n">
-        <v>96924</v>
+        <v>91542</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14145,37 +14140,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R133" t="n">
-        <v>7018807</v>
+        <v>7018786</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14219,22 +14214,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129056692</v>
+        <v>129045512</v>
       </c>
       <c r="B134" t="n">
-        <v>10964</v>
+        <v>91542</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14242,32 +14237,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602687</v>
+        <v>602682</v>
       </c>
       <c r="R134" t="n">
-        <v>7018836</v>
+        <v>7018827</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14311,22 +14311,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129045677</v>
+        <v>129046455</v>
       </c>
       <c r="B135" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602684</v>
+        <v>602667</v>
       </c>
       <c r="R135" t="n">
-        <v>7018786</v>
+        <v>7018757</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14420,10 +14420,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129045512</v>
+        <v>129044406</v>
       </c>
       <c r="B136" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14431,21 +14431,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602682</v>
+        <v>602756</v>
       </c>
       <c r="R136" t="n">
-        <v>7018827</v>
+        <v>7018769</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14517,48 +14517,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129046455</v>
+        <v>129056675</v>
       </c>
       <c r="B137" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602667</v>
+        <v>602672</v>
       </c>
       <c r="R137" t="n">
-        <v>7018757</v>
+        <v>7018832</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14602,22 +14602,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129044406</v>
+        <v>129056667</v>
       </c>
       <c r="B138" t="n">
-        <v>80146</v>
+        <v>96924</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14625,37 +14625,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R138" t="n">
-        <v>7018769</v>
+        <v>7018807</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14699,12 +14699,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14909,48 +14909,48 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129056679</v>
+        <v>129046813</v>
       </c>
       <c r="B141" t="n">
-        <v>91997</v>
+        <v>91099</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1209</v>
+        <v>937</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602737</v>
+        <v>602732</v>
       </c>
       <c r="R141" t="n">
-        <v>7018593</v>
+        <v>7018701</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14994,12 +14994,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15200,10 +15200,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056705</v>
+        <v>129048944</v>
       </c>
       <c r="B144" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15211,16 +15211,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15229,19 +15229,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602730</v>
+        <v>602734</v>
       </c>
       <c r="R144" t="n">
-        <v>7018719</v>
+        <v>7018579</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15275,7 +15280,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Färsk spillning</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15290,60 +15295,60 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129046813</v>
+        <v>129056679</v>
       </c>
       <c r="B145" t="n">
-        <v>91099</v>
+        <v>91997</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>937</v>
+        <v>1209</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602732</v>
+        <v>602737</v>
       </c>
       <c r="R145" t="n">
-        <v>7018701</v>
+        <v>7018593</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15387,22 +15392,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129048944</v>
+        <v>129056705</v>
       </c>
       <c r="B146" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15410,16 +15415,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15428,24 +15433,19 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602734</v>
+        <v>602730</v>
       </c>
       <c r="R146" t="n">
-        <v>7018579</v>
+        <v>7018719</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15494,57 +15494,61 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129048489</v>
+        <v>129045069</v>
       </c>
       <c r="B147" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602748</v>
+        <v>602751</v>
       </c>
       <c r="R147" t="n">
-        <v>7018591</v>
+        <v>7018815</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15603,7 +15607,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B148" t="n">
         <v>98678</v>
@@ -15642,10 +15646,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R148" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15704,49 +15708,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129046445</v>
+        <v>129048489</v>
       </c>
       <c r="B149" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602669</v>
+        <v>602748</v>
       </c>
       <c r="R149" t="n">
-        <v>7018754</v>
+        <v>7018591</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,48 +15805,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129056716</v>
+        <v>129044697</v>
       </c>
       <c r="B150" t="n">
-        <v>79041</v>
+        <v>80106</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602754</v>
+        <v>602730</v>
       </c>
       <c r="R150" t="n">
-        <v>7018801</v>
+        <v>7018771</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15890,60 +15890,60 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129044697</v>
+        <v>129056716</v>
       </c>
       <c r="B151" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602730</v>
+        <v>602754</v>
       </c>
       <c r="R151" t="n">
-        <v>7018771</v>
+        <v>7018801</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15987,12 +15987,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,48 +6872,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056690</v>
+        <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>91827</v>
+        <v>80050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602758</v>
+        <v>602684</v>
       </c>
       <c r="R59" t="n">
-        <v>7018806</v>
+        <v>7018786</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,22 +6957,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056682</v>
+        <v>129056690</v>
       </c>
       <c r="B60" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602751</v>
+        <v>602758</v>
       </c>
       <c r="R60" t="n">
-        <v>7018603</v>
+        <v>7018806</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,48 +7066,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045660</v>
+        <v>129056682</v>
       </c>
       <c r="B61" t="n">
-        <v>80050</v>
+        <v>91837</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602684</v>
+        <v>602751</v>
       </c>
       <c r="R61" t="n">
-        <v>7018786</v>
+        <v>7018603</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,12 +7151,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7166,7 +7166,7 @@
         <v>129048001</v>
       </c>
       <c r="B62" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048977</v>
+        <v>129045225</v>
       </c>
       <c r="B63" t="n">
-        <v>91827</v>
+        <v>97575</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602712</v>
+        <v>602705</v>
       </c>
       <c r="R63" t="n">
-        <v>7018600</v>
+        <v>7018799</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7454,32 +7454,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B65" t="n">
-        <v>97549</v>
+        <v>91837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R65" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045343</v>
+        <v>129056680</v>
       </c>
       <c r="B67" t="n">
-        <v>91953</v>
+        <v>91992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4217</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602684</v>
+        <v>602732</v>
       </c>
       <c r="R67" t="n">
-        <v>7018837</v>
+        <v>7018811</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7719,11 +7719,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7738,12 +7733,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7753,7 +7748,7 @@
         <v>129056672</v>
       </c>
       <c r="B68" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7850,7 +7845,7 @@
         <v>129050732</v>
       </c>
       <c r="B69" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7944,10 +7939,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129044277</v>
+        <v>129056715</v>
       </c>
       <c r="B70" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7955,37 +7950,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602759</v>
+        <v>602665</v>
       </c>
       <c r="R70" t="n">
-        <v>7018767</v>
+        <v>7018777</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8029,44 +8024,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056680</v>
+        <v>129056712</v>
       </c>
       <c r="B71" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8071,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602732</v>
+        <v>602730</v>
       </c>
       <c r="R71" t="n">
-        <v>7018811</v>
+        <v>7018697</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,32 +8133,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129045733</v>
+        <v>129044277</v>
       </c>
       <c r="B72" t="n">
-        <v>80175</v>
+        <v>91540</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8173,10 +8168,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602669</v>
+        <v>602759</v>
       </c>
       <c r="R72" t="n">
-        <v>7018781</v>
+        <v>7018767</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8235,48 +8230,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056715</v>
+        <v>129045343</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>91962</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602665</v>
+        <v>602684</v>
       </c>
       <c r="R73" t="n">
-        <v>7018777</v>
+        <v>7018837</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8306,6 +8301,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8320,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056712</v>
+        <v>129045733</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602730</v>
+        <v>602669</v>
       </c>
       <c r="R74" t="n">
-        <v>7018697</v>
+        <v>7018781</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,44 +8417,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129044345</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>91743</v>
+        <v>91837</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602772</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
         <v>7018759</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129045649</v>
+        <v>129049465</v>
       </c>
       <c r="B76" t="n">
         <v>80146</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602688</v>
+        <v>602650</v>
       </c>
       <c r="R76" t="n">
-        <v>7018774</v>
+        <v>7018649</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129049465</v>
+        <v>129045649</v>
       </c>
       <c r="B77" t="n">
         <v>80146</v>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602650</v>
+        <v>602688</v>
       </c>
       <c r="R77" t="n">
-        <v>7018649</v>
+        <v>7018774</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129046472</v>
+        <v>129044345</v>
       </c>
       <c r="B80" t="n">
-        <v>91827</v>
+        <v>91752</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602666</v>
+        <v>602772</v>
       </c>
       <c r="R80" t="n">
         <v>7018759</v>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129045508</v>
+        <v>129048233</v>
       </c>
       <c r="B82" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602674</v>
+        <v>602744</v>
       </c>
       <c r="R82" t="n">
-        <v>7018842</v>
+        <v>7018615</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9210,48 +9210,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129056687</v>
+        <v>129046057</v>
       </c>
       <c r="B83" t="n">
-        <v>91827</v>
+        <v>80106</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602733</v>
+        <v>602648</v>
       </c>
       <c r="R83" t="n">
-        <v>7018822</v>
+        <v>7018840</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9295,22 +9295,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048233</v>
+        <v>129056687</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>91837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,37 +9318,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602744</v>
+        <v>602733</v>
       </c>
       <c r="R84" t="n">
-        <v>7018615</v>
+        <v>7018822</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9392,22 +9392,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129048100</v>
+        <v>129045508</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9415,21 +9415,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602670</v>
+        <v>602674</v>
       </c>
       <c r="R85" t="n">
-        <v>7018643</v>
+        <v>7018842</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,32 +9501,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129046057</v>
+        <v>129048100</v>
       </c>
       <c r="B86" t="n">
-        <v>80106</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602648</v>
+        <v>602670</v>
       </c>
       <c r="R86" t="n">
-        <v>7018840</v>
+        <v>7018643</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9601,7 +9601,7 @@
         <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129044846</v>
+        <v>129056711</v>
       </c>
       <c r="B88" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,37 +9711,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602719</v>
+        <v>602771</v>
       </c>
       <c r="R88" t="n">
-        <v>7018813</v>
+        <v>7018641</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,12 +9785,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
         <v>129056688</v>
       </c>
       <c r="B89" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>129056686</v>
       </c>
       <c r="B90" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129048130</v>
+        <v>129044846</v>
       </c>
       <c r="B91" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,21 +10002,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602704</v>
+        <v>602719</v>
       </c>
       <c r="R91" t="n">
-        <v>7018634</v>
+        <v>7018813</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R92" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,22 +10173,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R93" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10270,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056683</v>
+        <v>129048547</v>
       </c>
       <c r="B94" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10293,37 +10293,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602739</v>
+        <v>602747</v>
       </c>
       <c r="R94" t="n">
-        <v>7018692</v>
+        <v>7018592</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056698</v>
+        <v>129056709</v>
       </c>
       <c r="B95" t="n">
-        <v>80146</v>
+        <v>91558</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602735</v>
+        <v>602654</v>
       </c>
       <c r="R95" t="n">
-        <v>7018716</v>
+        <v>7018820</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B96" t="n">
         <v>80146</v>
@@ -10507,17 +10507,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R96" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10561,22 +10561,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129046062</v>
+        <v>129056683</v>
       </c>
       <c r="B97" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10584,37 +10584,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602648</v>
+        <v>602739</v>
       </c>
       <c r="R97" t="n">
-        <v>7018840</v>
+        <v>7018692</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10658,63 +10658,64 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058560</v>
+        <v>129045623</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602760</v>
+        <v>602687</v>
       </c>
       <c r="R98" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10752,26 +10753,25 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129056713</v>
+        <v>129058560</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10800,16 +10800,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602690</v>
+        <v>602760</v>
       </c>
       <c r="R99" t="n">
-        <v>7018768</v>
+        <v>7018673</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10850,6 +10853,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10868,51 +10872,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129046720</v>
+        <v>129056713</v>
       </c>
       <c r="B100" t="n">
-        <v>92167</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602747</v>
+        <v>602690</v>
       </c>
       <c r="R100" t="n">
-        <v>7018721</v>
+        <v>7018768</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10944,40 +10945,34 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B101" t="n">
-        <v>98678</v>
+        <v>92182</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10985,38 +10980,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R101" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11051,12 +11045,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11075,45 +11075,49 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045453</v>
+        <v>129050244</v>
       </c>
       <c r="B102" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602673</v>
+        <v>602665</v>
       </c>
       <c r="R102" t="n">
-        <v>7018844</v>
+        <v>7018784</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11172,10 +11176,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044824</v>
+        <v>129045681</v>
       </c>
       <c r="B103" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11183,21 +11187,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11207,10 +11211,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602731</v>
+        <v>602667</v>
       </c>
       <c r="R103" t="n">
-        <v>7018789</v>
+        <v>7018779</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11269,10 +11273,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044805</v>
+        <v>129045582</v>
       </c>
       <c r="B104" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11280,21 +11284,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11304,10 +11308,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602747</v>
+        <v>602703</v>
       </c>
       <c r="R104" t="n">
-        <v>7018784</v>
+        <v>7018798</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11366,10 +11370,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129056684</v>
+        <v>129045453</v>
       </c>
       <c r="B105" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11377,37 +11381,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602651</v>
+        <v>602673</v>
       </c>
       <c r="R105" t="n">
-        <v>7018826</v>
+        <v>7018844</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11451,22 +11455,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056671</v>
+        <v>129044824</v>
       </c>
       <c r="B106" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11474,37 +11478,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602735</v>
+        <v>602731</v>
       </c>
       <c r="R106" t="n">
-        <v>7018592</v>
+        <v>7018789</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11548,22 +11552,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129045681</v>
+        <v>129044805</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11571,21 +11575,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11595,10 +11599,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602667</v>
+        <v>602747</v>
       </c>
       <c r="R107" t="n">
-        <v>7018779</v>
+        <v>7018784</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11657,10 +11661,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129045582</v>
+        <v>129056684</v>
       </c>
       <c r="B108" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11668,37 +11672,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602703</v>
+        <v>602651</v>
       </c>
       <c r="R108" t="n">
-        <v>7018798</v>
+        <v>7018826</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11742,22 +11746,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056693</v>
+        <v>129056671</v>
       </c>
       <c r="B109" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11765,21 +11769,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11789,10 +11793,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602670</v>
+        <v>602735</v>
       </c>
       <c r="R109" t="n">
-        <v>7018818</v>
+        <v>7018592</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11825,11 +11829,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11856,7 +11855,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056697</v>
+        <v>129056693</v>
       </c>
       <c r="B110" t="n">
         <v>80146</v>
@@ -11891,10 +11890,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602730</v>
+        <v>602670</v>
       </c>
       <c r="R110" t="n">
-        <v>7018719</v>
+        <v>7018818</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11927,6 +11926,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11953,52 +11957,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129050244</v>
+        <v>129056697</v>
       </c>
       <c r="B111" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602665</v>
+        <v>602730</v>
       </c>
       <c r="R111" t="n">
-        <v>7018784</v>
+        <v>7018719</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,22 +12042,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129056708</v>
+        <v>129046367</v>
       </c>
       <c r="B112" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12065,37 +12065,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602663</v>
+        <v>602644</v>
       </c>
       <c r="R112" t="n">
-        <v>7018823</v>
+        <v>7018800</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12125,6 +12130,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12139,62 +12149,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129044230</v>
+        <v>129044298</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>91992</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602777</v>
+        <v>602760</v>
       </c>
       <c r="R113" t="n">
-        <v>7018753</v>
+        <v>7018767</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12227,11 +12232,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12258,50 +12258,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129046367</v>
+        <v>129046525</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602644</v>
+        <v>602669</v>
       </c>
       <c r="R114" t="n">
-        <v>7018800</v>
+        <v>7018753</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12334,11 +12329,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12365,45 +12355,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129044298</v>
+        <v>129044230</v>
       </c>
       <c r="B115" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602760</v>
+        <v>602777</v>
       </c>
       <c r="R115" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12436,6 +12431,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12462,48 +12462,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129046525</v>
+        <v>129056708</v>
       </c>
       <c r="B116" t="n">
-        <v>91506</v>
+        <v>91558</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602669</v>
+        <v>602663</v>
       </c>
       <c r="R116" t="n">
-        <v>7018753</v>
+        <v>7018823</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12547,12 +12547,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12562,7 +12562,7 @@
         <v>129044719</v>
       </c>
       <c r="B117" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129056702</v>
+        <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>80146</v>
+        <v>91558</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12671,37 +12671,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602649</v>
+        <v>602766</v>
       </c>
       <c r="R118" t="n">
-        <v>7018829</v>
+        <v>7018781</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12745,22 +12745,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129050601</v>
+        <v>129056702</v>
       </c>
       <c r="B119" t="n">
-        <v>10964</v>
+        <v>80146</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,41 +12768,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602698</v>
+        <v>602649</v>
       </c>
       <c r="R119" t="n">
-        <v>7018836</v>
+        <v>7018829</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12834,30 +12830,24 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12867,7 +12857,7 @@
         <v>129056681</v>
       </c>
       <c r="B120" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12961,10 +12951,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129044475</v>
+        <v>129050601</v>
       </c>
       <c r="B121" t="n">
-        <v>91560</v>
+        <v>10964</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12972,34 +12962,38 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602766</v>
+        <v>602698</v>
       </c>
       <c r="R121" t="n">
-        <v>7018781</v>
+        <v>7018836</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13034,12 +13028,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
         <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13358,10 +13358,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129044962</v>
+        <v>129056668</v>
       </c>
       <c r="B125" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13389,17 +13389,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602750</v>
+        <v>602738</v>
       </c>
       <c r="R125" t="n">
-        <v>7018799</v>
+        <v>7018795</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13443,60 +13443,60 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056700</v>
+        <v>129044962</v>
       </c>
       <c r="B126" t="n">
-        <v>80146</v>
+        <v>91504</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602684</v>
+        <v>602750</v>
       </c>
       <c r="R126" t="n">
-        <v>7018776</v>
+        <v>7018799</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13540,60 +13540,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129050404</v>
+        <v>129056700</v>
       </c>
       <c r="B127" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602672</v>
+        <v>602684</v>
       </c>
       <c r="R127" t="n">
-        <v>7018808</v>
+        <v>7018776</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13637,22 +13637,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056668</v>
+        <v>129050404</v>
       </c>
       <c r="B128" t="n">
-        <v>91506</v>
+        <v>80175</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13660,37 +13660,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602738</v>
+        <v>602672</v>
       </c>
       <c r="R128" t="n">
-        <v>7018795</v>
+        <v>7018808</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13734,12 +13734,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129056692</v>
+        <v>129045512</v>
       </c>
       <c r="B132" t="n">
-        <v>10964</v>
+        <v>91540</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14048,32 +14048,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602687</v>
+        <v>602682</v>
       </c>
       <c r="R132" t="n">
-        <v>7018836</v>
+        <v>7018827</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14117,12 +14122,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14132,7 +14137,7 @@
         <v>129045677</v>
       </c>
       <c r="B133" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14226,10 +14231,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129045512</v>
+        <v>129056667</v>
       </c>
       <c r="B134" t="n">
-        <v>91542</v>
+        <v>96950</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14237,37 +14242,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602682</v>
+        <v>602672</v>
       </c>
       <c r="R134" t="n">
-        <v>7018827</v>
+        <v>7018807</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14311,60 +14316,60 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129046455</v>
+        <v>129056675</v>
       </c>
       <c r="B135" t="n">
-        <v>79041</v>
+        <v>92257</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602667</v>
+        <v>602672</v>
       </c>
       <c r="R135" t="n">
-        <v>7018757</v>
+        <v>7018832</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14408,19 +14413,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129044406</v>
+        <v>129056694</v>
       </c>
       <c r="B136" t="n">
         <v>80146</v>
@@ -14451,17 +14456,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602756</v>
+        <v>602656</v>
       </c>
       <c r="R136" t="n">
-        <v>7018769</v>
+        <v>7018656</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14505,60 +14510,60 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056675</v>
+        <v>129046455</v>
       </c>
       <c r="B137" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602672</v>
+        <v>602667</v>
       </c>
       <c r="R137" t="n">
-        <v>7018832</v>
+        <v>7018757</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14602,22 +14607,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056667</v>
+        <v>129044406</v>
       </c>
       <c r="B138" t="n">
-        <v>96924</v>
+        <v>80146</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14625,37 +14630,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R138" t="n">
-        <v>7018807</v>
+        <v>7018769</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14699,60 +14704,64 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056694</v>
+        <v>129046891</v>
       </c>
       <c r="B139" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602656</v>
+        <v>602726</v>
       </c>
       <c r="R139" t="n">
-        <v>7018656</v>
+        <v>7018723</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14796,64 +14805,55 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129046891</v>
+        <v>129056692</v>
       </c>
       <c r="B140" t="n">
-        <v>98678</v>
+        <v>10964</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602726</v>
+        <v>602687</v>
       </c>
       <c r="R140" t="n">
-        <v>7018723</v>
+        <v>7018836</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -14912,7 +14912,7 @@
         <v>129046813</v>
       </c>
       <c r="B141" t="n">
-        <v>91099</v>
+        <v>91100</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15006,32 +15006,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B142" t="n">
-        <v>80146</v>
+        <v>91992</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R142" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15103,7 +15103,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B143" t="n">
         <v>80146</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R143" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15200,10 +15200,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B144" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15211,42 +15211,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R144" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15276,11 +15271,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15295,60 +15285,65 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056679</v>
+        <v>129048944</v>
       </c>
       <c r="B145" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602737</v>
+        <v>602734</v>
       </c>
       <c r="R145" t="n">
-        <v>7018593</v>
+        <v>7018579</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15378,6 +15373,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15392,12 +15392,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15506,49 +15506,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129045069</v>
+        <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602751</v>
+        <v>602748</v>
       </c>
       <c r="R147" t="n">
-        <v>7018815</v>
+        <v>7018591</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15607,10 +15603,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15646,10 +15642,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15708,45 +15704,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129048489</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602748</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018591</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15805,32 +15805,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129044697</v>
+        <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>80106</v>
+        <v>91837</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15840,10 +15840,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602730</v>
+        <v>602637</v>
       </c>
       <c r="R150" t="n">
-        <v>7018771</v>
+        <v>7018802</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15902,10 +15902,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129056716</v>
+        <v>129046543</v>
       </c>
       <c r="B151" t="n">
-        <v>79041</v>
+        <v>90572</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15913,37 +15913,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602754</v>
+        <v>602686</v>
       </c>
       <c r="R151" t="n">
-        <v>7018801</v>
+        <v>7018745</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15987,44 +15987,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129046543</v>
+        <v>129044697</v>
       </c>
       <c r="B152" t="n">
-        <v>90571</v>
+        <v>80106</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>229497</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602686</v>
+        <v>602730</v>
       </c>
       <c r="R152" t="n">
-        <v>7018745</v>
+        <v>7018771</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16096,10 +16096,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129046382</v>
+        <v>129056716</v>
       </c>
       <c r="B153" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16107,37 +16107,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602637</v>
+        <v>602754</v>
       </c>
       <c r="R153" t="n">
-        <v>7018802</v>
+        <v>7018801</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16181,12 +16181,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16290,52 +16290,48 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129048151</v>
+        <v>129056714</v>
       </c>
       <c r="B155" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602715</v>
+        <v>602678</v>
       </c>
       <c r="R155" t="n">
-        <v>7018634</v>
+        <v>7018771</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16379,60 +16375,55 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129045378</v>
+        <v>129056691</v>
       </c>
       <c r="B156" t="n">
-        <v>92242</v>
+        <v>10964</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602682</v>
+        <v>602659</v>
       </c>
       <c r="R156" t="n">
-        <v>7018833</v>
+        <v>7018825</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16476,44 +16467,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129044275</v>
+        <v>129045378</v>
       </c>
       <c r="B157" t="n">
-        <v>91827</v>
+        <v>92257</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16523,10 +16514,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602766</v>
+        <v>602682</v>
       </c>
       <c r="R157" t="n">
-        <v>7018767</v>
+        <v>7018833</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16585,48 +16576,52 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129056714</v>
+        <v>129048151</v>
       </c>
       <c r="B158" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602678</v>
+        <v>602715</v>
       </c>
       <c r="R158" t="n">
-        <v>7018771</v>
+        <v>7018634</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16670,22 +16665,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056691</v>
+        <v>129044275</v>
       </c>
       <c r="B159" t="n">
-        <v>10964</v>
+        <v>91837</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16693,32 +16688,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>101449</v>
+        <v>658</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602659</v>
+        <v>602766</v>
       </c>
       <c r="R159" t="n">
-        <v>7018825</v>
+        <v>7018767</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16762,61 +16762,57 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129044553</v>
+        <v>129045867</v>
       </c>
       <c r="B160" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602758</v>
+        <v>602663</v>
       </c>
       <c r="R160" t="n">
-        <v>7018769</v>
+        <v>7018805</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16875,45 +16871,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129047010</v>
+        <v>129044553</v>
       </c>
       <c r="B161" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602728</v>
+        <v>602758</v>
       </c>
       <c r="R161" t="n">
-        <v>7018716</v>
+        <v>7018769</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16975,7 +16975,7 @@
         <v>129056685</v>
       </c>
       <c r="B162" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17069,52 +17069,48 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129058444</v>
+        <v>129047010</v>
       </c>
       <c r="B163" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602760</v>
+        <v>602728</v>
       </c>
       <c r="R163" t="n">
-        <v>7018673</v>
+        <v>7018716</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17152,67 +17148,70 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129045867</v>
+        <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R164" t="n">
-        <v>7018805</v>
+        <v>7018673</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17250,50 +17249,51 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129056666</v>
+        <v>129056678</v>
       </c>
       <c r="B165" t="n">
-        <v>96924</v>
+        <v>80050</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17303,10 +17303,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R165" t="n">
-        <v>7018643</v>
+        <v>7018832</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17365,10 +17365,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129046627</v>
+        <v>129048297</v>
       </c>
       <c r="B166" t="n">
-        <v>78798</v>
+        <v>91837</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17376,21 +17376,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602705</v>
+        <v>602752</v>
       </c>
       <c r="R166" t="n">
-        <v>7018763</v>
+        <v>7018614</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,48 +17462,48 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129056678</v>
+        <v>129044893</v>
       </c>
       <c r="B167" t="n">
-        <v>80050</v>
+        <v>91837</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602672</v>
+        <v>602729</v>
       </c>
       <c r="R167" t="n">
-        <v>7018832</v>
+        <v>7018798</v>
       </c>
       <c r="S167" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17547,22 +17547,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B168" t="n">
-        <v>91827</v>
+        <v>78798</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17570,21 +17570,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17594,10 +17594,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R168" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17656,10 +17656,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129044893</v>
+        <v>129046592</v>
       </c>
       <c r="B169" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17667,34 +17667,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602729</v>
+        <v>602704</v>
       </c>
       <c r="R169" t="n">
-        <v>7018798</v>
+        <v>7018751</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17727,6 +17732,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17753,7 +17763,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129046592</v>
+        <v>129048918</v>
       </c>
       <c r="B170" t="n">
         <v>57727</v>
@@ -17793,10 +17803,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602704</v>
+        <v>602737</v>
       </c>
       <c r="R170" t="n">
-        <v>7018751</v>
+        <v>7018577</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17833,7 +17843,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Äldre ringhack tall</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17860,10 +17870,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129048918</v>
+        <v>129056666</v>
       </c>
       <c r="B171" t="n">
-        <v>57727</v>
+        <v>96950</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17871,42 +17881,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602737</v>
+        <v>602756</v>
       </c>
       <c r="R171" t="n">
-        <v>7018577</v>
+        <v>7018643</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17936,11 +17941,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17955,12 +17955,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,10 +6775,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045323</v>
+        <v>129056690</v>
       </c>
       <c r="B58" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602682</v>
+        <v>602758</v>
       </c>
       <c r="R58" t="n">
-        <v>7018848</v>
+        <v>7018806</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,60 +6860,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045660</v>
+        <v>129056682</v>
       </c>
       <c r="B59" t="n">
-        <v>80050</v>
+        <v>91838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602684</v>
+        <v>602751</v>
       </c>
       <c r="R59" t="n">
-        <v>7018786</v>
+        <v>7018603</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,22 +6957,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056690</v>
+        <v>129045323</v>
       </c>
       <c r="B60" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7000,17 +7000,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602758</v>
+        <v>602682</v>
       </c>
       <c r="R60" t="n">
-        <v>7018806</v>
+        <v>7018848</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,60 +7054,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056682</v>
+        <v>129045660</v>
       </c>
       <c r="B61" t="n">
-        <v>91837</v>
+        <v>80050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602751</v>
+        <v>602684</v>
       </c>
       <c r="R61" t="n">
-        <v>7018603</v>
+        <v>7018786</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,44 +7151,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048001</v>
+        <v>129045225</v>
       </c>
       <c r="B62" t="n">
-        <v>91992</v>
+        <v>97576</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602696</v>
+        <v>602705</v>
       </c>
       <c r="R62" t="n">
-        <v>7018662</v>
+        <v>7018799</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B63" t="n">
-        <v>97575</v>
+        <v>91838</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R63" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,48 +7357,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129056720</v>
+        <v>129048001</v>
       </c>
       <c r="B64" t="n">
-        <v>80181</v>
+        <v>91993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602773</v>
+        <v>602696</v>
       </c>
       <c r="R64" t="n">
-        <v>7018642</v>
+        <v>7018662</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,60 +7442,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B65" t="n">
-        <v>91837</v>
+        <v>80181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R65" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,12 +7539,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129056680</v>
+        <v>129044277</v>
       </c>
       <c r="B67" t="n">
-        <v>91992</v>
+        <v>91540</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602732</v>
+        <v>602759</v>
       </c>
       <c r="R67" t="n">
-        <v>7018811</v>
+        <v>7018767</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7733,60 +7733,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129056672</v>
+        <v>129045343</v>
       </c>
       <c r="B68" t="n">
-        <v>91540</v>
+        <v>91963</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602651</v>
+        <v>602684</v>
       </c>
       <c r="R68" t="n">
-        <v>7018826</v>
+        <v>7018837</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7816,6 +7816,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7830,44 +7835,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129050732</v>
+        <v>129045733</v>
       </c>
       <c r="B69" t="n">
-        <v>91837</v>
+        <v>80175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602710</v>
+        <v>602669</v>
       </c>
       <c r="R69" t="n">
-        <v>7018856</v>
+        <v>7018781</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7939,32 +7944,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7974,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R70" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8036,10 +8041,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056712</v>
+        <v>129056672</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8047,21 +8052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8071,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R71" t="n">
-        <v>7018697</v>
+        <v>7018826</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8133,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129044277</v>
+        <v>129050732</v>
       </c>
       <c r="B72" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,21 +8149,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8168,10 +8173,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602759</v>
+        <v>602710</v>
       </c>
       <c r="R72" t="n">
-        <v>7018767</v>
+        <v>7018856</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8230,48 +8235,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129045343</v>
+        <v>129056715</v>
       </c>
       <c r="B73" t="n">
-        <v>91962</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602684</v>
+        <v>602665</v>
       </c>
       <c r="R73" t="n">
-        <v>7018837</v>
+        <v>7018777</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8301,11 +8306,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8320,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129045733</v>
+        <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602669</v>
+        <v>602730</v>
       </c>
       <c r="R74" t="n">
-        <v>7018781</v>
+        <v>7018697</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,22 +8417,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129045649</v>
       </c>
       <c r="B75" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,21 +8440,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602688</v>
       </c>
       <c r="R75" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129049465</v>
+        <v>129046472</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8537,21 +8537,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602650</v>
+        <v>602666</v>
       </c>
       <c r="R76" t="n">
-        <v>7018649</v>
+        <v>7018759</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129045649</v>
+        <v>129049465</v>
       </c>
       <c r="B77" t="n">
         <v>80146</v>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602688</v>
+        <v>602650</v>
       </c>
       <c r="R77" t="n">
-        <v>7018774</v>
+        <v>7018649</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8720,48 +8720,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129056718</v>
+        <v>129044345</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>91753</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602758</v>
+        <v>602772</v>
       </c>
       <c r="R78" t="n">
-        <v>7018806</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056699</v>
+        <v>129056676</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602729</v>
+        <v>602667</v>
       </c>
       <c r="R79" t="n">
-        <v>7018756</v>
+        <v>7018779</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8888,6 +8888,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8914,48 +8919,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129044345</v>
+        <v>129056718</v>
       </c>
       <c r="B80" t="n">
-        <v>91752</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602772</v>
+        <v>602758</v>
       </c>
       <c r="R80" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,22 +9004,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129056699</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602729</v>
       </c>
       <c r="R81" t="n">
-        <v>7018779</v>
+        <v>7018756</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129048233</v>
+        <v>129056687</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602744</v>
+        <v>602733</v>
       </c>
       <c r="R82" t="n">
-        <v>7018615</v>
+        <v>7018822</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,44 +9198,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129046057</v>
+        <v>129045508</v>
       </c>
       <c r="B83" t="n">
-        <v>80106</v>
+        <v>91838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602648</v>
+        <v>602674</v>
       </c>
       <c r="R83" t="n">
-        <v>7018840</v>
+        <v>7018842</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9307,10 +9307,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129056687</v>
+        <v>129048233</v>
       </c>
       <c r="B84" t="n">
-        <v>91837</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,37 +9318,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602733</v>
+        <v>602744</v>
       </c>
       <c r="R84" t="n">
-        <v>7018822</v>
+        <v>7018615</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9392,22 +9392,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129045508</v>
+        <v>129048100</v>
       </c>
       <c r="B85" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9415,21 +9415,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602674</v>
+        <v>602670</v>
       </c>
       <c r="R85" t="n">
-        <v>7018842</v>
+        <v>7018643</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,32 +9501,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129048100</v>
+        <v>129046057</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602670</v>
+        <v>602648</v>
       </c>
       <c r="R86" t="n">
-        <v>7018643</v>
+        <v>7018840</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9601,7 +9601,7 @@
         <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,37 +9711,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R88" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056688</v>
+        <v>129044846</v>
       </c>
       <c r="B89" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9828,17 +9828,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602732</v>
+        <v>602719</v>
       </c>
       <c r="R89" t="n">
-        <v>7018811</v>
+        <v>7018813</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,22 +9882,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056686</v>
+        <v>129056688</v>
       </c>
       <c r="B90" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602702</v>
+        <v>602732</v>
       </c>
       <c r="R90" t="n">
-        <v>7018842</v>
+        <v>7018811</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129044846</v>
+        <v>129056686</v>
       </c>
       <c r="B91" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10022,17 +10022,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602719</v>
+        <v>602702</v>
       </c>
       <c r="R91" t="n">
-        <v>7018813</v>
+        <v>7018842</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,22 +10076,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129048130</v>
+        <v>129056711</v>
       </c>
       <c r="B92" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602704</v>
+        <v>602771</v>
       </c>
       <c r="R92" t="n">
-        <v>7018634</v>
+        <v>7018641</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,12 +10173,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B95" t="n">
-        <v>91558</v>
+        <v>91838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,21 +10390,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R95" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,10 +10476,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056698</v>
+        <v>129056709</v>
       </c>
       <c r="B96" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,23 +10487,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10511,10 +10507,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602735</v>
+        <v>602654</v>
       </c>
       <c r="R96" t="n">
-        <v>7018716</v>
+        <v>7018820</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10573,10 +10569,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056683</v>
+        <v>129056698</v>
       </c>
       <c r="B97" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10584,21 +10580,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10608,10 +10604,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602739</v>
+        <v>602735</v>
       </c>
       <c r="R97" t="n">
-        <v>7018692</v>
+        <v>7018716</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10670,10 +10666,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045623</v>
+        <v>129046720</v>
       </c>
       <c r="B98" t="n">
-        <v>98704</v>
+        <v>92183</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,38 +10677,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602687</v>
+        <v>602747</v>
       </c>
       <c r="R98" t="n">
-        <v>7018769</v>
+        <v>7018721</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10747,12 +10742,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10771,51 +10772,52 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058560</v>
+        <v>129045623</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602760</v>
+        <v>602687</v>
       </c>
       <c r="R99" t="n">
-        <v>7018673</v>
+        <v>7018769</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10853,26 +10855,25 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129056713</v>
+        <v>129058560</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10901,16 +10902,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602690</v>
+        <v>602760</v>
       </c>
       <c r="R100" t="n">
-        <v>7018768</v>
+        <v>7018673</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10951,6 +10955,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10969,51 +10974,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129046720</v>
+        <v>129056713</v>
       </c>
       <c r="B101" t="n">
-        <v>92182</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602747</v>
+        <v>602690</v>
       </c>
       <c r="R101" t="n">
-        <v>7018721</v>
+        <v>7018768</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11045,79 +11047,69 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129050244</v>
+        <v>129045582</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602665</v>
+        <v>602703</v>
       </c>
       <c r="R102" t="n">
-        <v>7018784</v>
+        <v>7018798</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11176,10 +11168,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129045681</v>
+        <v>129056684</v>
       </c>
       <c r="B103" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11187,37 +11179,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602667</v>
+        <v>602651</v>
       </c>
       <c r="R103" t="n">
-        <v>7018779</v>
+        <v>7018826</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11261,22 +11253,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129045582</v>
+        <v>129056671</v>
       </c>
       <c r="B104" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11284,37 +11276,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602703</v>
+        <v>602735</v>
       </c>
       <c r="R104" t="n">
-        <v>7018798</v>
+        <v>7018592</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11358,22 +11350,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045453</v>
+        <v>129045681</v>
       </c>
       <c r="B105" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11381,21 +11373,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11405,10 +11397,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602673</v>
+        <v>602667</v>
       </c>
       <c r="R105" t="n">
-        <v>7018844</v>
+        <v>7018779</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11467,10 +11459,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129044824</v>
+        <v>129056693</v>
       </c>
       <c r="B106" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11478,37 +11470,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602731</v>
+        <v>602670</v>
       </c>
       <c r="R106" t="n">
-        <v>7018789</v>
+        <v>7018818</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11538,6 +11530,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11552,22 +11549,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044805</v>
+        <v>129056697</v>
       </c>
       <c r="B107" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11575,37 +11572,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602747</v>
+        <v>602730</v>
       </c>
       <c r="R107" t="n">
-        <v>7018784</v>
+        <v>7018719</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11649,60 +11646,64 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056684</v>
+        <v>129050244</v>
       </c>
       <c r="B108" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602651</v>
+        <v>602665</v>
       </c>
       <c r="R108" t="n">
-        <v>7018826</v>
+        <v>7018784</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11746,19 +11747,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056671</v>
+        <v>129045453</v>
       </c>
       <c r="B109" t="n">
         <v>91540</v>
@@ -11789,17 +11790,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602735</v>
+        <v>602673</v>
       </c>
       <c r="R109" t="n">
-        <v>7018592</v>
+        <v>7018844</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11843,22 +11844,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056693</v>
+        <v>129044824</v>
       </c>
       <c r="B110" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11866,37 +11867,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602670</v>
+        <v>602731</v>
       </c>
       <c r="R110" t="n">
-        <v>7018818</v>
+        <v>7018789</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11926,11 +11927,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11945,22 +11941,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129056697</v>
+        <v>129044805</v>
       </c>
       <c r="B111" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11968,37 +11964,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602730</v>
+        <v>602747</v>
       </c>
       <c r="R111" t="n">
-        <v>7018719</v>
+        <v>7018784</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12042,50 +12038,49 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129046367</v>
+        <v>129044719</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12094,10 +12089,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602644</v>
+        <v>602727</v>
       </c>
       <c r="R112" t="n">
-        <v>7018800</v>
+        <v>7018795</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12130,11 +12125,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12164,7 +12154,7 @@
         <v>129044298</v>
       </c>
       <c r="B113" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12258,42 +12248,47 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129046525</v>
+        <v>129044230</v>
       </c>
       <c r="B114" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>602669</v>
+        <v>602777</v>
       </c>
       <c r="R114" t="n">
         <v>7018753</v>
@@ -12329,6 +12324,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12355,7 +12355,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129044230</v>
+        <v>129046367</v>
       </c>
       <c r="B115" t="n">
         <v>57727</v>
@@ -12386,7 +12386,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12395,10 +12395,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>602777</v>
+        <v>602644</v>
       </c>
       <c r="R115" t="n">
-        <v>7018753</v>
+        <v>7018800</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Gammalt bohål i gran, 4.5 m ovan mark</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12462,48 +12462,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129056708</v>
+        <v>129046525</v>
       </c>
       <c r="B116" t="n">
-        <v>91558</v>
+        <v>91504</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602663</v>
+        <v>602669</v>
       </c>
       <c r="R116" t="n">
-        <v>7018823</v>
+        <v>7018753</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12547,64 +12547,56 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129044719</v>
+        <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>98704</v>
+        <v>91560</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>602727</v>
+        <v>602663</v>
       </c>
       <c r="R117" t="n">
-        <v>7018795</v>
+        <v>7018823</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12648,12 +12640,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12663,7 +12655,7 @@
         <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12680,14 +12672,10 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12757,10 +12745,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056702</v>
+        <v>129056681</v>
       </c>
       <c r="B119" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12768,21 +12756,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12792,10 +12780,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602649</v>
+        <v>602736</v>
       </c>
       <c r="R119" t="n">
-        <v>7018829</v>
+        <v>7018593</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12854,10 +12842,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B120" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12865,21 +12853,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12889,10 +12877,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R120" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12951,52 +12939,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129050601</v>
+        <v>129056704</v>
       </c>
       <c r="B121" t="n">
-        <v>10964</v>
+        <v>98705</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602698</v>
+        <v>602735</v>
       </c>
       <c r="R121" t="n">
-        <v>7018836</v>
+        <v>7018692</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13030,7 +13014,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Under bark, granlåga</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13039,67 +13023,70 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B122" t="n">
-        <v>98704</v>
+        <v>10964</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R122" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13133,7 +13120,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13142,18 +13129,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13163,7 +13151,7 @@
         <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13264,7 +13252,7 @@
         <v>129056689</v>
       </c>
       <c r="B124" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14234,7 +14222,7 @@
         <v>129056667</v>
       </c>
       <c r="B134" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14328,32 +14316,27 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129056675</v>
+        <v>129056692</v>
       </c>
       <c r="B135" t="n">
-        <v>92257</v>
+        <v>10964</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14363,10 +14346,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602672</v>
+        <v>602687</v>
       </c>
       <c r="R135" t="n">
-        <v>7018832</v>
+        <v>7018836</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14425,10 +14408,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056694</v>
+        <v>129046455</v>
       </c>
       <c r="B136" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14436,37 +14419,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602656</v>
+        <v>602667</v>
       </c>
       <c r="R136" t="n">
-        <v>7018656</v>
+        <v>7018757</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,22 +14493,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129046455</v>
+        <v>129044406</v>
       </c>
       <c r="B137" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14533,21 +14516,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14557,10 +14540,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602667</v>
+        <v>602756</v>
       </c>
       <c r="R137" t="n">
-        <v>7018757</v>
+        <v>7018769</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -14619,45 +14602,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B138" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R138" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14716,52 +14703,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129046891</v>
+        <v>129056675</v>
       </c>
       <c r="B139" t="n">
-        <v>98704</v>
+        <v>92258</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602726</v>
+        <v>602672</v>
       </c>
       <c r="R139" t="n">
-        <v>7018723</v>
+        <v>7018832</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14805,22 +14788,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056692</v>
+        <v>129056694</v>
       </c>
       <c r="B140" t="n">
-        <v>10964</v>
+        <v>80146</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14828,16 +14811,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14847,10 +14835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602687</v>
+        <v>602656</v>
       </c>
       <c r="R140" t="n">
-        <v>7018836</v>
+        <v>7018656</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14909,10 +14897,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129046813</v>
+        <v>129048944</v>
       </c>
       <c r="B141" t="n">
-        <v>91100</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14920,34 +14908,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>937</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602732</v>
+        <v>602734</v>
       </c>
       <c r="R141" t="n">
-        <v>7018701</v>
+        <v>7018579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14980,6 +14973,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15006,48 +15004,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129056679</v>
+        <v>129046813</v>
       </c>
       <c r="B142" t="n">
-        <v>91992</v>
+        <v>91100</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1209</v>
+        <v>937</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602737</v>
+        <v>602732</v>
       </c>
       <c r="R142" t="n">
-        <v>7018593</v>
+        <v>7018701</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15091,44 +15089,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>91993</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15138,10 +15136,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R143" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15200,7 +15198,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B144" t="n">
         <v>80146</v>
@@ -15235,10 +15233,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R144" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15297,10 +15295,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129048944</v>
+        <v>129056696</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15308,42 +15306,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602734</v>
+        <v>602779</v>
       </c>
       <c r="R145" t="n">
-        <v>7018579</v>
+        <v>7018639</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15373,11 +15366,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15392,12 +15380,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15606,7 +15594,7 @@
         <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15707,7 +15695,7 @@
         <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15808,7 +15796,7 @@
         <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16193,32 +16181,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129050391</v>
+        <v>129044275</v>
       </c>
       <c r="B154" t="n">
-        <v>80050</v>
+        <v>91838</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16228,10 +16216,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602671</v>
+        <v>602766</v>
       </c>
       <c r="R154" t="n">
-        <v>7018809</v>
+        <v>7018767</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16290,48 +16278,48 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129056714</v>
+        <v>129045378</v>
       </c>
       <c r="B155" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602678</v>
+        <v>602682</v>
       </c>
       <c r="R155" t="n">
-        <v>7018771</v>
+        <v>7018833</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16375,55 +16363,64 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129056691</v>
+        <v>129048151</v>
       </c>
       <c r="B156" t="n">
-        <v>10964</v>
+        <v>98705</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602659</v>
+        <v>602715</v>
       </c>
       <c r="R156" t="n">
-        <v>7018825</v>
+        <v>7018634</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16467,60 +16464,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129045378</v>
+        <v>129056714</v>
       </c>
       <c r="B157" t="n">
-        <v>92257</v>
+        <v>79041</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602682</v>
+        <v>602678</v>
       </c>
       <c r="R157" t="n">
-        <v>7018833</v>
+        <v>7018771</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16564,61 +16561,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B158" t="n">
-        <v>98704</v>
+        <v>80050</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R158" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16677,10 +16670,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129044275</v>
+        <v>129056691</v>
       </c>
       <c r="B159" t="n">
-        <v>91837</v>
+        <v>10964</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16688,37 +16681,32 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>658</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602766</v>
+        <v>602659</v>
       </c>
       <c r="R159" t="n">
-        <v>7018767</v>
+        <v>7018825</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16762,22 +16750,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129045867</v>
+        <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16785,21 +16773,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16809,10 +16797,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602663</v>
+        <v>602728</v>
       </c>
       <c r="R160" t="n">
-        <v>7018805</v>
+        <v>7018716</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16871,49 +16859,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129044553</v>
+        <v>129045867</v>
       </c>
       <c r="B161" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602758</v>
+        <v>602663</v>
       </c>
       <c r="R161" t="n">
-        <v>7018769</v>
+        <v>7018805</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16975,7 +16959,7 @@
         <v>129056685</v>
       </c>
       <c r="B162" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17069,45 +17053,49 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129047010</v>
+        <v>129044553</v>
       </c>
       <c r="B163" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602728</v>
+        <v>602758</v>
       </c>
       <c r="R163" t="n">
-        <v>7018716</v>
+        <v>7018769</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17169,7 +17157,7 @@
         <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17268,48 +17256,48 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129056678</v>
+        <v>129048297</v>
       </c>
       <c r="B165" t="n">
-        <v>80050</v>
+        <v>91838</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602672</v>
+        <v>602752</v>
       </c>
       <c r="R165" t="n">
-        <v>7018832</v>
+        <v>7018614</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17353,22 +17341,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129048297</v>
+        <v>129044893</v>
       </c>
       <c r="B166" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17400,10 +17388,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602752</v>
+        <v>602729</v>
       </c>
       <c r="R166" t="n">
-        <v>7018614</v>
+        <v>7018798</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17462,10 +17450,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129044893</v>
+        <v>129048918</v>
       </c>
       <c r="B167" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17473,34 +17461,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602729</v>
+        <v>602737</v>
       </c>
       <c r="R167" t="n">
-        <v>7018798</v>
+        <v>7018577</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17533,6 +17526,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17656,10 +17654,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129046592</v>
+        <v>129056666</v>
       </c>
       <c r="B169" t="n">
-        <v>57727</v>
+        <v>96951</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17667,42 +17665,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602704</v>
+        <v>602756</v>
       </c>
       <c r="R169" t="n">
-        <v>7018751</v>
+        <v>7018643</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17732,11 +17725,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17751,65 +17739,60 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129048918</v>
+        <v>129056678</v>
       </c>
       <c r="B170" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602737</v>
+        <v>602672</v>
       </c>
       <c r="R170" t="n">
-        <v>7018577</v>
+        <v>7018832</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17839,11 +17822,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17858,22 +17836,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056666</v>
+        <v>129046592</v>
       </c>
       <c r="B171" t="n">
-        <v>96950</v>
+        <v>57727</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17881,37 +17859,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602756</v>
+        <v>602704</v>
       </c>
       <c r="R171" t="n">
-        <v>7018643</v>
+        <v>7018751</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17941,6 +17924,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17955,12 +17943,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,7 +6775,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129056690</v>
+        <v>129045323</v>
       </c>
       <c r="B58" t="n">
         <v>91838</v>
@@ -6806,17 +6806,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602758</v>
+        <v>602682</v>
       </c>
       <c r="R58" t="n">
-        <v>7018806</v>
+        <v>7018848</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,60 +6860,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129056682</v>
+        <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>91838</v>
+        <v>80050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602751</v>
+        <v>602684</v>
       </c>
       <c r="R59" t="n">
-        <v>7018603</v>
+        <v>7018786</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,19 +6957,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129045323</v>
+        <v>129056690</v>
       </c>
       <c r="B60" t="n">
         <v>91838</v>
@@ -7000,17 +7000,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602682</v>
+        <v>602758</v>
       </c>
       <c r="R60" t="n">
-        <v>7018848</v>
+        <v>7018806</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7054,60 +7054,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045660</v>
+        <v>129056682</v>
       </c>
       <c r="B61" t="n">
-        <v>80050</v>
+        <v>91838</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602684</v>
+        <v>602751</v>
       </c>
       <c r="R61" t="n">
-        <v>7018786</v>
+        <v>7018603</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,12 +7151,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7166,7 +7166,7 @@
         <v>129045225</v>
       </c>
       <c r="B62" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7260,48 +7260,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B63" t="n">
-        <v>91838</v>
+        <v>80181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R63" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129056720</v>
+        <v>129048977</v>
       </c>
       <c r="B65" t="n">
-        <v>80181</v>
+        <v>91838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602773</v>
+        <v>602712</v>
       </c>
       <c r="R65" t="n">
-        <v>7018642</v>
+        <v>7018600</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,12 +7539,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7648,32 +7648,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044277</v>
+        <v>129045733</v>
       </c>
       <c r="B67" t="n">
-        <v>91540</v>
+        <v>80175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602759</v>
+        <v>602669</v>
       </c>
       <c r="R67" t="n">
-        <v>7018767</v>
+        <v>7018781</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7745,32 +7745,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045343</v>
+        <v>129044277</v>
       </c>
       <c r="B68" t="n">
-        <v>91963</v>
+        <v>91540</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602684</v>
+        <v>602759</v>
       </c>
       <c r="R68" t="n">
-        <v>7018837</v>
+        <v>7018767</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7816,11 +7816,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7847,10 +7842,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045733</v>
+        <v>129045343</v>
       </c>
       <c r="B69" t="n">
-        <v>80175</v>
+        <v>91963</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7858,21 +7853,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>4217</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602669</v>
+        <v>602684</v>
       </c>
       <c r="R69" t="n">
-        <v>7018781</v>
+        <v>7018837</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7918,6 +7913,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,32 +7944,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056680</v>
+        <v>129056715</v>
       </c>
       <c r="B70" t="n">
-        <v>91993</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602732</v>
+        <v>602665</v>
       </c>
       <c r="R70" t="n">
-        <v>7018811</v>
+        <v>7018777</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056672</v>
+        <v>129056712</v>
       </c>
       <c r="B71" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8052,21 +8052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602651</v>
+        <v>602730</v>
       </c>
       <c r="R71" t="n">
-        <v>7018826</v>
+        <v>7018697</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8235,32 +8235,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R73" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056712</v>
+        <v>129056672</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8343,21 +8343,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R74" t="n">
-        <v>7018697</v>
+        <v>7018826</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129045649</v>
+        <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,21 +8440,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602688</v>
+        <v>602666</v>
       </c>
       <c r="R75" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8526,32 +8526,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129046472</v>
+        <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>91838</v>
+        <v>91753</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602666</v>
+        <v>602772</v>
       </c>
       <c r="R76" t="n">
         <v>7018759</v>
@@ -8720,32 +8720,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129044345</v>
+        <v>129045649</v>
       </c>
       <c r="B78" t="n">
-        <v>91753</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602772</v>
+        <v>602688</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129056687</v>
+        <v>129048233</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602733</v>
+        <v>602744</v>
       </c>
       <c r="R82" t="n">
-        <v>7018822</v>
+        <v>7018615</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9198,12 +9198,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048233</v>
+        <v>129048100</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,21 +9318,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602744</v>
+        <v>602670</v>
       </c>
       <c r="R84" t="n">
-        <v>7018615</v>
+        <v>7018643</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9404,32 +9404,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129048100</v>
+        <v>129046057</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602670</v>
+        <v>602648</v>
       </c>
       <c r="R85" t="n">
-        <v>7018643</v>
+        <v>7018840</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,48 +9501,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129046057</v>
+        <v>129056687</v>
       </c>
       <c r="B86" t="n">
-        <v>80106</v>
+        <v>91838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602648</v>
+        <v>602733</v>
       </c>
       <c r="R86" t="n">
-        <v>7018840</v>
+        <v>7018822</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9586,12 +9586,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9601,7 +9601,7 @@
         <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129048130</v>
+        <v>129044846</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,21 +9711,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602704</v>
+        <v>602719</v>
       </c>
       <c r="R88" t="n">
-        <v>7018634</v>
+        <v>7018813</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9797,7 +9797,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129044846</v>
+        <v>129056688</v>
       </c>
       <c r="B89" t="n">
         <v>91838</v>
@@ -9828,17 +9828,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602719</v>
+        <v>602732</v>
       </c>
       <c r="R89" t="n">
-        <v>7018813</v>
+        <v>7018811</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9882,19 +9882,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056688</v>
+        <v>129056686</v>
       </c>
       <c r="B90" t="n">
         <v>91838</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602732</v>
+        <v>602702</v>
       </c>
       <c r="R90" t="n">
-        <v>7018811</v>
+        <v>7018842</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129056686</v>
+        <v>129056711</v>
       </c>
       <c r="B91" t="n">
-        <v>91838</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,21 +10002,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602702</v>
+        <v>602771</v>
       </c>
       <c r="R91" t="n">
-        <v>7018842</v>
+        <v>7018641</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129056711</v>
+        <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,37 +10099,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602771</v>
+        <v>602704</v>
       </c>
       <c r="R92" t="n">
-        <v>7018641</v>
+        <v>7018634</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10173,12 +10173,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056683</v>
+        <v>129056709</v>
       </c>
       <c r="B95" t="n">
-        <v>91838</v>
+        <v>91560</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,23 +10390,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10414,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602739</v>
+        <v>602654</v>
       </c>
       <c r="R95" t="n">
-        <v>7018692</v>
+        <v>7018820</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10476,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B96" t="n">
-        <v>91560</v>
+        <v>91838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10487,19 +10483,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10507,10 +10507,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R96" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10775,7 +10775,7 @@
         <v>129045623</v>
       </c>
       <c r="B99" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045582</v>
+        <v>129045453</v>
       </c>
       <c r="B102" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11082,21 +11082,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602703</v>
+        <v>602673</v>
       </c>
       <c r="R102" t="n">
-        <v>7018798</v>
+        <v>7018844</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129056684</v>
+        <v>129044824</v>
       </c>
       <c r="B103" t="n">
         <v>91838</v>
@@ -11199,17 +11199,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602651</v>
+        <v>602731</v>
       </c>
       <c r="R103" t="n">
-        <v>7018826</v>
+        <v>7018789</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11253,22 +11253,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129056671</v>
+        <v>129044805</v>
       </c>
       <c r="B104" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11276,37 +11276,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R104" t="n">
-        <v>7018592</v>
+        <v>7018784</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11350,12 +11350,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129056693</v>
+        <v>129045582</v>
       </c>
       <c r="B106" t="n">
         <v>80146</v>
@@ -11490,17 +11490,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602670</v>
+        <v>602703</v>
       </c>
       <c r="R106" t="n">
-        <v>7018818</v>
+        <v>7018798</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11530,11 +11530,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11549,22 +11544,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056697</v>
+        <v>129056684</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11567,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R107" t="n">
-        <v>7018719</v>
+        <v>7018826</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11658,52 +11653,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129050244</v>
+        <v>129056671</v>
       </c>
       <c r="B108" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602665</v>
+        <v>602735</v>
       </c>
       <c r="R108" t="n">
-        <v>7018784</v>
+        <v>7018592</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11747,22 +11738,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129045453</v>
+        <v>129056693</v>
       </c>
       <c r="B109" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11770,37 +11761,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602673</v>
+        <v>602670</v>
       </c>
       <c r="R109" t="n">
-        <v>7018844</v>
+        <v>7018818</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11830,6 +11821,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11844,22 +11840,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044824</v>
+        <v>129056697</v>
       </c>
       <c r="B110" t="n">
-        <v>91838</v>
+        <v>80146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11867,37 +11863,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602731</v>
+        <v>602730</v>
       </c>
       <c r="R110" t="n">
-        <v>7018789</v>
+        <v>7018719</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11941,54 +11937,58 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129044805</v>
+        <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602747</v>
+        <v>602665</v>
       </c>
       <c r="R111" t="n">
         <v>7018784</v>
@@ -12050,49 +12050,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044719</v>
+        <v>129046525</v>
       </c>
       <c r="B112" t="n">
-        <v>98705</v>
+        <v>91504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602727</v>
+        <v>602669</v>
       </c>
       <c r="R112" t="n">
-        <v>7018795</v>
+        <v>7018753</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12462,45 +12458,49 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129046525</v>
+        <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>91504</v>
+        <v>98706</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>602669</v>
+        <v>602727</v>
       </c>
       <c r="R116" t="n">
-        <v>7018753</v>
+        <v>7018795</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12652,10 +12652,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129044475</v>
+        <v>129056702</v>
       </c>
       <c r="B118" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12663,33 +12663,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602766</v>
+        <v>602649</v>
       </c>
       <c r="R118" t="n">
-        <v>7018781</v>
+        <v>7018829</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12733,22 +12737,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056681</v>
+        <v>129044475</v>
       </c>
       <c r="B119" t="n">
-        <v>91838</v>
+        <v>91560</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12756,37 +12760,33 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602736</v>
+        <v>602766</v>
       </c>
       <c r="R119" t="n">
-        <v>7018593</v>
+        <v>7018781</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12830,22 +12830,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056702</v>
+        <v>129056681</v>
       </c>
       <c r="B120" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12853,21 +12853,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12877,10 +12877,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602649</v>
+        <v>602736</v>
       </c>
       <c r="R120" t="n">
-        <v>7018829</v>
+        <v>7018593</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12939,48 +12939,52 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B121" t="n">
-        <v>98705</v>
+        <v>10964</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R121" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13014,7 +13018,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13023,70 +13027,67 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129050601</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>10964</v>
+        <v>98706</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602698</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018836</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13120,7 +13121,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Under bark, granlåga</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13129,19 +13130,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13151,7 +13151,7 @@
         <v>129046716</v>
       </c>
       <c r="B123" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13249,48 +13249,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129056689</v>
+        <v>129044962</v>
       </c>
       <c r="B124" t="n">
-        <v>91838</v>
+        <v>91504</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602754</v>
+        <v>602750</v>
       </c>
       <c r="R124" t="n">
-        <v>7018806</v>
+        <v>7018799</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13334,44 +13334,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056668</v>
+        <v>129056689</v>
       </c>
       <c r="B125" t="n">
-        <v>91504</v>
+        <v>91838</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602738</v>
+        <v>602754</v>
       </c>
       <c r="R125" t="n">
-        <v>7018795</v>
+        <v>7018806</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13443,48 +13443,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129044962</v>
+        <v>129056700</v>
       </c>
       <c r="B126" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602750</v>
+        <v>602684</v>
       </c>
       <c r="R126" t="n">
-        <v>7018799</v>
+        <v>7018776</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13528,60 +13528,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056700</v>
+        <v>129050404</v>
       </c>
       <c r="B127" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R127" t="n">
-        <v>7018776</v>
+        <v>7018808</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13625,22 +13625,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129050404</v>
+        <v>129056668</v>
       </c>
       <c r="B128" t="n">
-        <v>80175</v>
+        <v>91504</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13648,37 +13648,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602672</v>
+        <v>602738</v>
       </c>
       <c r="R128" t="n">
-        <v>7018808</v>
+        <v>7018795</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13722,12 +13722,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13831,32 +13831,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129050334</v>
+        <v>129045756</v>
       </c>
       <c r="B130" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13866,10 +13866,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602671</v>
+        <v>602663</v>
       </c>
       <c r="R130" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13928,32 +13928,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B131" t="n">
-        <v>80106</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R131" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14025,10 +14025,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129045512</v>
+        <v>129046455</v>
       </c>
       <c r="B132" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14036,21 +14036,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14060,10 +14060,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602682</v>
+        <v>602667</v>
       </c>
       <c r="R132" t="n">
-        <v>7018827</v>
+        <v>7018757</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14122,10 +14122,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129045677</v>
+        <v>129044406</v>
       </c>
       <c r="B133" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14133,21 +14133,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14157,10 +14157,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602684</v>
+        <v>602756</v>
       </c>
       <c r="R133" t="n">
-        <v>7018786</v>
+        <v>7018769</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14219,48 +14219,52 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129056667</v>
+        <v>129046891</v>
       </c>
       <c r="B134" t="n">
-        <v>96951</v>
+        <v>98706</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602672</v>
+        <v>602726</v>
       </c>
       <c r="R134" t="n">
-        <v>7018807</v>
+        <v>7018723</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14304,39 +14308,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129056692</v>
+        <v>129056675</v>
       </c>
       <c r="B135" t="n">
-        <v>10964</v>
+        <v>92258</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>101449</v>
+        <v>3298</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14346,10 +14355,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602687</v>
+        <v>602672</v>
       </c>
       <c r="R135" t="n">
-        <v>7018836</v>
+        <v>7018832</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14408,10 +14417,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129046455</v>
+        <v>129056692</v>
       </c>
       <c r="B136" t="n">
-        <v>79041</v>
+        <v>10964</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14419,37 +14428,32 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602667</v>
+        <v>602687</v>
       </c>
       <c r="R136" t="n">
-        <v>7018757</v>
+        <v>7018836</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14493,19 +14497,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129044406</v>
+        <v>129056694</v>
       </c>
       <c r="B137" t="n">
         <v>80146</v>
@@ -14536,17 +14540,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602756</v>
+        <v>602656</v>
       </c>
       <c r="R137" t="n">
-        <v>7018769</v>
+        <v>7018656</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14590,61 +14594,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129046891</v>
+        <v>129045677</v>
       </c>
       <c r="B138" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602726</v>
+        <v>602684</v>
       </c>
       <c r="R138" t="n">
-        <v>7018723</v>
+        <v>7018786</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -14703,48 +14703,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056675</v>
+        <v>129045512</v>
       </c>
       <c r="B139" t="n">
-        <v>92258</v>
+        <v>91540</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R139" t="n">
-        <v>7018832</v>
+        <v>7018827</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14788,22 +14788,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056694</v>
+        <v>129056667</v>
       </c>
       <c r="B140" t="n">
-        <v>80146</v>
+        <v>96952</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14811,21 +14811,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602656</v>
+        <v>602672</v>
       </c>
       <c r="R140" t="n">
-        <v>7018656</v>
+        <v>7018807</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14897,10 +14897,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129048944</v>
+        <v>129056705</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14908,16 +14908,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14926,24 +14926,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602734</v>
+        <v>602730</v>
       </c>
       <c r="R141" t="n">
-        <v>7018579</v>
+        <v>7018719</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14977,7 +14972,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14992,12 +14987,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15101,48 +15096,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056679</v>
+        <v>129048944</v>
       </c>
       <c r="B143" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602737</v>
+        <v>602734</v>
       </c>
       <c r="R143" t="n">
-        <v>7018593</v>
+        <v>7018579</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15172,6 +15172,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15186,44 +15191,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B144" t="n">
-        <v>80146</v>
+        <v>91993</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15233,10 +15238,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R144" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15295,7 +15300,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056696</v>
+        <v>129056695</v>
       </c>
       <c r="B145" t="n">
         <v>80146</v>
@@ -15330,10 +15335,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602779</v>
+        <v>602754</v>
       </c>
       <c r="R145" t="n">
-        <v>7018639</v>
+        <v>7018633</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15392,10 +15397,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129056705</v>
+        <v>129056696</v>
       </c>
       <c r="B146" t="n">
-        <v>56908</v>
+        <v>80146</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15403,21 +15408,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15427,10 +15432,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>602730</v>
+        <v>602779</v>
       </c>
       <c r="R146" t="n">
-        <v>7018719</v>
+        <v>7018639</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15463,11 +15468,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15494,45 +15494,49 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129048489</v>
+        <v>129045069</v>
       </c>
       <c r="B147" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602748</v>
+        <v>602751</v>
       </c>
       <c r="R147" t="n">
-        <v>7018591</v>
+        <v>7018815</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15591,10 +15595,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129045069</v>
+        <v>129046445</v>
       </c>
       <c r="B148" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15630,10 +15634,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602751</v>
+        <v>602669</v>
       </c>
       <c r="R148" t="n">
-        <v>7018815</v>
+        <v>7018754</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15692,49 +15696,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129046445</v>
+        <v>129048489</v>
       </c>
       <c r="B149" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602669</v>
+        <v>602748</v>
       </c>
       <c r="R149" t="n">
-        <v>7018754</v>
+        <v>7018591</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15793,32 +15793,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046382</v>
+        <v>129044697</v>
       </c>
       <c r="B150" t="n">
-        <v>91838</v>
+        <v>80106</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15828,10 +15828,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602637</v>
+        <v>602730</v>
       </c>
       <c r="R150" t="n">
-        <v>7018802</v>
+        <v>7018771</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15987,32 +15987,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129044697</v>
+        <v>129046382</v>
       </c>
       <c r="B152" t="n">
-        <v>80106</v>
+        <v>91838</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16022,10 +16022,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602730</v>
+        <v>602637</v>
       </c>
       <c r="R152" t="n">
-        <v>7018771</v>
+        <v>7018802</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16278,45 +16278,49 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129045378</v>
+        <v>129048151</v>
       </c>
       <c r="B155" t="n">
-        <v>92258</v>
+        <v>98706</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602682</v>
+        <v>602715</v>
       </c>
       <c r="R155" t="n">
-        <v>7018833</v>
+        <v>7018634</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16375,49 +16379,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129048151</v>
+        <v>129050391</v>
       </c>
       <c r="B156" t="n">
-        <v>98705</v>
+        <v>80050</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602715</v>
+        <v>602671</v>
       </c>
       <c r="R156" t="n">
-        <v>7018634</v>
+        <v>7018809</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16573,10 +16573,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129050391</v>
+        <v>129045378</v>
       </c>
       <c r="B158" t="n">
-        <v>80050</v>
+        <v>92258</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16584,21 +16584,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16608,10 +16608,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602671</v>
+        <v>602682</v>
       </c>
       <c r="R158" t="n">
-        <v>7018809</v>
+        <v>7018833</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16762,10 +16762,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129047010</v>
+        <v>129056685</v>
       </c>
       <c r="B160" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16773,37 +16773,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602728</v>
+        <v>602683</v>
       </c>
       <c r="R160" t="n">
-        <v>7018716</v>
+        <v>7018835</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16847,60 +16847,64 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129045867</v>
+        <v>129058444</v>
       </c>
       <c r="B161" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R161" t="n">
-        <v>7018805</v>
+        <v>7018673</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16938,66 +16942,71 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129056685</v>
+        <v>129044553</v>
       </c>
       <c r="B162" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>602683</v>
+        <v>602758</v>
       </c>
       <c r="R162" t="n">
-        <v>7018835</v>
+        <v>7018769</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17041,61 +17050,57 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129044553</v>
+        <v>129047010</v>
       </c>
       <c r="B163" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602758</v>
+        <v>602728</v>
       </c>
       <c r="R163" t="n">
-        <v>7018769</v>
+        <v>7018716</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17154,52 +17159,48 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129058444</v>
+        <v>129045867</v>
       </c>
       <c r="B164" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602760</v>
+        <v>602663</v>
       </c>
       <c r="R164" t="n">
-        <v>7018673</v>
+        <v>7018805</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17237,19 +17238,18 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17353,10 +17353,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129044893</v>
+        <v>129046627</v>
       </c>
       <c r="B166" t="n">
-        <v>91838</v>
+        <v>78798</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17364,21 +17364,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17388,10 +17388,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602729</v>
+        <v>602705</v>
       </c>
       <c r="R166" t="n">
-        <v>7018798</v>
+        <v>7018763</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17450,7 +17450,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129048918</v>
+        <v>129046592</v>
       </c>
       <c r="B167" t="n">
         <v>57727</v>
@@ -17490,10 +17490,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602737</v>
+        <v>602704</v>
       </c>
       <c r="R167" t="n">
-        <v>7018577</v>
+        <v>7018751</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17557,10 +17557,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129046627</v>
+        <v>129044893</v>
       </c>
       <c r="B168" t="n">
-        <v>78798</v>
+        <v>91838</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17568,21 +17568,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602705</v>
+        <v>602729</v>
       </c>
       <c r="R168" t="n">
-        <v>7018763</v>
+        <v>7018798</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17654,10 +17654,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129056666</v>
+        <v>129048918</v>
       </c>
       <c r="B169" t="n">
-        <v>96951</v>
+        <v>57727</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17665,37 +17665,42 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602756</v>
+        <v>602737</v>
       </c>
       <c r="R169" t="n">
-        <v>7018643</v>
+        <v>7018577</v>
       </c>
       <c r="S169" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17725,6 +17730,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17739,44 +17749,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056678</v>
+        <v>129056666</v>
       </c>
       <c r="B170" t="n">
-        <v>80050</v>
+        <v>96952</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17786,10 +17796,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R170" t="n">
-        <v>7018832</v>
+        <v>7018643</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17848,53 +17858,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129046592</v>
+        <v>129056678</v>
       </c>
       <c r="B171" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602704</v>
+        <v>602672</v>
       </c>
       <c r="R171" t="n">
-        <v>7018751</v>
+        <v>7018832</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17924,11 +17929,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17943,12 +17943,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>129045323</v>
       </c>
       <c r="B58" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129045660</v>
       </c>
       <c r="B59" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056690</v>
+        <v>129056682</v>
       </c>
       <c r="B60" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602758</v>
+        <v>602751</v>
       </c>
       <c r="R60" t="n">
-        <v>7018806</v>
+        <v>7018603</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056682</v>
+        <v>129056690</v>
       </c>
       <c r="B61" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602751</v>
+        <v>602758</v>
       </c>
       <c r="R61" t="n">
-        <v>7018603</v>
+        <v>7018806</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7163,32 +7163,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129045225</v>
+        <v>129048977</v>
       </c>
       <c r="B62" t="n">
-        <v>97577</v>
+        <v>91841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602705</v>
+        <v>602712</v>
       </c>
       <c r="R62" t="n">
-        <v>7018799</v>
+        <v>7018600</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7263,7 +7263,7 @@
         <v>129056720</v>
       </c>
       <c r="B63" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>129048001</v>
       </c>
       <c r="B64" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7454,32 +7454,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048977</v>
+        <v>129045225</v>
       </c>
       <c r="B65" t="n">
-        <v>91838</v>
+        <v>97581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602712</v>
+        <v>602705</v>
       </c>
       <c r="R65" t="n">
-        <v>7018600</v>
+        <v>7018799</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7554,7 +7554,7 @@
         <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045733</v>
+        <v>129045343</v>
       </c>
       <c r="B67" t="n">
-        <v>80175</v>
+        <v>91966</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>4217</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602669</v>
+        <v>602684</v>
       </c>
       <c r="R67" t="n">
-        <v>7018781</v>
+        <v>7018837</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7719,6 +7719,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7748,7 +7753,7 @@
         <v>129044277</v>
       </c>
       <c r="B68" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7842,10 +7847,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045343</v>
+        <v>129045733</v>
       </c>
       <c r="B69" t="n">
-        <v>91963</v>
+        <v>80177</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7853,21 +7858,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4217</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602684</v>
+        <v>602669</v>
       </c>
       <c r="R69" t="n">
-        <v>7018837</v>
+        <v>7018781</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7913,11 +7918,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,32 +7944,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>91996</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R70" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056712</v>
+        <v>129056672</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8052,21 +8052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R71" t="n">
-        <v>7018697</v>
+        <v>7018826</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129050732</v>
+        <v>129056715</v>
       </c>
       <c r="B72" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8149,37 +8149,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602710</v>
+        <v>602665</v>
       </c>
       <c r="R72" t="n">
-        <v>7018856</v>
+        <v>7018777</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,44 +8223,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056680</v>
+        <v>129056712</v>
       </c>
       <c r="B73" t="n">
-        <v>91993</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602732</v>
+        <v>602730</v>
       </c>
       <c r="R73" t="n">
-        <v>7018811</v>
+        <v>7018697</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056672</v>
+        <v>129050732</v>
       </c>
       <c r="B74" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8343,37 +8343,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602651</v>
+        <v>602710</v>
       </c>
       <c r="R74" t="n">
-        <v>7018826</v>
+        <v>7018856</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,12 +8417,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
         <v>129046472</v>
       </c>
       <c r="B75" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>129044345</v>
       </c>
       <c r="B76" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>129049465</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>129045649</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056676</v>
+        <v>129056718</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602667</v>
+        <v>602758</v>
       </c>
       <c r="R79" t="n">
-        <v>7018779</v>
+        <v>7018806</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8888,11 +8888,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8919,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056718</v>
+        <v>129056699</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8930,21 +8925,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8954,10 +8949,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602758</v>
+        <v>602729</v>
       </c>
       <c r="R80" t="n">
-        <v>7018806</v>
+        <v>7018756</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9016,10 +9011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056699</v>
+        <v>129056676</v>
       </c>
       <c r="B81" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,21 +9022,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9051,10 +9046,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602729</v>
+        <v>602667</v>
       </c>
       <c r="R81" t="n">
-        <v>7018756</v>
+        <v>7018779</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9087,6 +9082,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,32 +9113,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129048233</v>
+        <v>129046057</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>80108</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602744</v>
+        <v>602648</v>
       </c>
       <c r="R82" t="n">
-        <v>7018615</v>
+        <v>7018840</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129045508</v>
+        <v>129056687</v>
       </c>
       <c r="B83" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9241,17 +9241,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602674</v>
+        <v>602733</v>
       </c>
       <c r="R83" t="n">
-        <v>7018842</v>
+        <v>7018822</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9295,60 +9295,64 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129048100</v>
+        <v>129058573</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602670</v>
+        <v>602756</v>
       </c>
       <c r="R84" t="n">
-        <v>7018643</v>
+        <v>7018669</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9386,50 +9390,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129046057</v>
+        <v>129045508</v>
       </c>
       <c r="B85" t="n">
-        <v>80106</v>
+        <v>91841</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9439,10 +9444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602648</v>
+        <v>602674</v>
       </c>
       <c r="R85" t="n">
-        <v>7018840</v>
+        <v>7018842</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9501,10 +9506,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129056687</v>
+        <v>129048233</v>
       </c>
       <c r="B86" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9512,37 +9517,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602733</v>
+        <v>602744</v>
       </c>
       <c r="R86" t="n">
-        <v>7018822</v>
+        <v>7018615</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9586,64 +9591,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058573</v>
+        <v>129048100</v>
       </c>
       <c r="B87" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602756</v>
+        <v>602670</v>
       </c>
       <c r="R87" t="n">
-        <v>7018669</v>
+        <v>7018643</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9681,29 +9682,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129044846</v>
+        <v>129056711</v>
       </c>
       <c r="B88" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,37 +9711,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602719</v>
+        <v>602771</v>
       </c>
       <c r="R88" t="n">
-        <v>7018813</v>
+        <v>7018641</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9785,22 +9785,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129056688</v>
+        <v>129056686</v>
       </c>
       <c r="B89" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>602732</v>
+        <v>602702</v>
       </c>
       <c r="R89" t="n">
-        <v>7018811</v>
+        <v>7018842</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056686</v>
+        <v>129056688</v>
       </c>
       <c r="B90" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602702</v>
+        <v>602732</v>
       </c>
       <c r="R90" t="n">
-        <v>7018842</v>
+        <v>7018811</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129056711</v>
+        <v>129044846</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,37 +10002,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602771</v>
+        <v>602719</v>
       </c>
       <c r="R91" t="n">
-        <v>7018641</v>
+        <v>7018813</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10076,12 +10076,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
         <v>129048130</v>
       </c>
       <c r="B92" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129046062</v>
+        <v>129056709</v>
       </c>
       <c r="B93" t="n">
-        <v>80146</v>
+        <v>91563</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,37 +10196,33 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602648</v>
+        <v>602654</v>
       </c>
       <c r="R93" t="n">
-        <v>7018840</v>
+        <v>7018820</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10270,22 +10266,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10313,17 +10309,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R94" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10367,22 +10363,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056709</v>
+        <v>129056683</v>
       </c>
       <c r="B95" t="n">
-        <v>91560</v>
+        <v>91841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10390,19 +10386,23 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602654</v>
+        <v>602739</v>
       </c>
       <c r="R95" t="n">
-        <v>7018820</v>
+        <v>7018692</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10472,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129056683</v>
+        <v>129046062</v>
       </c>
       <c r="B96" t="n">
-        <v>91838</v>
+        <v>80148</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10483,37 +10483,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602739</v>
+        <v>602648</v>
       </c>
       <c r="R96" t="n">
-        <v>7018692</v>
+        <v>7018840</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10557,22 +10557,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B97" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10600,17 +10600,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R97" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10654,12 +10654,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
         <v>129046720</v>
       </c>
       <c r="B98" t="n">
-        <v>92183</v>
+        <v>92186</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>129045623</v>
       </c>
       <c r="B99" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>129058560</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>129056713</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>129045453</v>
       </c>
       <c r="B102" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>129044824</v>
       </c>
       <c r="B103" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>129044805</v>
       </c>
       <c r="B104" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045681</v>
+        <v>129056671</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11373,37 +11373,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>602667</v>
+        <v>602735</v>
       </c>
       <c r="R105" t="n">
-        <v>7018779</v>
+        <v>7018592</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11447,22 +11447,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129045582</v>
+        <v>129045681</v>
       </c>
       <c r="B106" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602703</v>
+        <v>602667</v>
       </c>
       <c r="R106" t="n">
-        <v>7018798</v>
+        <v>7018779</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11556,10 +11556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129056684</v>
+        <v>129045582</v>
       </c>
       <c r="B107" t="n">
-        <v>91838</v>
+        <v>80148</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11567,37 +11567,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602651</v>
+        <v>602703</v>
       </c>
       <c r="R107" t="n">
-        <v>7018826</v>
+        <v>7018798</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11641,22 +11641,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056671</v>
+        <v>129056693</v>
       </c>
       <c r="B108" t="n">
-        <v>91540</v>
+        <v>80148</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11664,21 +11664,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602735</v>
+        <v>602670</v>
       </c>
       <c r="R108" t="n">
-        <v>7018592</v>
+        <v>7018818</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11724,6 +11724,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11750,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056693</v>
+        <v>129056697</v>
       </c>
       <c r="B109" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11785,10 +11790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602670</v>
+        <v>602730</v>
       </c>
       <c r="R109" t="n">
-        <v>7018818</v>
+        <v>7018719</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11821,11 +11826,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11852,10 +11852,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056697</v>
+        <v>129056684</v>
       </c>
       <c r="B110" t="n">
-        <v>80146</v>
+        <v>91841</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11863,21 +11863,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602730</v>
+        <v>602651</v>
       </c>
       <c r="R110" t="n">
-        <v>7018719</v>
+        <v>7018826</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11952,7 +11952,7 @@
         <v>129050244</v>
       </c>
       <c r="B111" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129046525</v>
+        <v>129044298</v>
       </c>
       <c r="B112" t="n">
-        <v>91504</v>
+        <v>91996</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602669</v>
+        <v>602760</v>
       </c>
       <c r="R112" t="n">
-        <v>7018753</v>
+        <v>7018767</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129044298</v>
+        <v>129046525</v>
       </c>
       <c r="B113" t="n">
-        <v>91993</v>
+        <v>91507</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602760</v>
+        <v>602669</v>
       </c>
       <c r="R113" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12461,7 +12461,7 @@
         <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>129056702</v>
       </c>
       <c r="B118" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12749,10 +12749,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129044475</v>
+        <v>129056681</v>
       </c>
       <c r="B119" t="n">
-        <v>91560</v>
+        <v>91841</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12760,33 +12760,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602766</v>
+        <v>602736</v>
       </c>
       <c r="R119" t="n">
-        <v>7018781</v>
+        <v>7018593</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12830,44 +12834,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056681</v>
+        <v>129056704</v>
       </c>
       <c r="B120" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12877,10 +12881,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602736</v>
+        <v>602735</v>
       </c>
       <c r="R120" t="n">
-        <v>7018593</v>
+        <v>7018692</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12913,6 +12917,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12939,10 +12948,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129050601</v>
+        <v>129044475</v>
       </c>
       <c r="B121" t="n">
-        <v>10964</v>
+        <v>91563</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12950,38 +12959,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>101449</v>
+        <v>5432</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602698</v>
+        <v>602766</v>
       </c>
       <c r="R121" t="n">
-        <v>7018836</v>
+        <v>7018781</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13016,18 +13017,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Under bark, granlåga</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13039,55 +13034,59 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129056704</v>
+        <v>129050601</v>
       </c>
       <c r="B122" t="n">
-        <v>98706</v>
+        <v>10964</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602735</v>
+        <v>602698</v>
       </c>
       <c r="R122" t="n">
-        <v>7018692</v>
+        <v>7018836</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13121,7 +13120,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Under bark, granlåga</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13130,67 +13129,64 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129046716</v>
+        <v>129044962</v>
       </c>
       <c r="B123" t="n">
-        <v>98706</v>
+        <v>91507</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>602747</v>
+        <v>602750</v>
       </c>
       <c r="R123" t="n">
-        <v>7018722</v>
+        <v>7018799</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13249,45 +13245,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129044962</v>
+        <v>129046716</v>
       </c>
       <c r="B124" t="n">
-        <v>91504</v>
+        <v>98710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602750</v>
+        <v>602747</v>
       </c>
       <c r="R124" t="n">
-        <v>7018799</v>
+        <v>7018722</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B125" t="n">
-        <v>91838</v>
+        <v>80148</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13357,21 +13357,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R125" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13443,48 +13443,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129056700</v>
+        <v>129050404</v>
       </c>
       <c r="B126" t="n">
-        <v>80146</v>
+        <v>80177</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R126" t="n">
-        <v>7018776</v>
+        <v>7018808</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13528,60 +13528,60 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129050404</v>
+        <v>129056689</v>
       </c>
       <c r="B127" t="n">
-        <v>80175</v>
+        <v>91841</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602672</v>
+        <v>602754</v>
       </c>
       <c r="R127" t="n">
-        <v>7018808</v>
+        <v>7018806</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13625,12 +13625,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13640,7 +13640,7 @@
         <v>129056668</v>
       </c>
       <c r="B128" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>129045554</v>
       </c>
       <c r="B129" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>129045756</v>
       </c>
       <c r="B130" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>129050334</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14025,10 +14025,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129046455</v>
+        <v>129044406</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14036,21 +14036,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14060,10 +14060,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602667</v>
+        <v>602756</v>
       </c>
       <c r="R132" t="n">
-        <v>7018757</v>
+        <v>7018769</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14122,45 +14122,49 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B133" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R133" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14219,49 +14223,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129046891</v>
+        <v>129046455</v>
       </c>
       <c r="B134" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>602726</v>
+        <v>602667</v>
       </c>
       <c r="R134" t="n">
-        <v>7018723</v>
+        <v>7018757</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14320,48 +14320,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129056675</v>
+        <v>129045512</v>
       </c>
       <c r="B135" t="n">
-        <v>92258</v>
+        <v>91543</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602672</v>
+        <v>602682</v>
       </c>
       <c r="R135" t="n">
-        <v>7018832</v>
+        <v>7018827</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14405,22 +14405,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129056692</v>
+        <v>129045677</v>
       </c>
       <c r="B136" t="n">
-        <v>10964</v>
+        <v>91543</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14428,32 +14428,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602687</v>
+        <v>602684</v>
       </c>
       <c r="R136" t="n">
-        <v>7018836</v>
+        <v>7018786</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14497,22 +14502,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056694</v>
+        <v>129056667</v>
       </c>
       <c r="B137" t="n">
-        <v>80146</v>
+        <v>96956</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14520,21 +14525,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14544,10 +14549,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602656</v>
+        <v>602672</v>
       </c>
       <c r="R137" t="n">
-        <v>7018656</v>
+        <v>7018807</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14606,48 +14611,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129045677</v>
+        <v>129056675</v>
       </c>
       <c r="B138" t="n">
-        <v>91540</v>
+        <v>92261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>602684</v>
+        <v>602672</v>
       </c>
       <c r="R138" t="n">
-        <v>7018786</v>
+        <v>7018832</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14691,22 +14696,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129045512</v>
+        <v>129056694</v>
       </c>
       <c r="B139" t="n">
-        <v>91540</v>
+        <v>80148</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14714,37 +14719,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602682</v>
+        <v>602656</v>
       </c>
       <c r="R139" t="n">
-        <v>7018827</v>
+        <v>7018656</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14788,22 +14793,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056667</v>
+        <v>129056692</v>
       </c>
       <c r="B140" t="n">
-        <v>96952</v>
+        <v>10964</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14811,21 +14816,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>53</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602672</v>
+        <v>602687</v>
       </c>
       <c r="R140" t="n">
-        <v>7018807</v>
+        <v>7018836</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14897,10 +14897,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129056705</v>
+        <v>129046813</v>
       </c>
       <c r="B141" t="n">
-        <v>56908</v>
+        <v>91103</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14908,37 +14908,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>102612</v>
+        <v>937</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602730</v>
+        <v>602732</v>
       </c>
       <c r="R141" t="n">
-        <v>7018719</v>
+        <v>7018701</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14968,11 +14968,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14987,22 +14982,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129046813</v>
+        <v>129048944</v>
       </c>
       <c r="B142" t="n">
-        <v>91100</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15010,34 +15005,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>937</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602732</v>
+        <v>602734</v>
       </c>
       <c r="R142" t="n">
-        <v>7018701</v>
+        <v>7018579</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -15070,6 +15070,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15096,10 +15101,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129048944</v>
+        <v>129056705</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15107,16 +15112,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15125,24 +15130,19 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602734</v>
+        <v>602730</v>
       </c>
       <c r="R143" t="n">
-        <v>7018579</v>
+        <v>7018719</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15191,12 +15191,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
         <v>129056679</v>
       </c>
       <c r="B144" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>129056695</v>
       </c>
       <c r="B145" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>129056696</v>
       </c>
       <c r="B146" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15494,49 +15494,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129045069</v>
+        <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>602751</v>
+        <v>602748</v>
       </c>
       <c r="R147" t="n">
-        <v>7018815</v>
+        <v>7018591</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15595,10 +15591,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129046445</v>
+        <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15634,10 +15630,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>602669</v>
+        <v>602751</v>
       </c>
       <c r="R148" t="n">
-        <v>7018754</v>
+        <v>7018815</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15696,45 +15692,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129048489</v>
+        <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>602748</v>
+        <v>602669</v>
       </c>
       <c r="R149" t="n">
-        <v>7018591</v>
+        <v>7018754</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15793,32 +15793,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129044697</v>
+        <v>129046543</v>
       </c>
       <c r="B150" t="n">
-        <v>80106</v>
+        <v>90575</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229497</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15828,10 +15828,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602730</v>
+        <v>602686</v>
       </c>
       <c r="R150" t="n">
-        <v>7018771</v>
+        <v>7018745</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15890,10 +15890,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B151" t="n">
-        <v>90572</v>
+        <v>91841</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15901,21 +15901,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15925,10 +15925,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R151" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15987,32 +15987,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129046382</v>
+        <v>129044697</v>
       </c>
       <c r="B152" t="n">
-        <v>91838</v>
+        <v>80108</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16022,10 +16022,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>602637</v>
+        <v>602730</v>
       </c>
       <c r="R152" t="n">
-        <v>7018802</v>
+        <v>7018771</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>129056716</v>
       </c>
       <c r="B153" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16181,32 +16181,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129044275</v>
+        <v>129045378</v>
       </c>
       <c r="B154" t="n">
-        <v>91838</v>
+        <v>92261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602766</v>
+        <v>602682</v>
       </c>
       <c r="R154" t="n">
-        <v>7018767</v>
+        <v>7018833</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16278,49 +16278,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129048151</v>
+        <v>129044275</v>
       </c>
       <c r="B155" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602715</v>
+        <v>602766</v>
       </c>
       <c r="R155" t="n">
-        <v>7018634</v>
+        <v>7018767</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16379,45 +16375,49 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129050391</v>
+        <v>129048151</v>
       </c>
       <c r="B156" t="n">
-        <v>80050</v>
+        <v>98710</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602671</v>
+        <v>602715</v>
       </c>
       <c r="R156" t="n">
-        <v>7018809</v>
+        <v>7018634</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16476,48 +16476,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129056714</v>
+        <v>129050391</v>
       </c>
       <c r="B157" t="n">
-        <v>79041</v>
+        <v>80052</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602678</v>
+        <v>602671</v>
       </c>
       <c r="R157" t="n">
-        <v>7018771</v>
+        <v>7018809</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16561,60 +16561,60 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129045378</v>
+        <v>129056714</v>
       </c>
       <c r="B158" t="n">
-        <v>92258</v>
+        <v>79043</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602682</v>
+        <v>602678</v>
       </c>
       <c r="R158" t="n">
-        <v>7018833</v>
+        <v>7018771</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16658,12 +16658,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -16762,10 +16762,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129056685</v>
+        <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16773,37 +16773,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>602683</v>
+        <v>602728</v>
       </c>
       <c r="R160" t="n">
-        <v>7018835</v>
+        <v>7018716</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16847,64 +16847,60 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129058444</v>
+        <v>129045867</v>
       </c>
       <c r="B161" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>602760</v>
+        <v>602663</v>
       </c>
       <c r="R161" t="n">
-        <v>7018673</v>
+        <v>7018805</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16942,19 +16938,18 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -16964,7 +16959,7 @@
         <v>129044553</v>
       </c>
       <c r="B162" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17062,10 +17057,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129047010</v>
+        <v>129056685</v>
       </c>
       <c r="B163" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17073,37 +17068,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>602728</v>
+        <v>602683</v>
       </c>
       <c r="R163" t="n">
-        <v>7018716</v>
+        <v>7018835</v>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17147,60 +17142,64 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129045867</v>
+        <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>602663</v>
+        <v>602760</v>
       </c>
       <c r="R164" t="n">
-        <v>7018805</v>
+        <v>7018673</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17238,28 +17237,29 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129048297</v>
+        <v>129046627</v>
       </c>
       <c r="B165" t="n">
-        <v>91838</v>
+        <v>78800</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17267,21 +17267,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17291,10 +17291,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602752</v>
+        <v>602705</v>
       </c>
       <c r="R165" t="n">
-        <v>7018614</v>
+        <v>7018763</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17353,10 +17353,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129046627</v>
+        <v>129046592</v>
       </c>
       <c r="B166" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17364,34 +17364,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602705</v>
+        <v>602704</v>
       </c>
       <c r="R166" t="n">
-        <v>7018763</v>
+        <v>7018751</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17424,6 +17429,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17450,10 +17460,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129046592</v>
+        <v>129048297</v>
       </c>
       <c r="B167" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17461,39 +17471,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602704</v>
+        <v>602752</v>
       </c>
       <c r="R167" t="n">
-        <v>7018751</v>
+        <v>7018614</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17526,11 +17531,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17560,7 +17560,7 @@
         <v>129044893</v>
       </c>
       <c r="B168" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>129056666</v>
       </c>
       <c r="B170" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>129056678</v>
       </c>
       <c r="B171" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -7163,48 +7163,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129056720</v>
       </c>
       <c r="B62" t="n">
-        <v>91841</v>
+        <v>80183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602773</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018642</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,22 +7248,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129056720</v>
+        <v>129045225</v>
       </c>
       <c r="B63" t="n">
-        <v>80183</v>
+        <v>97581</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,37 +7271,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602773</v>
+        <v>602705</v>
       </c>
       <c r="R63" t="n">
-        <v>7018642</v>
+        <v>7018799</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7345,44 +7345,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129048001</v>
+        <v>129050367</v>
       </c>
       <c r="B64" t="n">
-        <v>91996</v>
+        <v>80108</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602696</v>
+        <v>602671</v>
       </c>
       <c r="R64" t="n">
-        <v>7018662</v>
+        <v>7018809</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7454,32 +7454,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129045225</v>
+        <v>129048001</v>
       </c>
       <c r="B65" t="n">
-        <v>97581</v>
+        <v>91996</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602705</v>
+        <v>602696</v>
       </c>
       <c r="R65" t="n">
-        <v>7018799</v>
+        <v>7018662</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129050367</v>
+        <v>129048977</v>
       </c>
       <c r="B66" t="n">
-        <v>80108</v>
+        <v>91841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602671</v>
+        <v>602712</v>
       </c>
       <c r="R66" t="n">
-        <v>7018809</v>
+        <v>7018600</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7648,32 +7648,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045343</v>
+        <v>129044277</v>
       </c>
       <c r="B67" t="n">
-        <v>91966</v>
+        <v>91543</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602684</v>
+        <v>602759</v>
       </c>
       <c r="R67" t="n">
-        <v>7018837</v>
+        <v>7018767</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7719,11 +7719,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7750,10 +7745,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129044277</v>
+        <v>129056715</v>
       </c>
       <c r="B68" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7761,37 +7756,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602759</v>
+        <v>602665</v>
       </c>
       <c r="R68" t="n">
-        <v>7018767</v>
+        <v>7018777</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7835,44 +7830,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045733</v>
+        <v>129050732</v>
       </c>
       <c r="B69" t="n">
-        <v>80177</v>
+        <v>91841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602669</v>
+        <v>602710</v>
       </c>
       <c r="R69" t="n">
-        <v>7018781</v>
+        <v>7018856</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8138,7 +8133,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056715</v>
+        <v>129056712</v>
       </c>
       <c r="B72" t="n">
         <v>79043</v>
@@ -8173,10 +8168,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602665</v>
+        <v>602730</v>
       </c>
       <c r="R72" t="n">
-        <v>7018777</v>
+        <v>7018697</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8235,48 +8230,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056712</v>
+        <v>129045343</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>91966</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602730</v>
+        <v>602684</v>
       </c>
       <c r="R73" t="n">
-        <v>7018697</v>
+        <v>7018837</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8306,6 +8301,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8320,44 +8320,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129050732</v>
+        <v>129045733</v>
       </c>
       <c r="B74" t="n">
-        <v>91841</v>
+        <v>80177</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602710</v>
+        <v>602669</v>
       </c>
       <c r="R74" t="n">
-        <v>7018856</v>
+        <v>7018781</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129046472</v>
+        <v>129056676</v>
       </c>
       <c r="B75" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,37 +8440,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602666</v>
+        <v>602667</v>
       </c>
       <c r="R75" t="n">
-        <v>7018759</v>
+        <v>7018779</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,6 +8500,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8514,44 +8519,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129044345</v>
+        <v>129046472</v>
       </c>
       <c r="B76" t="n">
-        <v>91756</v>
+        <v>91841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,7 +8566,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602772</v>
+        <v>602666</v>
       </c>
       <c r="R76" t="n">
         <v>7018759</v>
@@ -8623,32 +8628,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129049465</v>
+        <v>129044345</v>
       </c>
       <c r="B77" t="n">
-        <v>80148</v>
+        <v>91756</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8658,10 +8663,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602650</v>
+        <v>602772</v>
       </c>
       <c r="R77" t="n">
-        <v>7018649</v>
+        <v>7018759</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8720,7 +8725,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129045649</v>
+        <v>129049465</v>
       </c>
       <c r="B78" t="n">
         <v>80148</v>
@@ -8755,10 +8760,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602688</v>
+        <v>602650</v>
       </c>
       <c r="R78" t="n">
-        <v>7018774</v>
+        <v>7018649</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8817,10 +8822,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056718</v>
+        <v>129045649</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,37 +8833,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602758</v>
+        <v>602688</v>
       </c>
       <c r="R79" t="n">
-        <v>7018806</v>
+        <v>7018774</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8902,22 +8907,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056699</v>
+        <v>129056718</v>
       </c>
       <c r="B80" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8925,21 +8930,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8949,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602729</v>
+        <v>602758</v>
       </c>
       <c r="R80" t="n">
-        <v>7018756</v>
+        <v>7018806</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9011,10 +9016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056676</v>
+        <v>129056699</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>602667</v>
+        <v>602729</v>
       </c>
       <c r="R81" t="n">
-        <v>7018779</v>
+        <v>7018756</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9082,11 +9087,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9113,32 +9113,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129046057</v>
+        <v>129045508</v>
       </c>
       <c r="B82" t="n">
-        <v>80108</v>
+        <v>91841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602648</v>
+        <v>602674</v>
       </c>
       <c r="R82" t="n">
-        <v>7018840</v>
+        <v>7018842</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129056687</v>
+        <v>129048233</v>
       </c>
       <c r="B83" t="n">
-        <v>91841</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9221,37 +9221,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>602733</v>
+        <v>602744</v>
       </c>
       <c r="R83" t="n">
-        <v>7018822</v>
+        <v>7018615</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9295,64 +9295,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129058573</v>
+        <v>129048100</v>
       </c>
       <c r="B84" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>602756</v>
+        <v>602670</v>
       </c>
       <c r="R84" t="n">
-        <v>7018669</v>
+        <v>7018643</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9390,51 +9386,50 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129045508</v>
+        <v>129046057</v>
       </c>
       <c r="B85" t="n">
-        <v>91841</v>
+        <v>80108</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9444,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602674</v>
+        <v>602648</v>
       </c>
       <c r="R85" t="n">
-        <v>7018842</v>
+        <v>7018840</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9506,10 +9501,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129048233</v>
+        <v>129056687</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>91841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9517,37 +9512,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602744</v>
+        <v>602733</v>
       </c>
       <c r="R86" t="n">
-        <v>7018615</v>
+        <v>7018822</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9591,60 +9586,64 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129048100</v>
+        <v>129058573</v>
       </c>
       <c r="B87" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602670</v>
+        <v>602756</v>
       </c>
       <c r="R87" t="n">
-        <v>7018643</v>
+        <v>7018669</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9682,18 +9681,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129056709</v>
+        <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>91563</v>
+        <v>80148</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10196,33 +10196,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>602654</v>
+        <v>602648</v>
       </c>
       <c r="R93" t="n">
-        <v>7018820</v>
+        <v>7018840</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10266,19 +10270,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129056698</v>
+        <v>129048547</v>
       </c>
       <c r="B94" t="n">
         <v>80148</v>
@@ -10309,17 +10313,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>602735</v>
+        <v>602747</v>
       </c>
       <c r="R94" t="n">
-        <v>7018716</v>
+        <v>7018592</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10363,22 +10367,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129056683</v>
+        <v>129056709</v>
       </c>
       <c r="B95" t="n">
-        <v>91841</v>
+        <v>91563</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10386,23 +10390,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>602739</v>
+        <v>602654</v>
       </c>
       <c r="R95" t="n">
-        <v>7018692</v>
+        <v>7018820</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10472,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129046062</v>
+        <v>129056683</v>
       </c>
       <c r="B96" t="n">
-        <v>80148</v>
+        <v>91841</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10483,37 +10483,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>602648</v>
+        <v>602739</v>
       </c>
       <c r="R96" t="n">
-        <v>7018840</v>
+        <v>7018692</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10557,19 +10557,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129048547</v>
+        <v>129056698</v>
       </c>
       <c r="B97" t="n">
         <v>80148</v>
@@ -10600,17 +10600,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>602747</v>
+        <v>602735</v>
       </c>
       <c r="R97" t="n">
-        <v>7018592</v>
+        <v>7018716</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10654,12 +10654,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129044298</v>
+        <v>129046525</v>
       </c>
       <c r="B112" t="n">
-        <v>91996</v>
+        <v>91507</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>602760</v>
+        <v>602669</v>
       </c>
       <c r="R112" t="n">
-        <v>7018767</v>
+        <v>7018753</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129046525</v>
+        <v>129044298</v>
       </c>
       <c r="B113" t="n">
-        <v>91507</v>
+        <v>91996</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>602669</v>
+        <v>602760</v>
       </c>
       <c r="R113" t="n">
-        <v>7018753</v>
+        <v>7018767</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12652,10 +12652,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129056702</v>
+        <v>129044475</v>
       </c>
       <c r="B118" t="n">
-        <v>80148</v>
+        <v>91563</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12663,37 +12663,33 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602649</v>
+        <v>602766</v>
       </c>
       <c r="R118" t="n">
-        <v>7018829</v>
+        <v>7018781</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12737,22 +12733,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B119" t="n">
-        <v>91841</v>
+        <v>80148</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12760,21 +12756,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12784,10 +12780,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R119" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12846,32 +12842,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056704</v>
+        <v>129056681</v>
       </c>
       <c r="B120" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12881,10 +12877,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602735</v>
+        <v>602736</v>
       </c>
       <c r="R120" t="n">
-        <v>7018692</v>
+        <v>7018593</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12917,11 +12913,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12948,44 +12939,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129044475</v>
+        <v>129056704</v>
       </c>
       <c r="B121" t="n">
-        <v>91563</v>
+        <v>98710</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602766</v>
+        <v>602735</v>
       </c>
       <c r="R121" t="n">
-        <v>7018781</v>
+        <v>7018692</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13015,6 +13010,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13029,12 +13029,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056700</v>
+        <v>129056689</v>
       </c>
       <c r="B125" t="n">
-        <v>80148</v>
+        <v>91841</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13357,21 +13357,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602684</v>
+        <v>602754</v>
       </c>
       <c r="R125" t="n">
-        <v>7018776</v>
+        <v>7018806</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13443,10 +13443,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129050404</v>
+        <v>129056668</v>
       </c>
       <c r="B126" t="n">
-        <v>80177</v>
+        <v>91507</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13454,37 +13454,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>602672</v>
+        <v>602738</v>
       </c>
       <c r="R126" t="n">
-        <v>7018808</v>
+        <v>7018795</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13528,22 +13528,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B127" t="n">
-        <v>91841</v>
+        <v>80148</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13551,21 +13551,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13575,10 +13575,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R127" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13637,10 +13637,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129056668</v>
+        <v>129050404</v>
       </c>
       <c r="B128" t="n">
-        <v>91507</v>
+        <v>80177</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13648,37 +13648,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602738</v>
+        <v>602672</v>
       </c>
       <c r="R128" t="n">
-        <v>7018795</v>
+        <v>7018808</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13722,12 +13722,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6775,32 +6775,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045323</v>
+        <v>129045660</v>
       </c>
       <c r="B58" t="n">
-        <v>91841</v>
+        <v>80053</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R58" t="n">
-        <v>7018848</v>
+        <v>7018786</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6872,32 +6872,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045660</v>
+        <v>129045323</v>
       </c>
       <c r="B59" t="n">
-        <v>80052</v>
+        <v>91843</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602684</v>
+        <v>602682</v>
       </c>
       <c r="R59" t="n">
-        <v>7018786</v>
+        <v>7018848</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129056682</v>
+        <v>129056690</v>
       </c>
       <c r="B60" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602751</v>
+        <v>602758</v>
       </c>
       <c r="R60" t="n">
-        <v>7018603</v>
+        <v>7018806</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056690</v>
+        <v>129056682</v>
       </c>
       <c r="B61" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602758</v>
+        <v>602751</v>
       </c>
       <c r="R61" t="n">
-        <v>7018806</v>
+        <v>7018603</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7163,48 +7163,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129056720</v>
+        <v>129048977</v>
       </c>
       <c r="B62" t="n">
-        <v>80183</v>
+        <v>91843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602773</v>
+        <v>602712</v>
       </c>
       <c r="R62" t="n">
-        <v>7018642</v>
+        <v>7018600</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,44 +7248,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129045225</v>
+        <v>129048001</v>
       </c>
       <c r="B63" t="n">
-        <v>97581</v>
+        <v>91998</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602705</v>
+        <v>602696</v>
       </c>
       <c r="R63" t="n">
-        <v>7018799</v>
+        <v>7018662</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129050367</v>
+        <v>129056720</v>
       </c>
       <c r="B64" t="n">
-        <v>80108</v>
+        <v>80184</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,37 +7368,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602671</v>
+        <v>602773</v>
       </c>
       <c r="R64" t="n">
-        <v>7018809</v>
+        <v>7018642</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7442,44 +7442,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129048001</v>
+        <v>129045225</v>
       </c>
       <c r="B65" t="n">
-        <v>91996</v>
+        <v>97583</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602696</v>
+        <v>602705</v>
       </c>
       <c r="R65" t="n">
-        <v>7018662</v>
+        <v>7018799</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7551,32 +7551,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129048977</v>
+        <v>129050367</v>
       </c>
       <c r="B66" t="n">
-        <v>91841</v>
+        <v>80109</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602712</v>
+        <v>602671</v>
       </c>
       <c r="R66" t="n">
-        <v>7018600</v>
+        <v>7018809</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7651,7 +7651,7 @@
         <v>129044277</v>
       </c>
       <c r="B67" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7745,32 +7745,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129056715</v>
+        <v>129056680</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>91998</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602665</v>
+        <v>602732</v>
       </c>
       <c r="R68" t="n">
-        <v>7018777</v>
+        <v>7018811</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129050732</v>
+        <v>129056672</v>
       </c>
       <c r="B69" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7853,37 +7853,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602710</v>
+        <v>602651</v>
       </c>
       <c r="R69" t="n">
-        <v>7018856</v>
+        <v>7018826</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7927,60 +7927,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129056680</v>
+        <v>129050732</v>
       </c>
       <c r="B70" t="n">
-        <v>91996</v>
+        <v>91843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602732</v>
+        <v>602710</v>
       </c>
       <c r="R70" t="n">
-        <v>7018811</v>
+        <v>7018856</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8024,60 +8024,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129056672</v>
+        <v>129045343</v>
       </c>
       <c r="B71" t="n">
-        <v>91543</v>
+        <v>91968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602651</v>
+        <v>602684</v>
       </c>
       <c r="R71" t="n">
-        <v>7018826</v>
+        <v>7018837</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8107,6 +8107,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8121,60 +8126,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129056712</v>
+        <v>129045733</v>
       </c>
       <c r="B72" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602730</v>
+        <v>602669</v>
       </c>
       <c r="R72" t="n">
-        <v>7018697</v>
+        <v>7018781</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8218,60 +8223,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129045343</v>
+        <v>129056715</v>
       </c>
       <c r="B73" t="n">
-        <v>91966</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602684</v>
+        <v>602665</v>
       </c>
       <c r="R73" t="n">
-        <v>7018837</v>
+        <v>7018777</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8301,11 +8306,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8320,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129045733</v>
+        <v>129056712</v>
       </c>
       <c r="B74" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602669</v>
+        <v>602730</v>
       </c>
       <c r="R74" t="n">
-        <v>7018781</v>
+        <v>7018697</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,22 +8417,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129056676</v>
+        <v>129049465</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,37 +8440,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602667</v>
+        <v>602650</v>
       </c>
       <c r="R75" t="n">
-        <v>7018779</v>
+        <v>7018649</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,11 +8500,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8519,22 +8514,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129046472</v>
+        <v>129045649</v>
       </c>
       <c r="B76" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8542,21 +8537,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8566,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602666</v>
+        <v>602688</v>
       </c>
       <c r="R76" t="n">
-        <v>7018759</v>
+        <v>7018774</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8631,7 +8626,7 @@
         <v>129044345</v>
       </c>
       <c r="B77" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8725,10 +8720,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129049465</v>
+        <v>129046472</v>
       </c>
       <c r="B78" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8736,21 +8731,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8760,10 +8755,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602650</v>
+        <v>602666</v>
       </c>
       <c r="R78" t="n">
-        <v>7018649</v>
+        <v>7018759</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8822,10 +8817,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129045649</v>
+        <v>129056676</v>
       </c>
       <c r="B79" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8833,37 +8828,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602688</v>
+        <v>602667</v>
       </c>
       <c r="R79" t="n">
-        <v>7018774</v>
+        <v>7018779</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8893,6 +8888,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,12 +8907,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8922,7 +8922,7 @@
         <v>129056718</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>129056699</v>
       </c>
       <c r="B81" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129045508</v>
+        <v>129046057</v>
       </c>
       <c r="B82" t="n">
-        <v>91841</v>
+        <v>80109</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>602674</v>
+        <v>602648</v>
       </c>
       <c r="R82" t="n">
-        <v>7018842</v>
+        <v>7018840</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9213,7 +9213,7 @@
         <v>129048233</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>129048100</v>
       </c>
       <c r="B84" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9404,48 +9404,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129046057</v>
+        <v>129056687</v>
       </c>
       <c r="B85" t="n">
-        <v>80108</v>
+        <v>91843</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>602648</v>
+        <v>602733</v>
       </c>
       <c r="R85" t="n">
-        <v>7018840</v>
+        <v>7018822</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9489,57 +9489,61 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129056687</v>
+        <v>129058573</v>
       </c>
       <c r="B86" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>602733</v>
+        <v>602756</v>
       </c>
       <c r="R86" t="n">
-        <v>7018822</v>
+        <v>7018669</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9580,6 +9584,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9598,52 +9603,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058573</v>
+        <v>129045508</v>
       </c>
       <c r="B87" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>602756</v>
+        <v>602674</v>
       </c>
       <c r="R87" t="n">
-        <v>7018669</v>
+        <v>7018842</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9681,29 +9682,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129056711</v>
+        <v>129056688</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9711,21 +9711,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>602771</v>
+        <v>602732</v>
       </c>
       <c r="R88" t="n">
-        <v>7018641</v>
+        <v>7018811</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9800,7 +9800,7 @@
         <v>129056686</v>
       </c>
       <c r="B89" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129056688</v>
+        <v>129056711</v>
       </c>
       <c r="B90" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>602732</v>
+        <v>602771</v>
       </c>
       <c r="R90" t="n">
-        <v>7018811</v>
+        <v>7018641</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129044846</v>
+        <v>129048130</v>
       </c>
       <c r="B91" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10002,21 +10002,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>602719</v>
+        <v>602704</v>
       </c>
       <c r="R91" t="n">
-        <v>7018813</v>
+        <v>7018634</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129048130</v>
+        <v>129044846</v>
       </c>
       <c r="B92" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10099,21 +10099,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>602704</v>
+        <v>602719</v>
       </c>
       <c r="R92" t="n">
-        <v>7018634</v>
+        <v>7018813</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10188,7 +10188,7 @@
         <v>129046062</v>
       </c>
       <c r="B93" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>129048547</v>
       </c>
       <c r="B94" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>129056709</v>
       </c>
       <c r="B95" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>129056683</v>
       </c>
       <c r="B96" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>129056698</v>
       </c>
       <c r="B97" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10666,32 +10666,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129046720</v>
+        <v>129058560</v>
       </c>
       <c r="B98" t="n">
-        <v>92186</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>483</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10700,17 +10700,17 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>602747</v>
+        <v>602760</v>
       </c>
       <c r="R98" t="n">
-        <v>7018721</v>
+        <v>7018673</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10740,11 +10740,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10760,64 +10755,60 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129045623</v>
+        <v>129056713</v>
       </c>
       <c r="B99" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>602687</v>
+        <v>602690</v>
       </c>
       <c r="R99" t="n">
-        <v>7018769</v>
+        <v>7018768</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10861,44 +10852,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058560</v>
+        <v>129046720</v>
       </c>
       <c r="B100" t="n">
-        <v>79043</v>
+        <v>92188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10907,17 +10898,17 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>602760</v>
+        <v>602747</v>
       </c>
       <c r="R100" t="n">
-        <v>7018673</v>
+        <v>7018721</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10947,6 +10938,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10962,60 +10958,64 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129056713</v>
+        <v>129045623</v>
       </c>
       <c r="B101" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>602690</v>
+        <v>602687</v>
       </c>
       <c r="R101" t="n">
-        <v>7018768</v>
+        <v>7018769</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11059,22 +11059,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045453</v>
+        <v>129056697</v>
       </c>
       <c r="B102" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11082,37 +11082,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>602673</v>
+        <v>602730</v>
       </c>
       <c r="R102" t="n">
-        <v>7018844</v>
+        <v>7018719</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11156,22 +11156,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129044824</v>
+        <v>129056693</v>
       </c>
       <c r="B103" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11179,37 +11179,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>602731</v>
+        <v>602670</v>
       </c>
       <c r="R103" t="n">
-        <v>7018789</v>
+        <v>7018818</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11239,6 +11239,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11253,22 +11258,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044805</v>
+        <v>129056684</v>
       </c>
       <c r="B104" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11296,17 +11301,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>602747</v>
+        <v>602651</v>
       </c>
       <c r="R104" t="n">
-        <v>7018784</v>
+        <v>7018826</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11350,12 +11355,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11365,7 +11370,7 @@
         <v>129056671</v>
       </c>
       <c r="B105" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11459,45 +11464,49 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129045681</v>
+        <v>129050244</v>
       </c>
       <c r="B106" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>602667</v>
+        <v>602665</v>
       </c>
       <c r="R106" t="n">
-        <v>7018779</v>
+        <v>7018784</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11556,10 +11565,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129045582</v>
+        <v>129045453</v>
       </c>
       <c r="B107" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11567,21 +11576,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11600,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>602703</v>
+        <v>602673</v>
       </c>
       <c r="R107" t="n">
-        <v>7018798</v>
+        <v>7018844</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11653,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129056693</v>
+        <v>129044824</v>
       </c>
       <c r="B108" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11664,37 +11673,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>602670</v>
+        <v>602731</v>
       </c>
       <c r="R108" t="n">
-        <v>7018818</v>
+        <v>7018789</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11724,11 +11733,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11743,22 +11747,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129056697</v>
+        <v>129044805</v>
       </c>
       <c r="B109" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11766,37 +11770,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>602730</v>
+        <v>602747</v>
       </c>
       <c r="R109" t="n">
-        <v>7018719</v>
+        <v>7018784</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11840,22 +11844,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129056684</v>
+        <v>129045681</v>
       </c>
       <c r="B110" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11863,37 +11867,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>602651</v>
+        <v>602667</v>
       </c>
       <c r="R110" t="n">
-        <v>7018826</v>
+        <v>7018779</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11937,61 +11941,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129050244</v>
+        <v>129045582</v>
       </c>
       <c r="B111" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>602665</v>
+        <v>602703</v>
       </c>
       <c r="R111" t="n">
-        <v>7018784</v>
+        <v>7018798</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12053,7 +12053,7 @@
         <v>129046525</v>
       </c>
       <c r="B112" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>129044298</v>
       </c>
       <c r="B113" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>129044719</v>
       </c>
       <c r="B116" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>129056708</v>
       </c>
       <c r="B117" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12652,10 +12652,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129044475</v>
+        <v>129050601</v>
       </c>
       <c r="B118" t="n">
-        <v>91563</v>
+        <v>10964</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12663,30 +12663,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Olisthaerus substriatus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>602766</v>
+        <v>602698</v>
       </c>
       <c r="R118" t="n">
-        <v>7018781</v>
+        <v>7018836</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12721,12 +12729,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Under bark, granlåga</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12738,17 +12752,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Daniel Rutschman, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129056702</v>
+        <v>129044475</v>
       </c>
       <c r="B119" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12756,37 +12770,33 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>602649</v>
+        <v>602766</v>
       </c>
       <c r="R119" t="n">
-        <v>7018829</v>
+        <v>7018781</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12830,22 +12840,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129056681</v>
+        <v>129056702</v>
       </c>
       <c r="B120" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12853,21 +12863,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12877,10 +12887,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>602736</v>
+        <v>602649</v>
       </c>
       <c r="R120" t="n">
-        <v>7018593</v>
+        <v>7018829</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12939,32 +12949,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129056704</v>
+        <v>129056681</v>
       </c>
       <c r="B121" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12974,10 +12984,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>602735</v>
+        <v>602736</v>
       </c>
       <c r="R121" t="n">
-        <v>7018692</v>
+        <v>7018593</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13010,11 +13020,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13041,52 +13046,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129050601</v>
+        <v>129056704</v>
       </c>
       <c r="B122" t="n">
-        <v>10964</v>
+        <v>98712</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>101449</v>
+        <v>220787</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>602698</v>
+        <v>602735</v>
       </c>
       <c r="R122" t="n">
-        <v>7018836</v>
+        <v>7018692</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13120,7 +13121,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Under bark, granlåga</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13129,19 +13130,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13151,7 +13151,7 @@
         <v>129044962</v>
       </c>
       <c r="B123" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13245,49 +13245,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129046716</v>
+        <v>129050404</v>
       </c>
       <c r="B124" t="n">
-        <v>98710</v>
+        <v>80178</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>602747</v>
+        <v>602672</v>
       </c>
       <c r="R124" t="n">
-        <v>7018722</v>
+        <v>7018808</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -13346,10 +13342,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129056689</v>
+        <v>129056700</v>
       </c>
       <c r="B125" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13357,21 +13353,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13381,10 +13377,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>602754</v>
+        <v>602684</v>
       </c>
       <c r="R125" t="n">
-        <v>7018806</v>
+        <v>7018776</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13446,7 +13442,7 @@
         <v>129056668</v>
       </c>
       <c r="B126" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13540,10 +13536,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129056700</v>
+        <v>129056689</v>
       </c>
       <c r="B127" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13551,21 +13547,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13575,10 +13571,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>602684</v>
+        <v>602754</v>
       </c>
       <c r="R127" t="n">
-        <v>7018776</v>
+        <v>7018806</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13637,45 +13633,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129050404</v>
+        <v>129046716</v>
       </c>
       <c r="B128" t="n">
-        <v>80177</v>
+        <v>98712</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>602672</v>
+        <v>602747</v>
       </c>
       <c r="R128" t="n">
-        <v>7018808</v>
+        <v>7018722</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129045554</v>
+        <v>129045756</v>
       </c>
       <c r="B129" t="n">
-        <v>80148</v>
+        <v>80109</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>602696</v>
+        <v>602663</v>
       </c>
       <c r="R129" t="n">
         <v>7018818</v>
@@ -13831,32 +13831,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129045756</v>
+        <v>129050334</v>
       </c>
       <c r="B130" t="n">
-        <v>80108</v>
+        <v>80149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13866,10 +13866,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>602663</v>
+        <v>602671</v>
       </c>
       <c r="R130" t="n">
-        <v>7018818</v>
+        <v>7018809</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13928,10 +13928,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129050334</v>
+        <v>129045554</v>
       </c>
       <c r="B131" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>602671</v>
+        <v>602696</v>
       </c>
       <c r="R131" t="n">
-        <v>7018809</v>
+        <v>7018818</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14025,45 +14025,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129044406</v>
+        <v>129046891</v>
       </c>
       <c r="B132" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>602756</v>
+        <v>602726</v>
       </c>
       <c r="R132" t="n">
-        <v>7018769</v>
+        <v>7018723</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14122,52 +14126,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129046891</v>
+        <v>129056675</v>
       </c>
       <c r="B133" t="n">
-        <v>98710</v>
+        <v>92263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>602726</v>
+        <v>602672</v>
       </c>
       <c r="R133" t="n">
-        <v>7018723</v>
+        <v>7018832</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14211,12 +14211,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14226,7 +14226,7 @@
         <v>129046455</v>
       </c>
       <c r="B134" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14320,10 +14320,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129045512</v>
+        <v>129045677</v>
       </c>
       <c r="B135" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>602682</v>
+        <v>602684</v>
       </c>
       <c r="R135" t="n">
-        <v>7018827</v>
+        <v>7018786</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129045677</v>
+        <v>129045512</v>
       </c>
       <c r="B136" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>602684</v>
+        <v>602682</v>
       </c>
       <c r="R136" t="n">
-        <v>7018786</v>
+        <v>7018827</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14514,10 +14514,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129056667</v>
+        <v>129044406</v>
       </c>
       <c r="B137" t="n">
-        <v>96956</v>
+        <v>80149</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14525,37 +14525,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R137" t="n">
-        <v>7018807</v>
+        <v>7018769</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14599,44 +14599,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129056675</v>
+        <v>129056667</v>
       </c>
       <c r="B138" t="n">
-        <v>92261</v>
+        <v>96958</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14649,7 +14649,7 @@
         <v>602672</v>
       </c>
       <c r="R138" t="n">
-        <v>7018832</v>
+        <v>7018807</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14708,10 +14708,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129056694</v>
+        <v>129056692</v>
       </c>
       <c r="B139" t="n">
-        <v>80148</v>
+        <v>10964</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14719,21 +14719,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14743,10 +14738,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>602656</v>
+        <v>602687</v>
       </c>
       <c r="R139" t="n">
-        <v>7018656</v>
+        <v>7018836</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14805,10 +14800,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129056692</v>
+        <v>129056694</v>
       </c>
       <c r="B140" t="n">
-        <v>10964</v>
+        <v>80149</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14816,16 +14811,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>602687</v>
+        <v>602656</v>
       </c>
       <c r="R140" t="n">
-        <v>7018836</v>
+        <v>7018656</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14897,10 +14897,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129046813</v>
+        <v>129048944</v>
       </c>
       <c r="B141" t="n">
-        <v>91103</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14908,34 +14908,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>937</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>602732</v>
+        <v>602734</v>
       </c>
       <c r="R141" t="n">
-        <v>7018701</v>
+        <v>7018579</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14968,6 +14973,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14994,10 +15004,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129048944</v>
+        <v>129046813</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>91105</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15005,39 +15015,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>937</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>602734</v>
+        <v>602732</v>
       </c>
       <c r="R142" t="n">
-        <v>7018579</v>
+        <v>7018701</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -15070,11 +15075,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15101,10 +15101,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129056705</v>
+        <v>129056695</v>
       </c>
       <c r="B143" t="n">
-        <v>56908</v>
+        <v>80149</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15112,21 +15112,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15136,10 +15136,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>602730</v>
+        <v>602754</v>
       </c>
       <c r="R143" t="n">
-        <v>7018719</v>
+        <v>7018633</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15172,11 +15172,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15203,32 +15198,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129056679</v>
+        <v>129056705</v>
       </c>
       <c r="B144" t="n">
-        <v>91996</v>
+        <v>56908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15238,10 +15233,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>602737</v>
+        <v>602730</v>
       </c>
       <c r="R144" t="n">
-        <v>7018593</v>
+        <v>7018719</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15274,6 +15269,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15300,32 +15300,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129056695</v>
+        <v>129056679</v>
       </c>
       <c r="B145" t="n">
-        <v>80148</v>
+        <v>91998</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>602754</v>
+        <v>602737</v>
       </c>
       <c r="R145" t="n">
-        <v>7018633</v>
+        <v>7018593</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15400,7 +15400,7 @@
         <v>129056696</v>
       </c>
       <c r="B146" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>129048489</v>
       </c>
       <c r="B147" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>129045069</v>
       </c>
       <c r="B148" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>129046445</v>
       </c>
       <c r="B149" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15793,10 +15793,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129046543</v>
+        <v>129046382</v>
       </c>
       <c r="B150" t="n">
-        <v>90575</v>
+        <v>91843</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15804,21 +15804,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15828,10 +15828,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>602686</v>
+        <v>602637</v>
       </c>
       <c r="R150" t="n">
-        <v>7018745</v>
+        <v>7018802</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15890,10 +15890,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129046382</v>
+        <v>129056716</v>
       </c>
       <c r="B151" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15901,37 +15901,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>602637</v>
+        <v>602754</v>
       </c>
       <c r="R151" t="n">
-        <v>7018802</v>
+        <v>7018801</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15975,12 +15975,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -15990,7 +15990,7 @@
         <v>129044697</v>
       </c>
       <c r="B152" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16084,10 +16084,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129056716</v>
+        <v>129046543</v>
       </c>
       <c r="B153" t="n">
-        <v>79043</v>
+        <v>90577</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16095,37 +16095,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>602754</v>
+        <v>602686</v>
       </c>
       <c r="R153" t="n">
-        <v>7018801</v>
+        <v>7018745</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16169,57 +16169,61 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129045378</v>
+        <v>129048151</v>
       </c>
       <c r="B154" t="n">
-        <v>92261</v>
+        <v>98712</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>602682</v>
+        <v>602715</v>
       </c>
       <c r="R154" t="n">
-        <v>7018833</v>
+        <v>7018634</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16278,32 +16282,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129044275</v>
+        <v>129045378</v>
       </c>
       <c r="B155" t="n">
-        <v>91841</v>
+        <v>92263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16313,10 +16317,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>602766</v>
+        <v>602682</v>
       </c>
       <c r="R155" t="n">
-        <v>7018767</v>
+        <v>7018833</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16375,49 +16379,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129048151</v>
+        <v>129044275</v>
       </c>
       <c r="B156" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>602715</v>
+        <v>602766</v>
       </c>
       <c r="R156" t="n">
-        <v>7018634</v>
+        <v>7018767</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16476,48 +16476,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129050391</v>
+        <v>129056714</v>
       </c>
       <c r="B157" t="n">
-        <v>80052</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>602671</v>
+        <v>602678</v>
       </c>
       <c r="R157" t="n">
-        <v>7018809</v>
+        <v>7018771</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16561,22 +16561,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129056714</v>
+        <v>129056691</v>
       </c>
       <c r="B158" t="n">
-        <v>79043</v>
+        <v>10964</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16584,21 +16584,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16608,10 +16603,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>602678</v>
+        <v>602659</v>
       </c>
       <c r="R158" t="n">
-        <v>7018771</v>
+        <v>7018825</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16670,43 +16665,48 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129056691</v>
+        <v>129050391</v>
       </c>
       <c r="B159" t="n">
-        <v>10964</v>
+        <v>80053</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>101449</v>
+        <v>6456</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>602659</v>
+        <v>602671</v>
       </c>
       <c r="R159" t="n">
-        <v>7018825</v>
+        <v>7018809</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16750,12 +16750,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -16765,7 +16765,7 @@
         <v>129047010</v>
       </c>
       <c r="B160" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>129045867</v>
       </c>
       <c r="B161" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>129044553</v>
       </c>
       <c r="B162" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>129056685</v>
       </c>
       <c r="B163" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>129058444</v>
       </c>
       <c r="B164" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17256,10 +17256,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129046627</v>
+        <v>129048297</v>
       </c>
       <c r="B165" t="n">
-        <v>78800</v>
+        <v>91843</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17267,21 +17267,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17291,10 +17291,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>602705</v>
+        <v>602752</v>
       </c>
       <c r="R165" t="n">
-        <v>7018763</v>
+        <v>7018614</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -17353,10 +17353,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129046592</v>
+        <v>129044893</v>
       </c>
       <c r="B166" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17364,39 +17364,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>602704</v>
+        <v>602729</v>
       </c>
       <c r="R166" t="n">
-        <v>7018751</v>
+        <v>7018798</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17429,11 +17424,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17460,10 +17450,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129048297</v>
+        <v>129048918</v>
       </c>
       <c r="B167" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17471,34 +17461,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>602752</v>
+        <v>602737</v>
       </c>
       <c r="R167" t="n">
-        <v>7018614</v>
+        <v>7018577</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17531,6 +17526,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17557,10 +17557,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129044893</v>
+        <v>129046627</v>
       </c>
       <c r="B168" t="n">
-        <v>91841</v>
+        <v>78801</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17568,21 +17568,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>602729</v>
+        <v>602705</v>
       </c>
       <c r="R168" t="n">
-        <v>7018798</v>
+        <v>7018763</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -17654,7 +17654,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129048918</v>
+        <v>129046592</v>
       </c>
       <c r="B169" t="n">
         <v>57727</v>
@@ -17694,10 +17694,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>602737</v>
+        <v>602704</v>
       </c>
       <c r="R169" t="n">
-        <v>7018577</v>
+        <v>7018751</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Äldre ringhack tall</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17761,32 +17761,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129056666</v>
+        <v>129056678</v>
       </c>
       <c r="B170" t="n">
-        <v>96956</v>
+        <v>80053</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17796,10 +17796,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>602756</v>
+        <v>602672</v>
       </c>
       <c r="R170" t="n">
-        <v>7018643</v>
+        <v>7018832</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -17858,32 +17858,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129056678</v>
+        <v>129056666</v>
       </c>
       <c r="B171" t="n">
-        <v>80052</v>
+        <v>96958</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17893,10 +17893,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>602672</v>
+        <v>602756</v>
       </c>
       <c r="R171" t="n">
-        <v>7018832</v>
+        <v>7018643</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>

--- a/artfynd/A 44652-2025 artfynd.xlsx
+++ b/artfynd/A 44652-2025 artfynd.xlsx
@@ -6872,10 +6872,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045323</v>
+        <v>129056682</v>
       </c>
       <c r="B59" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,17 +6903,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602682</v>
+        <v>602751</v>
       </c>
       <c r="R59" t="n">
-        <v>7018848</v>
+        <v>7018603</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,12 +6957,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6972,7 +6972,7 @@
         <v>129056690</v>
       </c>
       <c r="B60" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129056682</v>
+        <v>129045323</v>
       </c>
       <c r="B61" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,17 +7097,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602751</v>
+        <v>602682</v>
       </c>
       <c r="R61" t="n">
-        <v>7018603</v>
+        <v>7018848</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7151,44 +7151,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129048977</v>
+        <v>129048001</v>
       </c>
       <c r="B62" t="n">
-        <v>91843</v>
+        <v>92002</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602712</v>
+        <v>602696</v>
       </c>
       <c r="R62" t="n">
-        <v>7018600</v>
+        <v>7018662</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7260,32 +7260,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129048001</v>
+        <v>129048977</v>
       </c>
       <c r="B63" t="n">
-        <v>91998</v>
+        <v>91847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602696</v>
+        <v>602712</v>
       </c>
       <c r="R63" t="n">
-        <v>7018662</v>
+        <v>7018600</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7457,7 +7457,7 @@
         <v>129045225</v>
       </c>
       <c r="B65" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7648,48 +7648,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044277</v>
+        <v>129056680</v>
       </c>
       <c r="B67" t="n">
-        <v>91545</v>
+        <v>92002</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602759</v>
+        <v>602732</v>
       </c>
       <c r="R67" t="n">
-        <v>7018767</v>
+        <v>7018811</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7733,44 +7733,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129056680</v>
+        <v>129056672</v>
       </c>
       <c r="B68" t="n">
-        <v>91998</v>
+        <v>91549</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602732</v>
+        <v>602651</v>
       </c>
       <c r="R68" t="n">
-        <v>7018811</v>
+        <v>7018826</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129056672</v>
+        <v>129050732</v>
       </c>
       <c r="B69" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7853,37 +7853,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602651</v>
+        <v>602710</v>
       </c>
       <c r="R69" t="n">
-        <v>7018826</v>
+        <v>7018856</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7927,22 +7927,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129050732</v>
+        <v>129044277</v>
       </c>
       <c r="B70" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602710</v>
+        <v>602759</v>
       </c>
       <c r="R70" t="n">
-        <v>7018856</v>
+        <v>7018767</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8036,48 +8036,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129045343</v>
+        <v>129056715</v>
       </c>
       <c r="B71" t="n">
-        <v>91968</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602684</v>
+        <v>602665</v>
       </c>
       <c r="R71" t="n">
-        <v>7018837</v>
+        <v>7018777</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8107,11 +8107,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8126,60 +8121,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129045733</v>
+        <v>129056712</v>
       </c>
       <c r="B72" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602669</v>
+        <v>602730</v>
       </c>
       <c r="R72" t="n">
-        <v>7018781</v>
+        <v>7018697</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8223,60 +8218,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129056715</v>
+        <v>129045343</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>91972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602665</v>
+        <v>602684</v>
       </c>
       <c r="R73" t="n">
-        <v>7018777</v>
+        <v>7018837</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8306,6 +8301,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8320,60 +8320,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129056712</v>
+        <v>129045733</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602730</v>
+        <v>602669</v>
       </c>
       <c r="R74" t="n">
-        <v>7018697</v>
+        <v>7018781</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8417,44 +8417,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129049465</v>
+        <v>129044345</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>91762</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>602650</v>
+        <v>602772</v>
       </c>
       <c r="R75" t="n">
-        <v>7018649</v>
+        <v>7018759</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129045649</v>
+        <v>129046472</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8537,21 +8537,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>602688</v>
+        <v>602666</v>
       </c>
       <c r="R76" t="n">
-        <v>7018774</v>
+        <v>7018759</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,48 +8623,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129044345</v>
+        <v>129056699</v>
       </c>
       <c r="B77" t="n">
-        <v>91758</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>602772</v>
+        <v>602729</v>
       </c>
       <c r="R77" t="n">
-        <v>7018759</v>
+        <v>7018756</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8708,22 +8708,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129046472</v>
+        <v>129056718</v>
       </c>
       <c r="B78" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8731,37 +8731,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torråsen, Torråsen, Ång</t>
+          <t>Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602666</v>
+        <v>602758</v>
       </c>
       <c r="R78" t="n">
-        <v>7018759</v>
+        <v>7018806</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8805,22 +8805,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129056676</v>
+        <v>129049465</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8828,37 +8828,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602667</v>
+        <v>602650</v>
       </c>
       <c r="R79" t="n">
-        <v>7018779</v>
+        <v>7018649</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8888,11 +8888,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,22 +8902,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129056718</v>
+        <v>129045649</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8930,37 +8925,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torråsen, Ång</t>
+          <t>Torråsen, Torråsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602758</v>
+        <v>602688</v>
       </c>
       <c r="R80" t="n">
-        <v>7018806</v>
+        <v>7018774</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9004,22 +8999,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129056699</v>
+        <v>129056676</v>
       </c>
       <c